--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP109" headerRowCount="1">
-  <autoFilter ref="A1:EP109"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP110" headerRowCount="1">
+  <autoFilter ref="A1:EP110"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP109"/>
+  <dimension ref="A1:EP110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -9918,7 +9918,7 @@
         <v>0</v>
       </c>
       <c r="DD19" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE19" t="n">
         <v>0.5</v>
@@ -11959,40 +11959,40 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
         <v>45893.52083333334</v>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J24" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -12004,111 +12004,119 @@
         <v>10</v>
       </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S24" t="n">
+        <v>6</v>
+      </c>
+      <c r="T24" t="n">
         <v>8</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
+        <v>16</v>
+      </c>
+      <c r="V24" t="n">
+        <v>12</v>
+      </c>
+      <c r="W24" t="n">
+        <v>6</v>
+      </c>
+      <c r="X24" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Stadion Galgenwaard</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>Herculesplein 241, Utrecht</t>
+        </is>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF24" t="n">
         <v>5</v>
       </c>
-      <c r="U24" t="n">
-        <v>18</v>
-      </c>
-      <c r="V24" t="n">
+      <c r="AG24" t="n">
         <v>7</v>
       </c>
-      <c r="W24" t="n">
-        <v>16</v>
-      </c>
-      <c r="X24" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>51</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>49</v>
-      </c>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AH24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AU24" t="n">
         <v>5</v>
       </c>
-      <c r="AH24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AU24" t="n">
+      <c r="AV24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>3</v>
       </c>
-      <c r="AV24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>2</v>
-      </c>
       <c r="BA24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB24" t="n">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="BC24" t="n">
         <v>0</v>
@@ -12126,76 +12134,76 @@
         <v>2</v>
       </c>
       <c r="BH24" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BJ24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BM24" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="BN24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BO24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ24" t="n">
         <v>0</v>
       </c>
       <c r="BR24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BT24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU24" t="n">
         <v>1</v>
       </c>
       <c r="BV24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BW24" t="n">
         <v>50</v>
       </c>
-      <c r="BW24" t="n">
-        <v>26</v>
-      </c>
       <c r="BX24" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="BY24" t="n">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="BZ24" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="CA24" t="n">
-        <v>0.78</v>
+        <v>1.41</v>
       </c>
       <c r="CB24" t="n">
-        <v>2.98</v>
+        <v>3.32</v>
       </c>
       <c r="CC24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD24" t="n">
         <v>0</v>
       </c>
       <c r="CE24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF24" t="n">
         <v>0</v>
@@ -12213,7 +12221,7 @@
         <v>1</v>
       </c>
       <c r="CK24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL24" t="n">
         <v>0</v>
@@ -12225,40 +12233,40 @@
         <v>0</v>
       </c>
       <c r="CO24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP24" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CQ24" t="n">
         <v>1</v>
       </c>
       <c r="CR24" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CS24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="CT24" t="n">
         <v>1</v>
       </c>
       <c r="CU24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CV24" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="CW24" t="n">
         <v>1</v>
       </c>
       <c r="CX24" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY24" t="n">
         <v>4</v>
       </c>
-      <c r="CY24" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ24" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="DA24" t="n">
         <v>100</v>
@@ -12270,10 +12278,10 @@
         <v>100</v>
       </c>
       <c r="DD24" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="DF24" t="n">
         <v>3</v>
@@ -12282,25 +12290,25 @@
         <v>0</v>
       </c>
       <c r="DH24" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DI24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="DJ24" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK24" t="n">
         <v>0</v>
       </c>
       <c r="DL24" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="DM24" t="n">
-        <v>0.6</v>
+        <v>1.31</v>
       </c>
       <c r="DN24" t="n">
-        <v>2.55</v>
+        <v>3.19</v>
       </c>
       <c r="DO24" t="n">
         <v>12</v>
@@ -12315,66 +12323,78 @@
         <v>1</v>
       </c>
       <c r="DS24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU24" t="b">
         <v>0</v>
       </c>
       <c r="DV24" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW24" t="inlineStr"/>
-      <c r="DX24" t="inlineStr"/>
-      <c r="DY24" t="inlineStr"/>
-      <c r="DZ24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="DW24" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="DX24" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="DY24" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="DZ24" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="EA24" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>6.92</t>
         </is>
       </c>
       <c r="EB24" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="EC24" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="ED24" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EE24" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="EF24" t="inlineStr"/>
       <c r="EG24" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EH24" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EI24" t="inlineStr"/>
       <c r="EJ24" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EK24" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EL24" t="inlineStr">
@@ -12383,16 +12403,8 @@
         </is>
       </c>
       <c r="EM24" t="inlineStr"/>
-      <c r="EN24" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
-      <c r="EO24" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
+      <c r="EN24" t="inlineStr"/>
+      <c r="EO24" t="inlineStr"/>
       <c r="EP24" t="inlineStr"/>
     </row>
     <row r="25">
@@ -12411,40 +12423,40 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
         <v>45893.52083333334</v>
       </c>
       <c r="G25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
         <v>4</v>
       </c>
-      <c r="H25" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>5</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7</v>
-      </c>
-      <c r="K25" t="n">
-        <v>5</v>
-      </c>
-      <c r="L25" t="n">
-        <v>12</v>
-      </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -12456,101 +12468,93 @@
         <v>10</v>
       </c>
       <c r="R25" t="n">
+        <v>2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>18</v>
+      </c>
+      <c r="V25" t="n">
+        <v>7</v>
+      </c>
+      <c r="W25" t="n">
+        <v>16</v>
+      </c>
+      <c r="X25" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>51</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>49</v>
+      </c>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD25" t="n">
         <v>4</v>
       </c>
-      <c r="S25" t="n">
-        <v>6</v>
-      </c>
-      <c r="T25" t="n">
-        <v>8</v>
-      </c>
-      <c r="U25" t="n">
-        <v>16</v>
-      </c>
-      <c r="V25" t="n">
-        <v>12</v>
-      </c>
-      <c r="W25" t="n">
-        <v>6</v>
-      </c>
-      <c r="X25" t="n">
-        <v>15</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>Stadion Galgenwaard</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>Herculesplein 241, Utrecht</t>
-        </is>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>0</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AF25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AG25" t="n">
         <v>5</v>
       </c>
-      <c r="AG25" t="n">
-        <v>7</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.2</v>
+        <v>2.56</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AO25" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AP25" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AR25" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="AU25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW25" t="n">
         <v>0</v>
@@ -12559,16 +12563,16 @@
         <v>2</v>
       </c>
       <c r="AY25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB25" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="BC25" t="n">
         <v>0</v>
@@ -12586,139 +12590,139 @@
         <v>2</v>
       </c>
       <c r="BH25" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI25" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BJ25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP25" t="n">
         <v>3</v>
       </c>
-      <c r="BM25" t="n">
-        <v>8</v>
-      </c>
-      <c r="BN25" t="n">
+      <c r="BQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>5</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW25" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX25" t="n">
+        <v>112</v>
+      </c>
+      <c r="BY25" t="n">
+        <v>87</v>
+      </c>
+      <c r="BZ25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CA25" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CB25" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR25" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS25" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU25" t="n">
+        <v>17</v>
+      </c>
+      <c r="CV25" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX25" t="n">
         <v>4</v>
       </c>
-      <c r="BO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU25" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV25" t="n">
-        <v>28</v>
-      </c>
-      <c r="BW25" t="n">
+      <c r="CY25" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ25" t="n">
         <v>50</v>
-      </c>
-      <c r="BX25" t="n">
-        <v>68</v>
-      </c>
-      <c r="BY25" t="n">
-        <v>109</v>
-      </c>
-      <c r="BZ25" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="CA25" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CB25" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="CC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI25" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ25" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CP25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="CQ25" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS25" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT25" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU25" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV25" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW25" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX25" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY25" t="n">
-        <v>4</v>
-      </c>
-      <c r="CZ25" t="n">
-        <v>100</v>
       </c>
       <c r="DA25" t="n">
         <v>100</v>
@@ -12730,10 +12734,10 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="DE25" t="n">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="DF25" t="n">
         <v>3</v>
@@ -12742,25 +12746,25 @@
         <v>0</v>
       </c>
       <c r="DH25" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI25" t="n">
         <v>1.5</v>
       </c>
-      <c r="DI25" t="n">
-        <v>0</v>
-      </c>
       <c r="DJ25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK25" t="n">
         <v>0</v>
       </c>
       <c r="DL25" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="DM25" t="n">
-        <v>1.31</v>
+        <v>0.6</v>
       </c>
       <c r="DN25" t="n">
-        <v>3.19</v>
+        <v>2.55</v>
       </c>
       <c r="DO25" t="n">
         <v>12</v>
@@ -12775,78 +12779,66 @@
         <v>1</v>
       </c>
       <c r="DS25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU25" t="b">
         <v>0</v>
       </c>
       <c r="DV25" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW25" t="n">
-        <v>20.71</v>
-      </c>
-      <c r="DX25" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="DY25" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="DZ25" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DW25" t="inlineStr"/>
+      <c r="DX25" t="inlineStr"/>
+      <c r="DY25" t="inlineStr"/>
+      <c r="DZ25" t="inlineStr"/>
       <c r="EA25" t="inlineStr">
         <is>
-          <t>6.92</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="EB25" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="EC25" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="ED25" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EE25" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EF25" t="inlineStr"/>
       <c r="EG25" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EH25" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EI25" t="inlineStr"/>
       <c r="EJ25" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EK25" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EL25" t="inlineStr">
@@ -12855,8 +12847,16 @@
         </is>
       </c>
       <c r="EM25" t="inlineStr"/>
-      <c r="EN25" t="inlineStr"/>
-      <c r="EO25" t="inlineStr"/>
+      <c r="EN25" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EO25" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
       <c r="EP25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -16171,12 +16171,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -16186,155 +16186,155 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7</v>
+      </c>
+      <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="I33" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>9</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="T33" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>14</v>
+      </c>
+      <c r="W33" t="n">
+        <v>13</v>
+      </c>
+      <c r="X33" t="n">
         <v>10</v>
       </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>11</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>13</v>
-      </c>
-      <c r="U33" t="n">
-        <v>7</v>
-      </c>
-      <c r="V33" t="n">
-        <v>24</v>
-      </c>
-      <c r="W33" t="n">
-        <v>5</v>
-      </c>
-      <c r="X33" t="n">
-        <v>9</v>
-      </c>
       <c r="Y33" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Z33" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Sparta-Stadion Het Kasteel</t>
+          <t>MAC³PARK Stadion</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Spartapark Noord 1, Rotterdam</t>
+          <t>Stadionplein 1, Zwolle</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.76</v>
+        <v>2.19</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.52</v>
+        <v>2.98</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AO33" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AU33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV33" t="n">
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB33" t="n">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -16349,37 +16349,37 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK33" t="n">
         <v>1</v>
       </c>
       <c r="BL33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BN33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BO33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP33" t="n">
         <v>1</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT33" t="n">
         <v>2</v>
@@ -16388,25 +16388,25 @@
         <v>1</v>
       </c>
       <c r="BV33" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BW33" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="BX33" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="BY33" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="CA33" t="n">
-        <v>2.94</v>
+        <v>1.56</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.78</v>
+        <v>2.43</v>
       </c>
       <c r="CC33" t="n">
         <v>0</v>
@@ -16439,7 +16439,7 @@
         <v>0</v>
       </c>
       <c r="CM33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
@@ -16454,7 +16454,7 @@
         <v>1</v>
       </c>
       <c r="CR33" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CS33" t="n">
         <v>15</v>
@@ -16463,28 +16463,28 @@
         <v>1</v>
       </c>
       <c r="CU33" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY33" t="n">
         <v>9</v>
       </c>
-      <c r="CV33" t="n">
-        <v>5</v>
-      </c>
-      <c r="CW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX33" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY33" t="n">
-        <v>1</v>
-      </c>
       <c r="CZ33" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA33" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC33" t="n">
         <v>100</v>
@@ -16493,34 +16493,34 @@
         <v>1.17</v>
       </c>
       <c r="DE33" t="n">
-        <v>2.17</v>
+        <v>0.6</v>
       </c>
       <c r="DF33" t="n">
         <v>3</v>
       </c>
       <c r="DG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH33" t="n">
         <v>3</v>
       </c>
-      <c r="DH33" t="n">
-        <v>2</v>
-      </c>
       <c r="DI33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL33" t="n">
-        <v>1.52</v>
+        <v>0.93</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="DN33" t="n">
-        <v>3.42</v>
+        <v>2.92</v>
       </c>
       <c r="DO33" t="n">
         <v>12</v>
@@ -16532,10 +16532,10 @@
         <v>1</v>
       </c>
       <c r="DR33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT33" t="b">
         <v>0</v>
@@ -16547,84 +16547,84 @@
         <v>0</v>
       </c>
       <c r="DW33" t="n">
-        <v>20.4</v>
+        <v>17.16</v>
       </c>
       <c r="DX33" t="n">
-        <v>6.09</v>
+        <v>6.34</v>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="DZ33" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA33" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="ED33" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EE33" t="inlineStr">
         <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EF33" t="inlineStr"/>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EF33" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
       <c r="EG33" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="EH33" t="inlineStr">
         <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="EI33" t="inlineStr"/>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
       <c r="EJ33" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EK33" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EL33" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EM33" t="inlineStr"/>
-      <c r="EN33" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EO33" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
+      <c r="EN33" t="inlineStr"/>
+      <c r="EO33" t="inlineStr"/>
       <c r="EP33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -16643,12 +16643,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -16658,155 +16658,155 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>13</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>24</v>
+      </c>
+      <c r="W34" t="n">
+        <v>5</v>
+      </c>
+      <c r="X34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Sparta-Stadion Het Kasteel</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Spartapark Noord 1, Rotterdam</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
         <v>3</v>
       </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="AD34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU34" t="n">
         <v>4</v>
       </c>
-      <c r="T34" t="n">
-        <v>7</v>
-      </c>
-      <c r="U34" t="n">
-        <v>6</v>
-      </c>
-      <c r="V34" t="n">
-        <v>14</v>
-      </c>
-      <c r="W34" t="n">
-        <v>13</v>
-      </c>
-      <c r="X34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>MAC³PARK Stadion</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>Stadionplein 1, Zwolle</t>
-        </is>
-      </c>
-      <c r="AC34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2</v>
-      </c>
       <c r="AV34" t="n">
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
         <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16821,37 +16821,37 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK34" t="n">
         <v>1</v>
       </c>
       <c r="BL34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BM34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP34" t="n">
         <v>1</v>
       </c>
       <c r="BQ34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT34" t="n">
         <v>2</v>
@@ -16860,25 +16860,25 @@
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BW34" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="BX34" t="n">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="BY34" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.56</v>
+        <v>2.94</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.43</v>
+        <v>3.78</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -16911,7 +16911,7 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CS34" t="n">
         <v>15</v>
@@ -16935,28 +16935,28 @@
         <v>1</v>
       </c>
       <c r="CU34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CV34" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="CW34" t="n">
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CY34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="CZ34" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB34" t="n">
         <v>50</v>
-      </c>
-      <c r="DA34" t="n">
-        <v>50</v>
-      </c>
-      <c r="DB34" t="n">
-        <v>0</v>
       </c>
       <c r="DC34" t="n">
         <v>100</v>
@@ -16965,34 +16965,34 @@
         <v>1.17</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.6</v>
+        <v>2.17</v>
       </c>
       <c r="DF34" t="n">
         <v>3</v>
       </c>
       <c r="DG34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH34" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI34" t="n">
         <v>3</v>
       </c>
-      <c r="DI34" t="n">
-        <v>2</v>
-      </c>
       <c r="DJ34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL34" t="n">
-        <v>0.93</v>
+        <v>1.52</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="DN34" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="DO34" t="n">
         <v>12</v>
@@ -17004,10 +17004,10 @@
         <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT34" t="b">
         <v>0</v>
@@ -17019,84 +17019,84 @@
         <v>0</v>
       </c>
       <c r="DW34" t="n">
-        <v>17.16</v>
+        <v>20.4</v>
       </c>
       <c r="DX34" t="n">
-        <v>6.34</v>
+        <v>6.09</v>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="EF34" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EF34" t="inlineStr"/>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI34" t="inlineStr">
-        <is>
-          <t>3.24</t>
-        </is>
-      </c>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr"/>
       <c r="EJ34" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK34" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EL34" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="EM34" t="inlineStr"/>
-      <c r="EN34" t="inlineStr"/>
-      <c r="EO34" t="inlineStr"/>
+      <c r="EN34" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EO34" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
       <c r="EP34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -17434,7 +17434,7 @@
         <v>100</v>
       </c>
       <c r="DD35" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE35" t="n">
         <v>2.17</v>
@@ -24474,7 +24474,7 @@
         <v>75</v>
       </c>
       <c r="DD50" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE50" t="n">
         <v>0.43</v>
@@ -25091,46 +25091,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>45921.52083333334</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
         <v>2</v>
       </c>
       <c r="I52" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>9</v>
+      </c>
+      <c r="K52" t="n">
         <v>5</v>
       </c>
-      <c r="J52" t="n">
-        <v>6</v>
-      </c>
-      <c r="K52" t="n">
-        <v>6</v>
-      </c>
       <c r="L52" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M52" t="n">
         <v>2</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>8</v>
@@ -25139,122 +25139,122 @@
         <v>6</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T52" t="n">
+        <v>8</v>
+      </c>
+      <c r="U52" t="n">
+        <v>16</v>
+      </c>
+      <c r="V52" t="n">
+        <v>14</v>
+      </c>
+      <c r="W52" t="n">
+        <v>17</v>
+      </c>
+      <c r="X52" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Philips Stadion</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Frederiklaan 10, Eindhoven</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD52" t="n">
         <v>5</v>
       </c>
-      <c r="U52" t="n">
-        <v>14</v>
-      </c>
-      <c r="V52" t="n">
-        <v>11</v>
-      </c>
-      <c r="W52" t="n">
-        <v>10</v>
-      </c>
-      <c r="X52" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>39</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Abe Lenstra Stadion</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>Abe Lenstra Boulevard 23Q, Heerenveen</t>
-        </is>
-      </c>
-      <c r="AC52" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>3</v>
-      </c>
       <c r="AE52" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AF52" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AO52" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AS52" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AU52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV52" t="n">
         <v>1</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB52" t="n">
-        <v>373</v>
+        <v>-1</v>
       </c>
       <c r="BC52" t="n">
         <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="BE52" t="n">
         <v>0</v>
@@ -25272,73 +25272,73 @@
         <v>4</v>
       </c>
       <c r="BJ52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BL52" t="n">
         <v>4</v>
       </c>
       <c r="BM52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN52" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BO52" t="n">
         <v>1</v>
       </c>
       <c r="BP52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ52" t="n">
         <v>1</v>
       </c>
       <c r="BR52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BS52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU52" t="n">
         <v>1</v>
       </c>
       <c r="BV52" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW52" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BX52" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="BY52" t="n">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="BZ52" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="CB52" t="n">
-        <v>3.17</v>
+        <v>3.44</v>
       </c>
       <c r="CC52" t="n">
         <v>0</v>
       </c>
       <c r="CD52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE52" t="n">
         <v>0</v>
       </c>
       <c r="CF52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG52" t="n">
         <v>0</v>
@@ -25353,7 +25353,7 @@
         <v>1</v>
       </c>
       <c r="CK52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL52" t="n">
         <v>0</v>
@@ -25362,7 +25362,7 @@
         <v>0</v>
       </c>
       <c r="CN52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO52" t="n">
         <v>0</v>
@@ -25374,73 +25374,73 @@
         <v>1</v>
       </c>
       <c r="CR52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="CS52" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="CT52" t="n">
         <v>1</v>
       </c>
       <c r="CU52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV52" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW52" t="n">
         <v>1</v>
       </c>
       <c r="CX52" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY52" t="n">
         <v>8</v>
       </c>
-      <c r="CY52" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ52" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="DA52" t="n">
         <v>100</v>
       </c>
       <c r="DB52" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="DC52" t="n">
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.5</v>
+        <v>2.17</v>
       </c>
       <c r="DE52" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DF52" t="n">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="DG52" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DH52" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="DI52" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="DJ52" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="DK52" t="n">
         <v>0</v>
       </c>
       <c r="DL52" t="n">
-        <v>1.93</v>
+        <v>2.56</v>
       </c>
       <c r="DM52" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="DN52" t="n">
-        <v>4.43</v>
+        <v>4.61</v>
       </c>
       <c r="DO52" t="n">
         <v>12</v>
@@ -25458,7 +25458,7 @@
         <v>1</v>
       </c>
       <c r="DT52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU52" t="b">
         <v>0</v>
@@ -25467,14 +25467,14 @@
         <v>1</v>
       </c>
       <c r="DW52" t="n">
-        <v>14.97</v>
+        <v>17.9</v>
       </c>
       <c r="DX52" t="n">
-        <v>8.869999999999999</v>
+        <v>5.53</v>
       </c>
       <c r="DY52" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="DZ52" t="inlineStr">
@@ -25484,27 +25484,27 @@
       </c>
       <c r="EA52" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="EB52" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="EC52" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="ED52" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EE52" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EF52" t="inlineStr"/>
@@ -25513,30 +25513,22 @@
       <c r="EI52" t="inlineStr"/>
       <c r="EJ52" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EK52" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EL52" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="EM52" t="inlineStr"/>
-      <c r="EN52" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EO52" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
+      <c r="EN52" t="inlineStr"/>
+      <c r="EO52" t="inlineStr"/>
       <c r="EP52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -25555,46 +25547,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45921.52083333334</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L53" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M53" t="n">
         <v>2</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>8</v>
@@ -25603,122 +25595,122 @@
         <v>6</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U53" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V53" t="n">
+        <v>11</v>
+      </c>
+      <c r="W53" t="n">
+        <v>10</v>
+      </c>
+      <c r="X53" t="n">
         <v>14</v>
       </c>
-      <c r="W53" t="n">
-        <v>17</v>
-      </c>
-      <c r="X53" t="n">
-        <v>13</v>
-      </c>
       <c r="Y53" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="Z53" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Philips Stadion</t>
+          <t>Abe Lenstra Stadion</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Frederiklaan 10, Eindhoven</t>
+          <t>Abe Lenstra Boulevard 23Q, Heerenveen</t>
         </is>
       </c>
       <c r="AC53" t="n">
         <v>2</v>
       </c>
       <c r="AD53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU53" t="n">
         <v>5</v>
       </c>
-      <c r="AE53" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AU53" t="n">
+      <c r="AV53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ53" t="n">
         <v>4</v>
       </c>
-      <c r="AV53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>2</v>
-      </c>
       <c r="BA53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB53" t="n">
-        <v>-1</v>
+        <v>373</v>
       </c>
       <c r="BC53" t="n">
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25736,175 +25728,175 @@
         <v>4</v>
       </c>
       <c r="BJ53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BL53" t="n">
         <v>4</v>
       </c>
       <c r="BM53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BO53" t="n">
         <v>1</v>
       </c>
       <c r="BP53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ53" t="n">
         <v>1</v>
       </c>
       <c r="BR53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY53" t="n">
         <v>4</v>
       </c>
-      <c r="BS53" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT53" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU53" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV53" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW53" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX53" t="n">
-        <v>118</v>
-      </c>
-      <c r="BY53" t="n">
-        <v>59</v>
-      </c>
-      <c r="BZ53" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CA53" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CB53" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="CC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>10</v>
-      </c>
-      <c r="CS53" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU53" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV53" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX53" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY53" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ53" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="DA53" t="n">
         <v>100</v>
       </c>
       <c r="DB53" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="DC53" t="n">
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="DF53" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="DG53" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DH53" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="DI53" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="DJ53" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="DK53" t="n">
         <v>0</v>
       </c>
       <c r="DL53" t="n">
-        <v>2.56</v>
+        <v>1.93</v>
       </c>
       <c r="DM53" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="DN53" t="n">
-        <v>4.61</v>
+        <v>4.43</v>
       </c>
       <c r="DO53" t="n">
         <v>12</v>
@@ -25922,7 +25914,7 @@
         <v>1</v>
       </c>
       <c r="DT53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU53" t="b">
         <v>0</v>
@@ -25931,14 +25923,14 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>17.9</v>
+        <v>14.97</v>
       </c>
       <c r="DX53" t="n">
-        <v>5.53</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
@@ -25948,27 +25940,27 @@
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EB53" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="EC53" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="ED53" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EE53" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EF53" t="inlineStr"/>
@@ -25977,22 +25969,30 @@
       <c r="EI53" t="inlineStr"/>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr"/>
-      <c r="EN53" t="inlineStr"/>
-      <c r="EO53" t="inlineStr"/>
+      <c r="EN53" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EO53" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
       <c r="EP53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -31506,7 +31506,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE65" t="n">
         <v>1.5</v>
@@ -37243,40 +37243,40 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>45948.79166666666</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>2</v>
       </c>
       <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" t="n">
         <v>4</v>
       </c>
-      <c r="J78" t="n">
-        <v>3</v>
-      </c>
-      <c r="K78" t="n">
-        <v>2</v>
-      </c>
       <c r="L78" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -37291,122 +37291,122 @@
         <v>3</v>
       </c>
       <c r="S78" t="n">
+        <v>11</v>
+      </c>
+      <c r="T78" t="n">
+        <v>10</v>
+      </c>
+      <c r="U78" t="n">
+        <v>17</v>
+      </c>
+      <c r="V78" t="n">
         <v>13</v>
       </c>
-      <c r="T78" t="n">
-        <v>8</v>
-      </c>
-      <c r="U78" t="n">
+      <c r="W78" t="n">
+        <v>13</v>
+      </c>
+      <c r="X78" t="n">
         <v>19</v>
       </c>
-      <c r="V78" t="n">
-        <v>11</v>
-      </c>
-      <c r="W78" t="n">
-        <v>9</v>
-      </c>
-      <c r="X78" t="n">
-        <v>10</v>
-      </c>
       <c r="Y78" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="Z78" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Rat Verlegh Stadion</t>
+          <t>Johan Cruijff Arena</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>Stadionstraat 23, Breda</t>
+          <t>ArenA Boulevard 1, Amsterdam</t>
         </is>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AF78" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="AG78" t="n">
-        <v>3.15</v>
+        <v>3.46</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AJ78" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="AK78" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL78" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AM78" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AN78" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AO78" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR78" t="n">
-        <v>2.59</v>
+        <v>2.27</v>
       </c>
       <c r="AS78" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AT78" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AU78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX78" t="n">
         <v>0</v>
       </c>
       <c r="AY78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB78" t="n">
-        <v>-1</v>
+        <v>378</v>
       </c>
       <c r="BC78" t="n">
         <v>0</v>
       </c>
       <c r="BD78" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="BE78" t="n">
         <v>0</v>
@@ -37421,22 +37421,22 @@
         <v>1</v>
       </c>
       <c r="BI78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK78" t="n">
         <v>3</v>
       </c>
-      <c r="BJ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK78" t="n">
-        <v>0</v>
-      </c>
       <c r="BL78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM78" t="n">
         <v>3</v>
       </c>
       <c r="BN78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BO78" t="n">
         <v>0</v>
@@ -37445,52 +37445,52 @@
         <v>1</v>
       </c>
       <c r="BQ78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BR78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS78" t="n">
         <v>1</v>
       </c>
       <c r="BT78" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU78" t="n">
         <v>1</v>
       </c>
       <c r="BV78" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="BW78" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="BX78" t="n">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="BY78" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="BZ78" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="CA78" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="CB78" t="n">
         <v>3.21</v>
       </c>
       <c r="CC78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG78" t="n">
         <v>0</v>
@@ -37511,7 +37511,7 @@
         <v>0</v>
       </c>
       <c r="CM78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN78" t="n">
         <v>0</v>
@@ -37526,19 +37526,19 @@
         <v>1</v>
       </c>
       <c r="CR78" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CS78" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV78" t="n">
         <v>12</v>
-      </c>
-      <c r="CT78" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU78" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV78" t="n">
-        <v>11</v>
       </c>
       <c r="CW78" t="n">
         <v>1</v>
@@ -37550,49 +37550,49 @@
         <v>9</v>
       </c>
       <c r="CZ78" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="DA78" t="n">
         <v>88</v>
       </c>
       <c r="DB78" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="DC78" t="n">
         <v>88</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.67</v>
+        <v>2.17</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.83</v>
+        <v>2.17</v>
       </c>
       <c r="DF78" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DG78" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DH78" t="n">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="DI78" t="n">
-        <v>0.88</v>
+        <v>1.88</v>
       </c>
       <c r="DJ78" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="DK78" t="n">
         <v>13</v>
       </c>
       <c r="DL78" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="DM78" t="n">
-        <v>1.1</v>
+        <v>1.93</v>
       </c>
       <c r="DN78" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="DO78" t="n">
         <v>12</v>
@@ -37604,10 +37604,10 @@
         <v>1</v>
       </c>
       <c r="DR78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT78" t="b">
         <v>0</v>
@@ -37616,102 +37616,94 @@
         <v>0</v>
       </c>
       <c r="DV78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW78" t="n">
-        <v>13.08</v>
+        <v>12.42</v>
       </c>
       <c r="DX78" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="DY78" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ78" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="EA78" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EB78" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="EC78" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="ED78" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EE78" t="inlineStr">
         <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EF78" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr"/>
       <c r="EG78" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EH78" t="inlineStr">
         <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EI78" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr"/>
       <c r="EJ78" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EK78" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EL78" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EM78" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EN78" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EO78" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EP78" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
@@ -37731,40 +37723,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45948.79166666666</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J79" t="n">
+        <v>3</v>
+      </c>
+      <c r="K79" t="n">
+        <v>2</v>
+      </c>
+      <c r="L79" t="n">
         <v>5</v>
       </c>
-      <c r="K79" t="n">
-        <v>4</v>
-      </c>
-      <c r="L79" t="n">
-        <v>9</v>
-      </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -37779,122 +37771,122 @@
         <v>3</v>
       </c>
       <c r="S79" t="n">
+        <v>13</v>
+      </c>
+      <c r="T79" t="n">
+        <v>8</v>
+      </c>
+      <c r="U79" t="n">
+        <v>19</v>
+      </c>
+      <c r="V79" t="n">
         <v>11</v>
       </c>
-      <c r="T79" t="n">
+      <c r="W79" t="n">
+        <v>9</v>
+      </c>
+      <c r="X79" t="n">
         <v>10</v>
       </c>
-      <c r="U79" t="n">
-        <v>17</v>
-      </c>
-      <c r="V79" t="n">
-        <v>13</v>
-      </c>
-      <c r="W79" t="n">
-        <v>13</v>
-      </c>
-      <c r="X79" t="n">
-        <v>19</v>
-      </c>
       <c r="Y79" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="Z79" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Johan Cruijff Arena</t>
+          <t>Rat Verlegh Stadion</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>ArenA Boulevard 1, Amsterdam</t>
+          <t>Stadionstraat 23, Breda</t>
         </is>
       </c>
       <c r="AC79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU79" t="n">
         <v>4</v>
       </c>
-      <c r="AD79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF79" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AG79" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AH79" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI79" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ79" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AK79" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM79" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AN79" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AS79" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT79" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AU79" t="n">
-        <v>2</v>
-      </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX79" t="n">
         <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB79" t="n">
-        <v>378</v>
+        <v>-1</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -37909,22 +37901,22 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM79" t="n">
         <v>3</v>
       </c>
       <c r="BN79" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BO79" t="n">
         <v>0</v>
@@ -37933,52 +37925,52 @@
         <v>1</v>
       </c>
       <c r="BQ79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BR79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS79" t="n">
         <v>1</v>
       </c>
       <c r="BT79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="BW79" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="BX79" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="BY79" t="n">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="BZ79" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="CB79" t="n">
         <v>3.21</v>
       </c>
       <c r="CC79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -37999,7 +37991,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -38014,19 +38006,19 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CS79" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CT79" t="n">
         <v>1</v>
       </c>
       <c r="CU79" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="CV79" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
@@ -38038,49 +38030,49 @@
         <v>9</v>
       </c>
       <c r="CZ79" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="DA79" t="n">
         <v>88</v>
       </c>
       <c r="DB79" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="DC79" t="n">
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>2.17</v>
+        <v>1.43</v>
       </c>
       <c r="DE79" t="n">
-        <v>2.17</v>
+        <v>0.83</v>
       </c>
       <c r="DF79" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DG79" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="DH79" t="n">
-        <v>2</v>
+        <v>0.88</v>
       </c>
       <c r="DI79" t="n">
-        <v>1.88</v>
+        <v>0.88</v>
       </c>
       <c r="DJ79" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="DK79" t="n">
         <v>13</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.93</v>
+        <v>1.1</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="DO79" t="n">
         <v>12</v>
@@ -38092,10 +38084,10 @@
         <v>1</v>
       </c>
       <c r="DR79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT79" t="b">
         <v>0</v>
@@ -38104,94 +38096,102 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>12.42</v>
+        <v>13.08</v>
       </c>
       <c r="DX79" t="n">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="EF79" t="inlineStr"/>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr"/>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EM79" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
@@ -45122,7 +45122,7 @@
         <v>80</v>
       </c>
       <c r="DD94" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="DE94" t="n">
         <v>0.83</v>
@@ -52266,6 +52266,470 @@
         </is>
       </c>
       <c r="EP109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Netherlands_Eredivisie_2025-2026</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>13</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NAC Breda</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>PSV</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>45983.64583333334</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J110" t="n">
+        <v>6</v>
+      </c>
+      <c r="K110" t="n">
+        <v>5</v>
+      </c>
+      <c r="L110" t="n">
+        <v>11</v>
+      </c>
+      <c r="M110" t="n">
+        <v>2</v>
+      </c>
+      <c r="N110" t="n">
+        <v>1</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>3</v>
+      </c>
+      <c r="R110" t="n">
+        <v>4</v>
+      </c>
+      <c r="S110" t="n">
+        <v>13</v>
+      </c>
+      <c r="T110" t="n">
+        <v>5</v>
+      </c>
+      <c r="U110" t="n">
+        <v>16</v>
+      </c>
+      <c r="V110" t="n">
+        <v>9</v>
+      </c>
+      <c r="W110" t="n">
+        <v>11</v>
+      </c>
+      <c r="X110" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y110" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z110" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>Rat Verlegh Stadion</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>Stadionstraat 23, Breda</t>
+        </is>
+      </c>
+      <c r="AC110" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE110" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AF110" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH110" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI110" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK110" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL110" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM110" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AN110" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AP110" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ110" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR110" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS110" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AT110" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY110" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB110" t="n">
+        <v>121</v>
+      </c>
+      <c r="BC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD110" t="n">
+        <v>67</v>
+      </c>
+      <c r="BE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI110" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL110" t="n">
+        <v>4</v>
+      </c>
+      <c r="BM110" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN110" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ110" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS110" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT110" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU110" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV110" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW110" t="n">
+        <v>10</v>
+      </c>
+      <c r="BX110" t="n">
+        <v>10</v>
+      </c>
+      <c r="BY110" t="n">
+        <v>11</v>
+      </c>
+      <c r="BZ110" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CA110" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="CB110" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CC110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP110" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR110" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS110" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU110" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV110" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW110" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX110" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY110" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ110" t="n">
+        <v>75</v>
+      </c>
+      <c r="DA110" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB110" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC110" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD110" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE110" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF110" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DG110" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH110" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI110" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DJ110" t="n">
+        <v>25</v>
+      </c>
+      <c r="DK110" t="n">
+        <v>17</v>
+      </c>
+      <c r="DL110" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="DM110" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DN110" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="DO110" t="n">
+        <v>13</v>
+      </c>
+      <c r="DP110" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV110" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW110" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="DX110" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="DY110" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="DZ110" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA110" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EB110" t="inlineStr">
+        <is>
+          <t>6.26</t>
+        </is>
+      </c>
+      <c r="EC110" t="inlineStr">
+        <is>
+          <t>7.70</t>
+        </is>
+      </c>
+      <c r="ED110" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EE110" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EF110" t="inlineStr"/>
+      <c r="EG110" t="inlineStr"/>
+      <c r="EH110" t="inlineStr"/>
+      <c r="EI110" t="inlineStr"/>
+      <c r="EJ110" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EK110" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EL110" t="inlineStr">
+        <is>
+          <t>1.12</t>
+        </is>
+      </c>
+      <c r="EM110" t="inlineStr"/>
+      <c r="EN110" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EO110" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EP110" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP118" headerRowCount="1">
-  <autoFilter ref="A1:EP118"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP119" headerRowCount="1">
+  <autoFilter ref="A1:EP119"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP118"/>
+  <dimension ref="A1:EP119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -4186,7 +4186,7 @@
         <v>0</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="DE7" t="n">
         <v>1.29</v>
@@ -7521,7 +7521,7 @@
         <v>1.57</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF14" t="n">
         <v>0</v>
@@ -16490,7 +16490,7 @@
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="DE33" t="n">
         <v>0.67</v>
@@ -19313,7 +19313,7 @@
         <v>2.14</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF39" t="n">
         <v>3</v>
@@ -24946,7 +24946,7 @@
         <v>100</v>
       </c>
       <c r="DD51" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="DE51" t="n">
         <v>0.71</v>
@@ -25091,46 +25091,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>45921.52083333334</v>
       </c>
       <c r="G52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H52" t="n">
         <v>2</v>
       </c>
       <c r="I52" t="n">
+        <v>4</v>
+      </c>
+      <c r="J52" t="n">
+        <v>9</v>
+      </c>
+      <c r="K52" t="n">
         <v>5</v>
       </c>
-      <c r="J52" t="n">
-        <v>6</v>
-      </c>
-      <c r="K52" t="n">
-        <v>6</v>
-      </c>
       <c r="L52" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M52" t="n">
         <v>2</v>
       </c>
       <c r="N52" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>8</v>
@@ -25139,122 +25139,122 @@
         <v>6</v>
       </c>
       <c r="S52" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T52" t="n">
+        <v>8</v>
+      </c>
+      <c r="U52" t="n">
+        <v>16</v>
+      </c>
+      <c r="V52" t="n">
+        <v>14</v>
+      </c>
+      <c r="W52" t="n">
+        <v>17</v>
+      </c>
+      <c r="X52" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>62</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>Philips Stadion</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>Frederiklaan 10, Eindhoven</t>
+        </is>
+      </c>
+      <c r="AC52" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD52" t="n">
         <v>5</v>
       </c>
-      <c r="U52" t="n">
-        <v>14</v>
-      </c>
-      <c r="V52" t="n">
-        <v>11</v>
-      </c>
-      <c r="W52" t="n">
-        <v>10</v>
-      </c>
-      <c r="X52" t="n">
-        <v>14</v>
-      </c>
-      <c r="Y52" t="n">
-        <v>39</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>61</v>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>Abe Lenstra Stadion</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>Abe Lenstra Boulevard 23Q, Heerenveen</t>
-        </is>
-      </c>
-      <c r="AC52" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>3</v>
-      </c>
       <c r="AE52" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="AF52" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AG52" t="n">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.34</v>
+        <v>2.01</v>
       </c>
       <c r="AK52" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AL52" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AO52" t="n">
-        <v>2.88</v>
+        <v>2.61</v>
       </c>
       <c r="AP52" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="AQ52" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AR52" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AS52" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AT52" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AU52" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV52" t="n">
         <v>1</v>
       </c>
       <c r="AW52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB52" t="n">
-        <v>373</v>
+        <v>-1</v>
       </c>
       <c r="BC52" t="n">
         <v>0</v>
       </c>
       <c r="BD52" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="BE52" t="n">
         <v>0</v>
@@ -25272,73 +25272,73 @@
         <v>4</v>
       </c>
       <c r="BJ52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BL52" t="n">
         <v>4</v>
       </c>
       <c r="BM52" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BN52" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BO52" t="n">
         <v>1</v>
       </c>
       <c r="BP52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ52" t="n">
         <v>1</v>
       </c>
       <c r="BR52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BS52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BU52" t="n">
         <v>1</v>
       </c>
       <c r="BV52" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW52" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BX52" t="n">
-        <v>73</v>
+        <v>118</v>
       </c>
       <c r="BY52" t="n">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="BZ52" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="CA52" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="CB52" t="n">
-        <v>3.17</v>
+        <v>3.44</v>
       </c>
       <c r="CC52" t="n">
         <v>0</v>
       </c>
       <c r="CD52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE52" t="n">
         <v>0</v>
       </c>
       <c r="CF52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG52" t="n">
         <v>0</v>
@@ -25353,7 +25353,7 @@
         <v>1</v>
       </c>
       <c r="CK52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL52" t="n">
         <v>0</v>
@@ -25362,7 +25362,7 @@
         <v>0</v>
       </c>
       <c r="CN52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO52" t="n">
         <v>0</v>
@@ -25374,73 +25374,73 @@
         <v>1</v>
       </c>
       <c r="CR52" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="CS52" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="CT52" t="n">
         <v>1</v>
       </c>
       <c r="CU52" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="CV52" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CW52" t="n">
         <v>1</v>
       </c>
       <c r="CX52" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY52" t="n">
         <v>8</v>
       </c>
-      <c r="CY52" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ52" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
       <c r="DA52" t="n">
         <v>100</v>
       </c>
       <c r="DB52" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="DC52" t="n">
         <v>100</v>
       </c>
       <c r="DD52" t="n">
-        <v>1.71</v>
+        <v>2.17</v>
       </c>
       <c r="DE52" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="DF52" t="n">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="DG52" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DH52" t="n">
-        <v>0.4</v>
+        <v>2.4</v>
       </c>
       <c r="DI52" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="DJ52" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="DK52" t="n">
         <v>0</v>
       </c>
       <c r="DL52" t="n">
-        <v>1.93</v>
+        <v>2.56</v>
       </c>
       <c r="DM52" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="DN52" t="n">
-        <v>4.43</v>
+        <v>4.61</v>
       </c>
       <c r="DO52" t="n">
         <v>13</v>
@@ -25458,7 +25458,7 @@
         <v>1</v>
       </c>
       <c r="DT52" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU52" t="b">
         <v>0</v>
@@ -25467,14 +25467,14 @@
         <v>1</v>
       </c>
       <c r="DW52" t="n">
-        <v>14.97</v>
+        <v>17.9</v>
       </c>
       <c r="DX52" t="n">
-        <v>8.869999999999999</v>
+        <v>5.53</v>
       </c>
       <c r="DY52" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="DZ52" t="inlineStr">
@@ -25484,27 +25484,27 @@
       </c>
       <c r="EA52" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="EB52" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>4.44</t>
         </is>
       </c>
       <c r="EC52" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="ED52" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EE52" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="EF52" t="inlineStr"/>
@@ -25513,30 +25513,22 @@
       <c r="EI52" t="inlineStr"/>
       <c r="EJ52" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EK52" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EL52" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="EM52" t="inlineStr"/>
-      <c r="EN52" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EO52" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
+      <c r="EN52" t="inlineStr"/>
+      <c r="EO52" t="inlineStr"/>
       <c r="EP52" t="inlineStr"/>
     </row>
     <row r="53">
@@ -25555,46 +25547,46 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>45921.52083333334</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H53" t="n">
         <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L53" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M53" t="n">
         <v>2</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q53" t="n">
         <v>8</v>
@@ -25603,122 +25595,122 @@
         <v>6</v>
       </c>
       <c r="S53" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T53" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U53" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="V53" t="n">
+        <v>11</v>
+      </c>
+      <c r="W53" t="n">
+        <v>10</v>
+      </c>
+      <c r="X53" t="n">
         <v>14</v>
       </c>
-      <c r="W53" t="n">
-        <v>17</v>
-      </c>
-      <c r="X53" t="n">
-        <v>13</v>
-      </c>
       <c r="Y53" t="n">
-        <v>62</v>
+        <v>39</v>
       </c>
       <c r="Z53" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Philips Stadion</t>
+          <t>Abe Lenstra Stadion</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>Frederiklaan 10, Eindhoven</t>
+          <t>Abe Lenstra Boulevard 23Q, Heerenveen</t>
         </is>
       </c>
       <c r="AC53" t="n">
         <v>2</v>
       </c>
       <c r="AD53" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU53" t="n">
         <v>5</v>
       </c>
-      <c r="AE53" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AU53" t="n">
+      <c r="AV53" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ53" t="n">
         <v>4</v>
       </c>
-      <c r="AV53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ53" t="n">
-        <v>2</v>
-      </c>
       <c r="BA53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB53" t="n">
-        <v>-1</v>
+        <v>373</v>
       </c>
       <c r="BC53" t="n">
         <v>0</v>
       </c>
       <c r="BD53" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="BE53" t="n">
         <v>0</v>
@@ -25736,175 +25728,175 @@
         <v>4</v>
       </c>
       <c r="BJ53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BL53" t="n">
         <v>4</v>
       </c>
       <c r="BM53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN53" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BO53" t="n">
         <v>1</v>
       </c>
       <c r="BP53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ53" t="n">
         <v>1</v>
       </c>
       <c r="BR53" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>42</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>73</v>
+      </c>
+      <c r="BY53" t="n">
+        <v>104</v>
+      </c>
+      <c r="BZ53" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CA53" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CB53" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR53" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS53" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU53" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV53" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW53" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX53" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY53" t="n">
         <v>4</v>
       </c>
-      <c r="BS53" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT53" t="n">
-        <v>5</v>
-      </c>
-      <c r="BU53" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV53" t="n">
-        <v>44</v>
-      </c>
-      <c r="BW53" t="n">
-        <v>34</v>
-      </c>
-      <c r="BX53" t="n">
-        <v>118</v>
-      </c>
-      <c r="BY53" t="n">
-        <v>59</v>
-      </c>
-      <c r="BZ53" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CA53" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CB53" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="CC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP53" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>10</v>
-      </c>
-      <c r="CS53" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU53" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV53" t="n">
-        <v>16</v>
-      </c>
-      <c r="CW53" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX53" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY53" t="n">
-        <v>8</v>
-      </c>
       <c r="CZ53" t="n">
-        <v>59</v>
+        <v>84</v>
       </c>
       <c r="DA53" t="n">
         <v>100</v>
       </c>
       <c r="DB53" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="DC53" t="n">
         <v>100</v>
       </c>
       <c r="DD53" t="n">
-        <v>2.17</v>
+        <v>1.71</v>
       </c>
       <c r="DE53" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DF53" t="n">
-        <v>2</v>
+        <v>0.67</v>
       </c>
       <c r="DG53" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DH53" t="n">
-        <v>2.4</v>
+        <v>0.4</v>
       </c>
       <c r="DI53" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="DJ53" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="DK53" t="n">
         <v>0</v>
       </c>
       <c r="DL53" t="n">
-        <v>2.56</v>
+        <v>1.93</v>
       </c>
       <c r="DM53" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="DN53" t="n">
-        <v>4.61</v>
+        <v>4.43</v>
       </c>
       <c r="DO53" t="n">
         <v>13</v>
@@ -25922,7 +25914,7 @@
         <v>1</v>
       </c>
       <c r="DT53" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU53" t="b">
         <v>0</v>
@@ -25931,14 +25923,14 @@
         <v>1</v>
       </c>
       <c r="DW53" t="n">
-        <v>17.9</v>
+        <v>14.97</v>
       </c>
       <c r="DX53" t="n">
-        <v>5.53</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DY53" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="DZ53" t="inlineStr">
@@ -25948,27 +25940,27 @@
       </c>
       <c r="EA53" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>2.81</t>
         </is>
       </c>
       <c r="EB53" t="inlineStr">
         <is>
-          <t>4.44</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="EC53" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="ED53" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EE53" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.90</t>
         </is>
       </c>
       <c r="EF53" t="inlineStr"/>
@@ -25977,22 +25969,30 @@
       <c r="EI53" t="inlineStr"/>
       <c r="EJ53" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EK53" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="EL53" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EM53" t="inlineStr"/>
-      <c r="EN53" t="inlineStr"/>
-      <c r="EO53" t="inlineStr"/>
+      <c r="EN53" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EO53" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
       <c r="EP53" t="inlineStr"/>
     </row>
     <row r="54">
@@ -29791,43 +29791,43 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
         <v>45928.52083333334</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J62" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" t="n">
         <v>3</v>
       </c>
-      <c r="K62" t="n">
-        <v>4</v>
-      </c>
       <c r="L62" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N62" t="n">
         <v>2</v>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
         <v>0</v>
@@ -29836,34 +29836,42 @@
         <v>5</v>
       </c>
       <c r="R62" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T62" t="n">
         <v>6</v>
       </c>
       <c r="U62" t="n">
+        <v>14</v>
+      </c>
+      <c r="V62" t="n">
+        <v>10</v>
+      </c>
+      <c r="W62" t="n">
+        <v>14</v>
+      </c>
+      <c r="X62" t="n">
         <v>12</v>
       </c>
-      <c r="V62" t="n">
-        <v>11</v>
-      </c>
-      <c r="W62" t="n">
-        <v>16</v>
-      </c>
-      <c r="X62" t="n">
-        <v>6</v>
-      </c>
       <c r="Y62" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z62" t="n">
         <v>48</v>
       </c>
-      <c r="Z62" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA62" t="inlineStr"/>
-      <c r="AB62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>Stadion Galgenwaard</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>Herculesplein 241, Utrecht</t>
+        </is>
+      </c>
       <c r="AC62" t="n">
         <v>2</v>
       </c>
@@ -29871,82 +29879,82 @@
         <v>2</v>
       </c>
       <c r="AE62" t="n">
-        <v>3.65</v>
+        <v>1.9</v>
       </c>
       <c r="AF62" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AG62" t="n">
-        <v>1.91</v>
+        <v>3.7</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AI62" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AJ62" t="n">
-        <v>2.6</v>
+        <v>2.77</v>
       </c>
       <c r="AK62" t="n">
         <v>1.66</v>
       </c>
       <c r="AL62" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AM62" t="n">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="AN62" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR62" t="n">
         <v>2.35</v>
       </c>
-      <c r="AO62" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AP62" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AQ62" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AR62" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AS62" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AU62" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY62" t="n">
         <v>1</v>
       </c>
       <c r="AZ62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB62" t="n">
-        <v>367</v>
+        <v>-1</v>
       </c>
       <c r="BC62" t="n">
         <v>0</v>
       </c>
       <c r="BD62" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="BE62" t="n">
         <v>0</v>
@@ -29964,61 +29972,61 @@
         <v>1</v>
       </c>
       <c r="BJ62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BL62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN62" t="n">
         <v>4</v>
       </c>
       <c r="BO62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP62" t="n">
         <v>0</v>
       </c>
       <c r="BQ62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR62" t="n">
         <v>2</v>
       </c>
       <c r="BS62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU62" t="n">
         <v>1</v>
       </c>
       <c r="BV62" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="BW62" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BX62" t="n">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="BY62" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="BZ62" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="CA62" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="CB62" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="CC62" t="n">
         <v>0</v>
@@ -30054,7 +30062,7 @@
         <v>0</v>
       </c>
       <c r="CN62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO62" t="n">
         <v>0</v>
@@ -30066,73 +30074,73 @@
         <v>1</v>
       </c>
       <c r="CR62" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="CS62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CT62" t="n">
         <v>1</v>
       </c>
       <c r="CU62" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="CV62" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="CW62" t="n">
         <v>1</v>
       </c>
       <c r="CX62" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY62" t="n">
         <v>9</v>
       </c>
-      <c r="CY62" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ62" t="n">
+        <v>59</v>
+      </c>
+      <c r="DA62" t="n">
+        <v>59</v>
+      </c>
+      <c r="DB62" t="n">
+        <v>42</v>
+      </c>
+      <c r="DC62" t="n">
         <v>84</v>
       </c>
-      <c r="DA62" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB62" t="n">
-        <v>67</v>
-      </c>
-      <c r="DC62" t="n">
-        <v>100</v>
-      </c>
       <c r="DD62" t="n">
-        <v>1.57</v>
+        <v>2.29</v>
       </c>
       <c r="DE62" t="n">
-        <v>2.17</v>
+        <v>0.71</v>
       </c>
       <c r="DF62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DG62" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="DH62" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DI62" t="n">
-        <v>2.67</v>
+        <v>0.83</v>
       </c>
       <c r="DJ62" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="DK62" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="DL62" t="n">
-        <v>1.52</v>
+        <v>1.69</v>
       </c>
       <c r="DM62" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="DN62" t="n">
-        <v>3.72</v>
+        <v>3.09</v>
       </c>
       <c r="DO62" t="n">
         <v>13</v>
@@ -30141,13 +30149,13 @@
         <v>1</v>
       </c>
       <c r="DQ62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS62" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT62" t="b">
         <v>0</v>
@@ -30156,74 +30164,102 @@
         <v>0</v>
       </c>
       <c r="DV62" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW62" t="inlineStr"/>
-      <c r="DX62" t="inlineStr"/>
-      <c r="DY62" t="inlineStr"/>
-      <c r="DZ62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="DW62" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="DX62" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="DY62" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ62" t="inlineStr">
+        <is>
+          <t>7%</t>
+        </is>
+      </c>
       <c r="EA62" t="inlineStr">
         <is>
+          <t>4.29</t>
+        </is>
+      </c>
+      <c r="EB62" t="inlineStr">
+        <is>
+          <t>3.97</t>
+        </is>
+      </c>
+      <c r="EC62" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="ED62" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="EE62" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EF62" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG62" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EH62" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EI62" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
+      <c r="EJ62" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EK62" t="inlineStr">
+        <is>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EL62" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EM62" t="inlineStr">
+        <is>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EN62" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EO62" t="inlineStr">
+        <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="EB62" t="inlineStr">
-        <is>
-          <t>3.44</t>
-        </is>
-      </c>
-      <c r="EC62" t="inlineStr">
-        <is>
-          <t>4.22</t>
-        </is>
-      </c>
-      <c r="ED62" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="EE62" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EF62" t="inlineStr"/>
-      <c r="EG62" t="inlineStr"/>
-      <c r="EH62" t="inlineStr"/>
-      <c r="EI62" t="inlineStr"/>
-      <c r="EJ62" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="EK62" t="inlineStr">
-        <is>
-          <t>3.14</t>
-        </is>
-      </c>
-      <c r="EL62" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="EM62" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
-      <c r="EN62" t="inlineStr">
-        <is>
-          <t>2.11</t>
-        </is>
-      </c>
-      <c r="EO62" t="inlineStr">
-        <is>
-          <t>1.71</t>
-        </is>
-      </c>
       <c r="EP62" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.47</t>
         </is>
       </c>
     </row>
@@ -30243,43 +30279,43 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>45928.52083333334</v>
       </c>
       <c r="G63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3</v>
+      </c>
+      <c r="K63" t="n">
         <v>4</v>
       </c>
-      <c r="J63" t="n">
-        <v>5</v>
-      </c>
-      <c r="K63" t="n">
-        <v>3</v>
-      </c>
       <c r="L63" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N63" t="n">
         <v>2</v>
       </c>
       <c r="O63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P63" t="n">
         <v>0</v>
@@ -30288,42 +30324,34 @@
         <v>5</v>
       </c>
       <c r="R63" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T63" t="n">
         <v>6</v>
       </c>
       <c r="U63" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="V63" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W63" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="X63" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Y63" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z63" t="n">
         <v>52</v>
       </c>
-      <c r="Z63" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA63" t="inlineStr">
-        <is>
-          <t>Stadion Galgenwaard</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>Herculesplein 241, Utrecht</t>
-        </is>
-      </c>
+      <c r="AA63" t="inlineStr"/>
+      <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="n">
         <v>2</v>
       </c>
@@ -30331,82 +30359,82 @@
         <v>2</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.9</v>
+        <v>3.65</v>
       </c>
       <c r="AF63" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="AG63" t="n">
-        <v>3.7</v>
+        <v>1.91</v>
       </c>
       <c r="AH63" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AI63" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AJ63" t="n">
-        <v>2.77</v>
+        <v>2.6</v>
       </c>
       <c r="AK63" t="n">
         <v>1.66</v>
       </c>
       <c r="AL63" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AM63" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AN63" t="n">
-        <v>1.91</v>
+        <v>2.35</v>
       </c>
       <c r="AO63" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR63" t="n">
         <v>2.62</v>
       </c>
-      <c r="AP63" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AS63" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AU63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY63" t="n">
         <v>1</v>
       </c>
       <c r="AZ63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA63" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB63" t="n">
-        <v>-1</v>
+        <v>367</v>
       </c>
       <c r="BC63" t="n">
         <v>0</v>
       </c>
       <c r="BD63" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BE63" t="n">
         <v>0</v>
@@ -30424,175 +30452,175 @@
         <v>1</v>
       </c>
       <c r="BJ63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL63" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM63" t="n">
         <v>3</v>
-      </c>
-      <c r="BK63" t="n">
-        <v>4</v>
-      </c>
-      <c r="BL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM63" t="n">
-        <v>4</v>
       </c>
       <c r="BN63" t="n">
         <v>4</v>
       </c>
       <c r="BO63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP63" t="n">
         <v>0</v>
       </c>
       <c r="BQ63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR63" t="n">
         <v>2</v>
       </c>
       <c r="BS63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT63" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>29</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY63" t="n">
+        <v>99</v>
+      </c>
+      <c r="BZ63" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CA63" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CB63" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CC63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP63" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR63" t="n">
+        <v>22</v>
+      </c>
+      <c r="CS63" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU63" t="n">
+        <v>6</v>
+      </c>
+      <c r="CV63" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW63" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX63" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY63" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ63" t="n">
+        <v>84</v>
+      </c>
+      <c r="DA63" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB63" t="n">
+        <v>67</v>
+      </c>
+      <c r="DC63" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD63" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE63" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF63" t="n">
         <v>3</v>
       </c>
-      <c r="BU63" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV63" t="n">
-        <v>42</v>
-      </c>
-      <c r="BW63" t="n">
-        <v>36</v>
-      </c>
-      <c r="BX63" t="n">
-        <v>88</v>
-      </c>
-      <c r="BY63" t="n">
-        <v>95</v>
-      </c>
-      <c r="BZ63" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CA63" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CB63" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="CC63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP63" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>13</v>
-      </c>
-      <c r="CS63" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU63" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV63" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW63" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX63" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY63" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ63" t="n">
-        <v>59</v>
-      </c>
-      <c r="DA63" t="n">
-        <v>59</v>
-      </c>
-      <c r="DB63" t="n">
-        <v>42</v>
-      </c>
-      <c r="DC63" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD63" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="DE63" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="DF63" t="n">
-        <v>2</v>
-      </c>
       <c r="DG63" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="DH63" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DI63" t="n">
-        <v>0.83</v>
+        <v>2.67</v>
       </c>
       <c r="DJ63" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="DK63" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="DL63" t="n">
-        <v>1.69</v>
+        <v>1.52</v>
       </c>
       <c r="DM63" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="DN63" t="n">
-        <v>3.09</v>
+        <v>3.72</v>
       </c>
       <c r="DO63" t="n">
         <v>13</v>
@@ -30601,13 +30629,13 @@
         <v>1</v>
       </c>
       <c r="DQ63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS63" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT63" t="b">
         <v>0</v>
@@ -30616,102 +30644,74 @@
         <v>0</v>
       </c>
       <c r="DV63" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW63" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="DX63" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="DY63" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="DZ63" t="inlineStr">
-        <is>
-          <t>7%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DW63" t="inlineStr"/>
+      <c r="DX63" t="inlineStr"/>
+      <c r="DY63" t="inlineStr"/>
+      <c r="DZ63" t="inlineStr"/>
       <c r="EA63" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EB63" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="EC63" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>4.22</t>
         </is>
       </c>
       <c r="ED63" t="inlineStr">
         <is>
+          <t>1.76</t>
+        </is>
+      </c>
+      <c r="EE63" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EF63" t="inlineStr"/>
+      <c r="EG63" t="inlineStr"/>
+      <c r="EH63" t="inlineStr"/>
+      <c r="EI63" t="inlineStr"/>
+      <c r="EJ63" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EK63" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EL63" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="EM63" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="EN63" t="inlineStr">
+        <is>
+          <t>2.11</t>
+        </is>
+      </c>
+      <c r="EO63" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EP63" t="inlineStr">
+        <is>
           <t>1.68</t>
-        </is>
-      </c>
-      <c r="EE63" t="inlineStr">
-        <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="EF63" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
-      <c r="EG63" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="EH63" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EI63" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
-      <c r="EJ63" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
-      </c>
-      <c r="EK63" t="inlineStr">
-        <is>
-          <t>2.78</t>
-        </is>
-      </c>
-      <c r="EL63" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EM63" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EN63" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EO63" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
-      <c r="EP63" t="inlineStr">
-        <is>
-          <t>1.47</t>
         </is>
       </c>
     </row>
@@ -32930,7 +32930,7 @@
         <v>84</v>
       </c>
       <c r="DD68" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="DE68" t="n">
         <v>3</v>
@@ -35443,40 +35443,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
         <v>45948.60416666666</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K74" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L74" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -35485,10 +35485,10 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -35497,108 +35497,108 @@
         <v>7</v>
       </c>
       <c r="U74" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="V74" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="W74" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="X74" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Y74" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="Z74" t="n">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE74" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AF74" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW74" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY74" t="n">
         <v>3</v>
       </c>
-      <c r="AE74" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF74" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AG74" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AH74" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI74" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AJ74" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AK74" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL74" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM74" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN74" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO74" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AP74" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ74" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR74" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS74" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT74" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AU74" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW74" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX74" t="n">
-        <v>2</v>
-      </c>
-      <c r="AY74" t="n">
-        <v>2</v>
-      </c>
       <c r="AZ74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BA74" t="n">
         <v>4</v>
       </c>
-      <c r="BA74" t="n">
-        <v>2</v>
-      </c>
       <c r="BB74" t="n">
-        <v>-1</v>
+        <v>367</v>
       </c>
       <c r="BC74" t="n">
         <v>0</v>
       </c>
       <c r="BD74" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="BE74" t="n">
         <v>0</v>
@@ -35616,73 +35616,73 @@
         <v>1</v>
       </c>
       <c r="BJ74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BM74" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN74" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS74" t="n">
         <v>3</v>
       </c>
-      <c r="BN74" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO74" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP74" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ74" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR74" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS74" t="n">
-        <v>1</v>
-      </c>
       <c r="BT74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BU74" t="n">
         <v>1</v>
       </c>
       <c r="BV74" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="BW74" t="n">
-        <v>31</v>
+        <v>64</v>
       </c>
       <c r="BX74" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="BY74" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="BZ74" t="n">
-        <v>1.08</v>
+        <v>0.43</v>
       </c>
       <c r="CA74" t="n">
-        <v>1.07</v>
+        <v>2.5</v>
       </c>
       <c r="CB74" t="n">
-        <v>2.15</v>
+        <v>2.93</v>
       </c>
       <c r="CC74" t="n">
         <v>0</v>
       </c>
       <c r="CD74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CE74" t="n">
         <v>0</v>
       </c>
       <c r="CF74" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CG74" t="n">
         <v>0</v>
@@ -35700,7 +35700,7 @@
         <v>0</v>
       </c>
       <c r="CL74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM74" t="n">
         <v>0</v>
@@ -35709,7 +35709,7 @@
         <v>0</v>
       </c>
       <c r="CO74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP74" t="n">
         <v>0</v>
@@ -35718,73 +35718,73 @@
         <v>1</v>
       </c>
       <c r="CR74" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CS74" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="CT74" t="n">
         <v>1</v>
       </c>
       <c r="CU74" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CV74" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="CW74" t="n">
         <v>1</v>
       </c>
       <c r="CX74" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="CY74" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CZ74" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="DA74" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="DB74" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="DC74" t="n">
         <v>88</v>
       </c>
       <c r="DD74" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE74" t="n">
         <v>2.17</v>
       </c>
-      <c r="DE74" t="n">
-        <v>1.29</v>
-      </c>
       <c r="DF74" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="DG74" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="DH74" t="n">
-        <v>1.63</v>
+        <v>0.38</v>
       </c>
       <c r="DI74" t="n">
-        <v>1.63</v>
+        <v>2.75</v>
       </c>
       <c r="DJ74" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="DK74" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="DL74" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DM74" t="n">
         <v>1.96</v>
       </c>
-      <c r="DM74" t="n">
-        <v>2.08</v>
-      </c>
       <c r="DN74" t="n">
-        <v>4.04</v>
+        <v>3.6</v>
       </c>
       <c r="DO74" t="n">
         <v>13</v>
@@ -35808,54 +35808,74 @@
         <v>1</v>
       </c>
       <c r="DV74" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW74" t="inlineStr"/>
-      <c r="DX74" t="inlineStr"/>
-      <c r="DY74" t="inlineStr"/>
-      <c r="DZ74" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="DW74" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="DX74" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="DY74" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="DZ74" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="EA74" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EB74" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="EC74" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="ED74" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EE74" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EF74" t="inlineStr"/>
-      <c r="EG74" t="inlineStr"/>
-      <c r="EH74" t="inlineStr"/>
+      <c r="EG74" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EH74" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
       <c r="EI74" t="inlineStr"/>
       <c r="EJ74" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EK74" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EL74" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="EM74" t="inlineStr"/>
@@ -35879,40 +35899,40 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
         <v>45948.60416666666</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K75" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L75" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -35921,10 +35941,10 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S75" t="n">
         <v>4</v>
@@ -35933,108 +35953,108 @@
         <v>7</v>
       </c>
       <c r="U75" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V75" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="W75" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X75" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Y75" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="Z75" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE75" t="n">
-        <v>7.25</v>
+        <v>2.37</v>
       </c>
       <c r="AF75" t="n">
-        <v>5.1</v>
+        <v>3.74</v>
       </c>
       <c r="AG75" t="n">
-        <v>1.35</v>
+        <v>2.71</v>
       </c>
       <c r="AH75" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AI75" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM75" t="n">
         <v>1.41</v>
       </c>
-      <c r="AJ75" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AK75" t="n">
+      <c r="AN75" t="n">
         <v>1.7</v>
       </c>
-      <c r="AL75" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AM75" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN75" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AO75" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="AP75" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AR75" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AS75" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AT75" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AU75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ75" t="n">
         <v>4</v>
       </c>
-      <c r="AX75" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY75" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ75" t="n">
-        <v>3</v>
-      </c>
       <c r="BA75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB75" t="n">
-        <v>367</v>
+        <v>-1</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
       </c>
       <c r="BD75" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="BE75" t="n">
         <v>0</v>
@@ -36052,73 +36072,73 @@
         <v>1</v>
       </c>
       <c r="BJ75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM75" t="n">
         <v>3</v>
       </c>
-      <c r="BK75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL75" t="n">
-        <v>5</v>
-      </c>
-      <c r="BM75" t="n">
+      <c r="BN75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT75" t="n">
         <v>4</v>
       </c>
-      <c r="BN75" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP75" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS75" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT75" t="n">
-        <v>0</v>
-      </c>
       <c r="BU75" t="n">
         <v>1</v>
       </c>
       <c r="BV75" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BW75" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="BX75" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="BY75" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="BZ75" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="CA75" t="n">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="CB75" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="CC75" t="n">
         <v>0</v>
       </c>
       <c r="CD75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE75" t="n">
         <v>0</v>
       </c>
       <c r="CF75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG75" t="n">
         <v>0</v>
@@ -36136,7 +36156,7 @@
         <v>0</v>
       </c>
       <c r="CL75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM75" t="n">
         <v>0</v>
@@ -36145,7 +36165,7 @@
         <v>0</v>
       </c>
       <c r="CO75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP75" t="n">
         <v>0</v>
@@ -36154,73 +36174,73 @@
         <v>1</v>
       </c>
       <c r="CR75" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CS75" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU75" t="n">
         <v>21</v>
       </c>
-      <c r="CT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU75" t="n">
+      <c r="CV75" t="n">
         <v>13</v>
       </c>
-      <c r="CV75" t="n">
-        <v>11</v>
-      </c>
       <c r="CW75" t="n">
         <v>1</v>
       </c>
       <c r="CX75" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CY75" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ75" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="DA75" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="DB75" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="DC75" t="n">
         <v>88</v>
       </c>
       <c r="DD75" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DE75" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF75" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG75" t="n">
         <v>1.5</v>
       </c>
-      <c r="DE75" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="DF75" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG75" t="n">
-        <v>2.5</v>
-      </c>
       <c r="DH75" t="n">
-        <v>0.38</v>
+        <v>1.63</v>
       </c>
       <c r="DI75" t="n">
-        <v>2.75</v>
+        <v>1.63</v>
       </c>
       <c r="DJ75" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="DK75" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="DL75" t="n">
-        <v>1.64</v>
+        <v>1.96</v>
       </c>
       <c r="DM75" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="DN75" t="n">
-        <v>3.6</v>
+        <v>4.04</v>
       </c>
       <c r="DO75" t="n">
         <v>13</v>
@@ -36244,74 +36264,54 @@
         <v>1</v>
       </c>
       <c r="DV75" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW75" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="DX75" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="DY75" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="DZ75" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW75" t="inlineStr"/>
+      <c r="DX75" t="inlineStr"/>
+      <c r="DY75" t="inlineStr"/>
+      <c r="DZ75" t="inlineStr"/>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EE75" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EF75" t="inlineStr"/>
-      <c r="EG75" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EH75" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
+      <c r="EG75" t="inlineStr"/>
+      <c r="EH75" t="inlineStr"/>
       <c r="EI75" t="inlineStr"/>
       <c r="EJ75" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EK75" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EL75" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EM75" t="inlineStr"/>
@@ -36335,170 +36335,170 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45948.69791666666</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
       </c>
       <c r="I76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>10</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>6</v>
+      </c>
+      <c r="R76" t="n">
         <v>3</v>
-      </c>
-      <c r="J76" t="n">
-        <v>6</v>
-      </c>
-      <c r="K76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" t="n">
-        <v>7</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>8</v>
-      </c>
-      <c r="R76" t="n">
-        <v>2</v>
       </c>
       <c r="S76" t="n">
         <v>16</v>
       </c>
       <c r="T76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V76" t="n">
+        <v>3</v>
+      </c>
+      <c r="W76" t="n">
+        <v>12</v>
+      </c>
+      <c r="X76" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Stadion Galgenwaard</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Herculesplein 241, Utrecht</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AU76" t="n">
         <v>4</v>
       </c>
-      <c r="W76" t="n">
-        <v>7</v>
-      </c>
-      <c r="X76" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>43</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Philips Stadion</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Frederiklaan 10, Eindhoven</t>
-        </is>
-      </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL76" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN76" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ76" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AR76" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS76" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT76" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AU76" t="n">
+      <c r="AV76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX76" t="n">
         <v>3</v>
       </c>
-      <c r="AV76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX76" t="n">
-        <v>1</v>
-      </c>
       <c r="AY76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA76" t="n">
         <v>1</v>
       </c>
       <c r="BB76" t="n">
-        <v>121</v>
+        <v>376</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36513,7 +36513,7 @@
         <v>1</v>
       </c>
       <c r="BI76" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BJ76" t="n">
         <v>0</v>
@@ -36522,14 +36522,14 @@
         <v>3</v>
       </c>
       <c r="BL76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM76" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN76" t="n">
         <v>3</v>
       </c>
-      <c r="BN76" t="n">
-        <v>4</v>
-      </c>
       <c r="BO76" t="n">
         <v>0</v>
       </c>
@@ -36552,25 +36552,25 @@
         <v>1</v>
       </c>
       <c r="BV76" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="BW76" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BX76" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="BY76" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="BZ76" t="n">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="CA76" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="CB76" t="n">
-        <v>3.02</v>
+        <v>2.79</v>
       </c>
       <c r="CC76" t="n">
         <v>0</v>
@@ -36618,73 +36618,73 @@
         <v>1</v>
       </c>
       <c r="CR76" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS76" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="CT76" t="n">
         <v>1</v>
       </c>
       <c r="CU76" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CV76" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CW76" t="n">
         <v>1</v>
       </c>
       <c r="CX76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CY76" t="n">
         <v>10</v>
       </c>
       <c r="CZ76" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA76" t="n">
         <v>75</v>
       </c>
-      <c r="DA76" t="n">
-        <v>100</v>
-      </c>
       <c r="DB76" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DC76" t="n">
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
       </c>
       <c r="DG76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH76" t="n">
         <v>1.25</v>
       </c>
-      <c r="DH76" t="n">
-        <v>2.38</v>
-      </c>
       <c r="DI76" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="DJ76" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK76" t="n">
         <v>25</v>
       </c>
-      <c r="DK76" t="n">
-        <v>0</v>
-      </c>
       <c r="DL76" t="n">
-        <v>2.39</v>
+        <v>1.65</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.54</v>
+        <v>1.16</v>
       </c>
       <c r="DN76" t="n">
-        <v>3.93</v>
+        <v>2.81</v>
       </c>
       <c r="DO76" t="n">
         <v>13</v>
@@ -36699,7 +36699,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -36711,14 +36711,14 @@
         <v>1</v>
       </c>
       <c r="DW76" t="n">
-        <v>13.13</v>
+        <v>12.46</v>
       </c>
       <c r="DX76" t="n">
-        <v>3.69</v>
+        <v>3.16</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
@@ -36728,27 +36728,27 @@
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr"/>
@@ -36757,15 +36757,19 @@
       <c r="EI76" t="inlineStr"/>
       <c r="EJ76" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EK76" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EL76" t="inlineStr"/>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
       <c r="EM76" t="inlineStr"/>
       <c r="EN76" t="inlineStr"/>
       <c r="EO76" t="inlineStr"/>
@@ -36787,34 +36791,34 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
         <v>45948.69791666666</v>
       </c>
       <c r="G77" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
         <v>3</v>
       </c>
-      <c r="H77" t="n">
-        <v>1</v>
-      </c>
-      <c r="I77" t="n">
-        <v>4</v>
-      </c>
       <c r="J77" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M77" t="n">
         <v>1</v>
@@ -36829,128 +36833,128 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S77" t="n">
         <v>16</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V77" t="n">
+        <v>4</v>
+      </c>
+      <c r="W77" t="n">
+        <v>7</v>
+      </c>
+      <c r="X77" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Philips Stadion</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Frederiklaan 10, Eindhoven</t>
+        </is>
+      </c>
+      <c r="AC77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AU77" t="n">
         <v>3</v>
       </c>
-      <c r="W77" t="n">
-        <v>12</v>
-      </c>
-      <c r="X77" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Stadion Galgenwaard</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>Herculesplein 241, Utrecht</t>
-        </is>
-      </c>
-      <c r="AC77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AG77" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AK77" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL77" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM77" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN77" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO77" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AP77" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ77" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR77" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS77" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AT77" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AU77" t="n">
-        <v>4</v>
-      </c>
       <c r="AV77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA77" t="n">
         <v>1</v>
       </c>
       <c r="BB77" t="n">
-        <v>376</v>
+        <v>121</v>
       </c>
       <c r="BC77" t="n">
         <v>0</v>
       </c>
       <c r="BD77" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BE77" t="n">
         <v>0</v>
@@ -36965,7 +36969,7 @@
         <v>1</v>
       </c>
       <c r="BI77" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BJ77" t="n">
         <v>0</v>
@@ -36974,169 +36978,169 @@
         <v>3</v>
       </c>
       <c r="BL77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV77" t="n">
         <v>7</v>
       </c>
-      <c r="BN77" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ77" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR77" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT77" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU77" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV77" t="n">
-        <v>56</v>
-      </c>
-      <c r="BW77" t="n">
-        <v>22</v>
-      </c>
-      <c r="BX77" t="n">
-        <v>133</v>
-      </c>
-      <c r="BY77" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ77" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CA77" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="CB77" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR77" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS77" t="n">
-        <v>12</v>
-      </c>
-      <c r="CT77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU77" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV77" t="n">
-        <v>12</v>
-      </c>
       <c r="CW77" t="n">
         <v>1</v>
       </c>
       <c r="CX77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CY77" t="n">
         <v>10</v>
       </c>
       <c r="CZ77" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="DA77" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB77" t="n">
         <v>75</v>
-      </c>
-      <c r="DB77" t="n">
-        <v>50</v>
       </c>
       <c r="DC77" t="n">
         <v>88</v>
       </c>
       <c r="DD77" t="n">
-        <v>2.29</v>
+        <v>2.17</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.33</v>
+        <v>0.71</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
       </c>
       <c r="DG77" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="DH77" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DI77" t="n">
         <v>1.25</v>
       </c>
-      <c r="DI77" t="n">
-        <v>0.88</v>
-      </c>
       <c r="DJ77" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="DK77" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL77" t="n">
-        <v>1.65</v>
+        <v>2.39</v>
       </c>
       <c r="DM77" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="DN77" t="n">
-        <v>2.81</v>
+        <v>3.93</v>
       </c>
       <c r="DO77" t="n">
         <v>13</v>
@@ -37151,7 +37155,7 @@
         <v>1</v>
       </c>
       <c r="DS77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT77" t="b">
         <v>0</v>
@@ -37163,14 +37167,14 @@
         <v>1</v>
       </c>
       <c r="DW77" t="n">
-        <v>12.46</v>
+        <v>13.13</v>
       </c>
       <c r="DX77" t="n">
-        <v>3.16</v>
+        <v>3.69</v>
       </c>
       <c r="DY77" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ77" t="inlineStr">
@@ -37180,27 +37184,27 @@
       </c>
       <c r="EA77" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="EB77" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="EC77" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="ED77" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE77" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EF77" t="inlineStr"/>
@@ -37209,19 +37213,15 @@
       <c r="EI77" t="inlineStr"/>
       <c r="EJ77" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="EK77" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EL77" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EL77" t="inlineStr"/>
       <c r="EM77" t="inlineStr"/>
       <c r="EN77" t="inlineStr"/>
       <c r="EO77" t="inlineStr"/>
@@ -38525,7 +38525,7 @@
         <v>0.86</v>
       </c>
       <c r="DE80" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF80" t="n">
         <v>1</v>
@@ -41822,7 +41822,7 @@
         <v>88</v>
       </c>
       <c r="DD87" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="DE87" t="n">
         <v>1.14</v>
@@ -44653,7 +44653,7 @@
         <v>1.86</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF93" t="n">
         <v>2.4</v>
@@ -49809,7 +49809,7 @@
         <v>2.17</v>
       </c>
       <c r="DE104" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DF104" t="n">
         <v>2</v>
@@ -50270,7 +50270,7 @@
         <v>80</v>
       </c>
       <c r="DD105" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="DE105" t="n">
         <v>1.5</v>
@@ -56504,6 +56504,486 @@
       <c r="EP118" t="inlineStr">
         <is>
           <t>1.57</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Netherlands_Eredivisie_2025-2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>14</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PEC Zwolle</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>45989.79166666666</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2</v>
+      </c>
+      <c r="H119" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" t="n">
+        <v>3</v>
+      </c>
+      <c r="J119" t="n">
+        <v>3</v>
+      </c>
+      <c r="K119" t="n">
+        <v>9</v>
+      </c>
+      <c r="L119" t="n">
+        <v>12</v>
+      </c>
+      <c r="M119" t="n">
+        <v>3</v>
+      </c>
+      <c r="N119" t="n">
+        <v>2</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>4</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7</v>
+      </c>
+      <c r="S119" t="n">
+        <v>7</v>
+      </c>
+      <c r="T119" t="n">
+        <v>12</v>
+      </c>
+      <c r="U119" t="n">
+        <v>11</v>
+      </c>
+      <c r="V119" t="n">
+        <v>19</v>
+      </c>
+      <c r="W119" t="n">
+        <v>11</v>
+      </c>
+      <c r="X119" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>57</v>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>MAC³PARK Stadion</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>Stadionplein 1, Zwolle</t>
+        </is>
+      </c>
+      <c r="AC119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>380</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>31</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>56</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>98</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>97</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>16</v>
+      </c>
+      <c r="CT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU119" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV119" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX119" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY119" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ119" t="n">
+        <v>42</v>
+      </c>
+      <c r="DA119" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB119" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC119" t="n">
+        <v>83</v>
+      </c>
+      <c r="DD119" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DE119" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DF119" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DG119" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DH119" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI119" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DJ119" t="n">
+        <v>59</v>
+      </c>
+      <c r="DK119" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL119" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="DM119" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="DN119" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DO119" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DS119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW119" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="DX119" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="DY119" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="DZ119" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA119" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="EB119" t="inlineStr">
+        <is>
+          <t>3.92</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="ED119" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="EF119" t="inlineStr"/>
+      <c r="EG119" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="EH119" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EI119" t="inlineStr"/>
+      <c r="EJ119" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EK119" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="EL119" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EM119" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EN119" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EO119" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EP119" t="inlineStr">
+        <is>
+          <t>1.49</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP126" headerRowCount="1">
-  <autoFilter ref="A1:EP126"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP127" headerRowCount="1">
+  <autoFilter ref="A1:EP127"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP126"/>
+  <dimension ref="A1:EP127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -4677,7 +4677,7 @@
         <v>1.83</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -4707,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -5146,7 +5146,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE9" t="n">
         <v>0.67</v>
@@ -5179,7 +5179,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -7551,7 +7551,7 @@
         <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP14" t="b">
         <v>1</v>
@@ -8039,7 +8039,7 @@
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP15" t="b">
         <v>1</v>
@@ -8167,164 +8167,164 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>45886.52083333334</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
       </c>
       <c r="L16" t="n">
+        <v>14</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="n">
         <v>11</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>5</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
+        <v>19</v>
+      </c>
+      <c r="V16" t="n">
+        <v>15</v>
+      </c>
+      <c r="W16" t="n">
         <v>10</v>
       </c>
-      <c r="T16" t="n">
-        <v>15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>15</v>
-      </c>
-      <c r="V16" t="n">
-        <v>20</v>
-      </c>
-      <c r="W16" t="n">
-        <v>9</v>
-      </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Sparta-Stadion Het Kasteel</t>
+          <t>De Grolsch Veste</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Spartapark Noord 1, Rotterdam</t>
+          <t>Colosseum 65, Enschede</t>
         </is>
       </c>
       <c r="AC16" t="n">
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.39</v>
+        <v>5.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.55</v>
+        <v>4.45</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.15</v>
+        <v>2.61</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AO16" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AS16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AU16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA16" t="n">
         <v>1</v>
       </c>
       <c r="BB16" t="n">
-        <v>371</v>
+        <v>121</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
@@ -8345,73 +8345,73 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL16" t="n">
         <v>3</v>
       </c>
-      <c r="BL16" t="n">
-        <v>4</v>
-      </c>
       <c r="BM16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BN16" t="n">
         <v>7</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="BW16" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="BX16" t="n">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="BY16" t="n">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.99</v>
+        <v>1.53</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF16" t="n">
         <v>0</v>
@@ -8432,13 +8432,13 @@
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CS16" t="n">
         <v>24</v>
@@ -8459,19 +8459,19 @@
         <v>1</v>
       </c>
       <c r="CU16" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV16" t="n">
         <v>10</v>
       </c>
-      <c r="CV16" t="n">
-        <v>9</v>
-      </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CY16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ16" t="n">
         <v>0</v>
@@ -8486,10 +8486,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.71</v>
+        <v>3</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8528,7 +8528,7 @@
         <v>1</v>
       </c>
       <c r="DR16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS16" t="b">
         <v>0</v>
@@ -8540,17 +8540,17 @@
         <v>0</v>
       </c>
       <c r="DV16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="inlineStr"/>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
@@ -8560,73 +8560,65 @@
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="EF16" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr"/>
       <c r="EG16" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EH16" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI16" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI16" t="inlineStr"/>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EM16" t="inlineStr"/>
       <c r="EN16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EO16" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EP16" t="inlineStr"/>
@@ -8647,40 +8639,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>45886.52083333334</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -8689,122 +8681,122 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
         <v>15</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V17" t="n">
+        <v>20</v>
+      </c>
+      <c r="W17" t="n">
+        <v>9</v>
+      </c>
+      <c r="X17" t="n">
         <v>11</v>
       </c>
-      <c r="U17" t="n">
-        <v>19</v>
-      </c>
-      <c r="V17" t="n">
-        <v>15</v>
-      </c>
-      <c r="W17" t="n">
-        <v>10</v>
-      </c>
-      <c r="X17" t="n">
-        <v>12</v>
-      </c>
       <c r="Y17" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>De Grolsch Veste</t>
+          <t>Sparta-Stadion Het Kasteel</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Colosseum 65, Enschede</t>
+          <t>Spartapark Noord 1, Rotterdam</t>
         </is>
       </c>
       <c r="AC17" t="n">
         <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>5.2</v>
+        <v>2.39</v>
       </c>
       <c r="AF17" t="n">
-        <v>4.45</v>
+        <v>3.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AO17" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AR17" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA17" t="n">
         <v>1</v>
       </c>
       <c r="BB17" t="n">
-        <v>121</v>
+        <v>371</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8825,73 +8817,73 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL17" t="n">
         <v>4</v>
       </c>
-      <c r="BJ17" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK17" t="n">
+      <c r="BM17" t="n">
         <v>4</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>7</v>
       </c>
       <c r="BN17" t="n">
         <v>7</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="BW17" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="BX17" t="n">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="BY17" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF17" t="n">
         <v>0</v>
@@ -8912,13 +8904,13 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8930,7 +8922,7 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CS17" t="n">
         <v>24</v>
@@ -8939,19 +8931,19 @@
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CV17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CY17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ17" t="n">
         <v>0</v>
@@ -8966,10 +8958,10 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="DE17" t="n">
-        <v>3</v>
+        <v>0.71</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9008,7 +9000,7 @@
         <v>1</v>
       </c>
       <c r="DR17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS17" t="b">
         <v>0</v>
@@ -9020,17 +9012,17 @@
         <v>0</v>
       </c>
       <c r="DV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW17" t="inlineStr"/>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
@@ -9040,65 +9032,73 @@
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="EF17" t="inlineStr"/>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EF17" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
       <c r="EG17" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EH17" t="inlineStr">
         <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EI17" t="inlineStr"/>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="EM17" t="inlineStr"/>
       <c r="EN17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EO17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EP17" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
         <v>2.29</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF21" t="n">
         <v>3</v>
@@ -10887,7 +10887,7 @@
         <v>4.44</v>
       </c>
       <c r="DO21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP21" t="b">
         <v>1</v>
@@ -13194,7 +13194,7 @@
         <v>100</v>
       </c>
       <c r="DD26" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE26" t="n">
         <v>0.5</v>
@@ -13227,7 +13227,7 @@
         <v>3.02</v>
       </c>
       <c r="DO26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP26" t="b">
         <v>1</v>
@@ -13691,7 +13691,7 @@
         <v>1.9</v>
       </c>
       <c r="DO27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP27" t="b">
         <v>1</v>
@@ -14167,7 +14167,7 @@
         <v>3.51</v>
       </c>
       <c r="DO28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP28" t="b">
         <v>1</v>
@@ -16171,12 +16171,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -16186,155 +16186,155 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
+        <v>2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" t="n">
+        <v>5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7</v>
+      </c>
+      <c r="S33" t="n">
         <v>4</v>
       </c>
-      <c r="I33" t="n">
-        <v>4</v>
-      </c>
-      <c r="J33" t="n">
-        <v>1</v>
-      </c>
-      <c r="K33" t="n">
-        <v>9</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="T33" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>14</v>
+      </c>
+      <c r="W33" t="n">
+        <v>13</v>
+      </c>
+      <c r="X33" t="n">
         <v>10</v>
       </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>11</v>
-      </c>
-      <c r="S33" t="n">
-        <v>5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>13</v>
-      </c>
-      <c r="U33" t="n">
-        <v>7</v>
-      </c>
-      <c r="V33" t="n">
-        <v>24</v>
-      </c>
-      <c r="W33" t="n">
-        <v>5</v>
-      </c>
-      <c r="X33" t="n">
-        <v>9</v>
-      </c>
       <c r="Y33" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="Z33" t="n">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Sparta-Stadion Het Kasteel</t>
+          <t>MAC³PARK Stadion</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>Spartapark Noord 1, Rotterdam</t>
+          <t>Stadionplein 1, Zwolle</t>
         </is>
       </c>
       <c r="AC33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE33" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AF33" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.76</v>
+        <v>2.19</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>2.52</v>
+        <v>2.98</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AO33" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="AP33" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AR33" t="n">
-        <v>2.3</v>
+        <v>2.51</v>
       </c>
       <c r="AS33" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AU33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV33" t="n">
         <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX33" t="n">
         <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB33" t="n">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="BC33" t="n">
         <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BE33" t="n">
         <v>0</v>
@@ -16349,37 +16349,37 @@
         <v>1</v>
       </c>
       <c r="BI33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BK33" t="n">
         <v>1</v>
       </c>
       <c r="BL33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BM33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BN33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BO33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP33" t="n">
         <v>1</v>
       </c>
       <c r="BQ33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT33" t="n">
         <v>2</v>
@@ -16388,25 +16388,25 @@
         <v>1</v>
       </c>
       <c r="BV33" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BW33" t="n">
-        <v>92</v>
+        <v>25</v>
       </c>
       <c r="BX33" t="n">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="BY33" t="n">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="BZ33" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="CA33" t="n">
-        <v>2.94</v>
+        <v>1.56</v>
       </c>
       <c r="CB33" t="n">
-        <v>3.78</v>
+        <v>2.43</v>
       </c>
       <c r="CC33" t="n">
         <v>0</v>
@@ -16439,7 +16439,7 @@
         <v>0</v>
       </c>
       <c r="CM33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN33" t="n">
         <v>0</v>
@@ -16454,7 +16454,7 @@
         <v>1</v>
       </c>
       <c r="CR33" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="CS33" t="n">
         <v>15</v>
@@ -16463,64 +16463,64 @@
         <v>1</v>
       </c>
       <c r="CU33" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV33" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW33" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX33" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY33" t="n">
         <v>9</v>
       </c>
-      <c r="CV33" t="n">
-        <v>5</v>
-      </c>
-      <c r="CW33" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX33" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY33" t="n">
-        <v>1</v>
-      </c>
       <c r="CZ33" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DA33" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="DB33" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC33" t="n">
         <v>100</v>
       </c>
       <c r="DD33" t="n">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="DE33" t="n">
-        <v>2.29</v>
+        <v>0.71</v>
       </c>
       <c r="DF33" t="n">
         <v>3</v>
       </c>
       <c r="DG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH33" t="n">
         <v>3</v>
       </c>
-      <c r="DH33" t="n">
-        <v>2</v>
-      </c>
       <c r="DI33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DJ33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DK33" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DL33" t="n">
-        <v>1.52</v>
+        <v>0.93</v>
       </c>
       <c r="DM33" t="n">
-        <v>1.9</v>
+        <v>1.99</v>
       </c>
       <c r="DN33" t="n">
-        <v>3.42</v>
+        <v>2.92</v>
       </c>
       <c r="DO33" t="n">
         <v>14</v>
@@ -16532,10 +16532,10 @@
         <v>1</v>
       </c>
       <c r="DR33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT33" t="b">
         <v>0</v>
@@ -16547,84 +16547,84 @@
         <v>0</v>
       </c>
       <c r="DW33" t="n">
-        <v>20.4</v>
+        <v>17.16</v>
       </c>
       <c r="DX33" t="n">
-        <v>6.09</v>
+        <v>6.34</v>
       </c>
       <c r="DY33" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="DZ33" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA33" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EB33" t="inlineStr">
         <is>
-          <t>3.92</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EC33" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="ED33" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EE33" t="inlineStr">
         <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EF33" t="inlineStr"/>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="EF33" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
       <c r="EG33" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="EH33" t="inlineStr">
         <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="EI33" t="inlineStr"/>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI33" t="inlineStr">
+        <is>
+          <t>3.24</t>
+        </is>
+      </c>
       <c r="EJ33" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EK33" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.99</t>
         </is>
       </c>
       <c r="EL33" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EM33" t="inlineStr"/>
-      <c r="EN33" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EO33" t="inlineStr">
-        <is>
-          <t>2.14</t>
-        </is>
-      </c>
+      <c r="EN33" t="inlineStr"/>
+      <c r="EO33" t="inlineStr"/>
       <c r="EP33" t="inlineStr"/>
     </row>
     <row r="34">
@@ -16643,12 +16643,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -16658,155 +16658,155 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>9</v>
+      </c>
+      <c r="L34" t="n">
+        <v>10</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1</v>
+      </c>
+      <c r="N34" t="n">
+        <v>2</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>2</v>
+      </c>
+      <c r="R34" t="n">
+        <v>11</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="n">
+        <v>13</v>
+      </c>
+      <c r="U34" t="n">
+        <v>7</v>
+      </c>
+      <c r="V34" t="n">
+        <v>24</v>
+      </c>
+      <c r="W34" t="n">
+        <v>5</v>
+      </c>
+      <c r="X34" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>38</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>62</v>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>Sparta-Stadion Het Kasteel</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>Spartapark Noord 1, Rotterdam</t>
+        </is>
+      </c>
+      <c r="AC34" t="n">
         <v>3</v>
       </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>5</v>
-      </c>
-      <c r="M34" t="n">
-        <v>2</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>7</v>
-      </c>
-      <c r="S34" t="n">
+      <c r="AD34" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AU34" t="n">
         <v>4</v>
       </c>
-      <c r="T34" t="n">
-        <v>7</v>
-      </c>
-      <c r="U34" t="n">
-        <v>6</v>
-      </c>
-      <c r="V34" t="n">
-        <v>14</v>
-      </c>
-      <c r="W34" t="n">
-        <v>13</v>
-      </c>
-      <c r="X34" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>MAC³PARK Stadion</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>Stadionplein 1, Zwolle</t>
-        </is>
-      </c>
-      <c r="AC34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>2</v>
-      </c>
       <c r="AV34" t="n">
         <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX34" t="n">
         <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB34" t="n">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="BC34" t="n">
         <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="BE34" t="n">
         <v>0</v>
@@ -16821,37 +16821,37 @@
         <v>1</v>
       </c>
       <c r="BI34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BK34" t="n">
         <v>1</v>
       </c>
       <c r="BL34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BM34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN34" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BO34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP34" t="n">
         <v>1</v>
       </c>
       <c r="BQ34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BR34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT34" t="n">
         <v>2</v>
@@ -16860,25 +16860,25 @@
         <v>1</v>
       </c>
       <c r="BV34" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BW34" t="n">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="BX34" t="n">
-        <v>103</v>
+        <v>65</v>
       </c>
       <c r="BY34" t="n">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="BZ34" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="CA34" t="n">
-        <v>1.56</v>
+        <v>2.94</v>
       </c>
       <c r="CB34" t="n">
-        <v>2.43</v>
+        <v>3.78</v>
       </c>
       <c r="CC34" t="n">
         <v>0</v>
@@ -16911,7 +16911,7 @@
         <v>0</v>
       </c>
       <c r="CM34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN34" t="n">
         <v>0</v>
@@ -16926,7 +16926,7 @@
         <v>1</v>
       </c>
       <c r="CR34" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="CS34" t="n">
         <v>15</v>
@@ -16935,64 +16935,64 @@
         <v>1</v>
       </c>
       <c r="CU34" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CV34" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="CW34" t="n">
         <v>1</v>
       </c>
       <c r="CX34" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CY34" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="CZ34" t="n">
+        <v>100</v>
+      </c>
+      <c r="DA34" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB34" t="n">
         <v>50</v>
-      </c>
-      <c r="DA34" t="n">
-        <v>50</v>
-      </c>
-      <c r="DB34" t="n">
-        <v>0</v>
       </c>
       <c r="DC34" t="n">
         <v>100</v>
       </c>
       <c r="DD34" t="n">
-        <v>1.43</v>
+        <v>1.14</v>
       </c>
       <c r="DE34" t="n">
-        <v>0.71</v>
+        <v>2.29</v>
       </c>
       <c r="DF34" t="n">
         <v>3</v>
       </c>
       <c r="DG34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DH34" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI34" t="n">
         <v>3</v>
       </c>
-      <c r="DI34" t="n">
-        <v>2</v>
-      </c>
       <c r="DJ34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DK34" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DL34" t="n">
-        <v>0.93</v>
+        <v>1.52</v>
       </c>
       <c r="DM34" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="DN34" t="n">
-        <v>2.92</v>
+        <v>3.42</v>
       </c>
       <c r="DO34" t="n">
         <v>14</v>
@@ -17004,10 +17004,10 @@
         <v>1</v>
       </c>
       <c r="DR34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT34" t="b">
         <v>0</v>
@@ -17019,84 +17019,84 @@
         <v>0</v>
       </c>
       <c r="DW34" t="n">
-        <v>17.16</v>
+        <v>20.4</v>
       </c>
       <c r="DX34" t="n">
-        <v>6.34</v>
+        <v>6.09</v>
       </c>
       <c r="DY34" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ34" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="EA34" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB34" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="EC34" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="ED34" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE34" t="inlineStr">
         <is>
-          <t>2.26</t>
-        </is>
-      </c>
-      <c r="EF34" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EF34" t="inlineStr"/>
       <c r="EG34" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EH34" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI34" t="inlineStr">
-        <is>
-          <t>3.24</t>
-        </is>
-      </c>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="EI34" t="inlineStr"/>
       <c r="EJ34" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK34" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EL34" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="EM34" t="inlineStr"/>
-      <c r="EN34" t="inlineStr"/>
-      <c r="EO34" t="inlineStr"/>
+      <c r="EN34" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EO34" t="inlineStr">
+        <is>
+          <t>2.14</t>
+        </is>
+      </c>
       <c r="EP34" t="inlineStr"/>
     </row>
     <row r="35">
@@ -17914,7 +17914,7 @@
         <v>100</v>
       </c>
       <c r="DD36" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE36" t="n">
         <v>0.86</v>
@@ -17947,7 +17947,7 @@
         <v>3.4</v>
       </c>
       <c r="DO36" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP36" t="b">
         <v>1</v>
@@ -18991,34 +18991,34 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>45913.79166666666</v>
       </c>
       <c r="G39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K39" t="n">
         <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M39" t="n">
         <v>2</v>
@@ -19027,134 +19027,134 @@
         <v>1</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R39" t="n">
+        <v>1</v>
+      </c>
+      <c r="S39" t="n">
         <v>4</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
+        <v>10</v>
+      </c>
+      <c r="U39" t="n">
         <v>9</v>
       </c>
-      <c r="T39" t="n">
-        <v>6</v>
-      </c>
-      <c r="U39" t="n">
-        <v>15</v>
-      </c>
       <c r="V39" t="n">
+        <v>11</v>
+      </c>
+      <c r="W39" t="n">
         <v>10</v>
       </c>
-      <c r="W39" t="n">
-        <v>15</v>
-      </c>
       <c r="X39" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Y39" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="Z39" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>De Grolsch Veste</t>
+          <t>Stadion Feijenoord</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>Colosseum 65, Enschede</t>
+          <t>Van Zandvlietplein 1, Rotterdam</t>
         </is>
       </c>
       <c r="AC39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AF39" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AG39" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="AK39" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL39" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AO39" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AP39" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AQ39" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR39" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AS39" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AT39" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AU39" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA39" t="n">
         <v>1</v>
       </c>
       <c r="BB39" t="n">
-        <v>-1</v>
+        <v>367</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE39" t="n">
         <v>0</v>
@@ -19175,7 +19175,7 @@
         <v>1</v>
       </c>
       <c r="BK39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL39" t="n">
         <v>2</v>
@@ -19184,58 +19184,58 @@
         <v>4</v>
       </c>
       <c r="BN39" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT39" t="n">
         <v>3</v>
       </c>
-      <c r="BO39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS39" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT39" t="n">
-        <v>1</v>
-      </c>
       <c r="BU39" t="n">
         <v>1</v>
       </c>
       <c r="BV39" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="BW39" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BX39" t="n">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="BY39" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="BZ39" t="n">
-        <v>1.81</v>
+        <v>1.28</v>
       </c>
       <c r="CA39" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="CB39" t="n">
-        <v>2.93</v>
+        <v>2.49</v>
       </c>
       <c r="CC39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD39" t="n">
         <v>0</v>
       </c>
       <c r="CE39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF39" t="n">
         <v>0</v>
@@ -19256,10 +19256,10 @@
         <v>0</v>
       </c>
       <c r="CL39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN39" t="n">
         <v>0</v>
@@ -19274,73 +19274,73 @@
         <v>1</v>
       </c>
       <c r="CR39" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="CS39" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="CT39" t="n">
         <v>1</v>
       </c>
       <c r="CU39" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CV39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="CW39" t="n">
         <v>1</v>
       </c>
       <c r="CX39" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CY39" t="n">
         <v>10</v>
       </c>
       <c r="CZ39" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA39" t="n">
         <v>100</v>
       </c>
       <c r="DB39" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC39" t="n">
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.29</v>
+        <v>0.71</v>
       </c>
       <c r="DF39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG39" t="n">
         <v>0</v>
       </c>
       <c r="DH39" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="DI39" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="DJ39" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK39" t="n">
         <v>0</v>
       </c>
       <c r="DL39" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="DM39" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="DN39" t="n">
-        <v>2.65</v>
+        <v>3.64</v>
       </c>
       <c r="DO39" t="n">
         <v>14</v>
@@ -19349,13 +19349,13 @@
         <v>1</v>
       </c>
       <c r="DQ39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT39" t="b">
         <v>0</v>
@@ -19364,17 +19364,17 @@
         <v>0</v>
       </c>
       <c r="DV39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW39" t="n">
-        <v>16.03</v>
+        <v>15.9</v>
       </c>
       <c r="DX39" t="n">
-        <v>7.1</v>
+        <v>7.35</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
@@ -19384,73 +19384,65 @@
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="ED39" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EE39" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EF39" t="inlineStr"/>
+      <c r="EG39" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EH39" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="EE39" t="inlineStr">
+      <c r="EI39" t="inlineStr"/>
+      <c r="EJ39" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EK39" t="inlineStr">
         <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EF39" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EG39" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="EH39" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EI39" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EJ39" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EK39" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr"/>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr"/>
@@ -19471,170 +19463,170 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>45913.79166666666</v>
       </c>
       <c r="G40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
         <v>3</v>
       </c>
       <c r="L40" t="n">
+        <v>7</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>6</v>
+      </c>
+      <c r="R40" t="n">
+        <v>4</v>
+      </c>
+      <c r="S40" t="n">
         <v>9</v>
       </c>
-      <c r="M40" t="n">
-        <v>2</v>
-      </c>
-      <c r="N40" t="n">
-        <v>1</v>
-      </c>
-      <c r="O40" t="n">
-        <v>1</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>5</v>
-      </c>
-      <c r="R40" t="n">
-        <v>1</v>
-      </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
+        <v>6</v>
+      </c>
+      <c r="U40" t="n">
+        <v>15</v>
+      </c>
+      <c r="V40" t="n">
+        <v>10</v>
+      </c>
+      <c r="W40" t="n">
+        <v>15</v>
+      </c>
+      <c r="X40" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>De Grolsch Veste</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>Colosseum 65, Enschede</t>
+        </is>
+      </c>
+      <c r="AC40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU40" t="n">
         <v>4</v>
       </c>
-      <c r="T40" t="n">
-        <v>10</v>
-      </c>
-      <c r="U40" t="n">
-        <v>9</v>
-      </c>
-      <c r="V40" t="n">
-        <v>11</v>
-      </c>
-      <c r="W40" t="n">
-        <v>10</v>
-      </c>
-      <c r="X40" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>47</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>Stadion Feijenoord</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>Van Zandvlietplein 1, Rotterdam</t>
-        </is>
-      </c>
-      <c r="AC40" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>1</v>
-      </c>
       <c r="AV40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA40" t="n">
         <v>1</v>
       </c>
       <c r="BB40" t="n">
-        <v>367</v>
+        <v>-1</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE40" t="n">
         <v>0</v>
@@ -19655,7 +19647,7 @@
         <v>1</v>
       </c>
       <c r="BK40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL40" t="n">
         <v>2</v>
@@ -19664,163 +19656,163 @@
         <v>4</v>
       </c>
       <c r="BN40" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV40" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW40" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX40" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY40" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ40" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CA40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CB40" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR40" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS40" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU40" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV40" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW40" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX40" t="n">
         <v>5</v>
-      </c>
-      <c r="BO40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ40" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS40" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT40" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV40" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW40" t="n">
-        <v>60</v>
-      </c>
-      <c r="BX40" t="n">
-        <v>76</v>
-      </c>
-      <c r="BY40" t="n">
-        <v>110</v>
-      </c>
-      <c r="BZ40" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CA40" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CB40" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="CC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS40" t="n">
-        <v>23</v>
-      </c>
-      <c r="CT40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU40" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV40" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW40" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX40" t="n">
-        <v>7</v>
       </c>
       <c r="CY40" t="n">
         <v>10</v>
       </c>
       <c r="CZ40" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DA40" t="n">
         <v>100</v>
       </c>
       <c r="DB40" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC40" t="n">
         <v>100</v>
       </c>
       <c r="DD40" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="DF40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG40" t="n">
         <v>0</v>
       </c>
       <c r="DH40" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="DI40" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="DJ40" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK40" t="n">
         <v>0</v>
       </c>
       <c r="DL40" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DM40" t="n">
-        <v>1.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DN40" t="n">
-        <v>3.64</v>
+        <v>2.65</v>
       </c>
       <c r="DO40" t="n">
         <v>14</v>
@@ -19829,13 +19821,13 @@
         <v>1</v>
       </c>
       <c r="DQ40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT40" t="b">
         <v>0</v>
@@ -19844,17 +19836,17 @@
         <v>0</v>
       </c>
       <c r="DV40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW40" t="n">
-        <v>15.9</v>
+        <v>16.03</v>
       </c>
       <c r="DX40" t="n">
-        <v>7.35</v>
+        <v>7.1</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
@@ -19864,65 +19856,73 @@
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="ED40" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EE40" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EF40" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EF40" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
       <c r="EG40" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EH40" t="inlineStr">
         <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EI40" t="inlineStr"/>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EI40" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
       <c r="EJ40" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EK40" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr"/>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr"/>
@@ -20407,141 +20407,149 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
         <v>45914.52083333334</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
         <v>3</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
+        <v>4</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" t="n">
         <v>6</v>
       </c>
-      <c r="K42" t="n">
+      <c r="S42" t="n">
+        <v>11</v>
+      </c>
+      <c r="T42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U42" t="n">
+        <v>14</v>
+      </c>
+      <c r="V42" t="n">
+        <v>13</v>
+      </c>
+      <c r="W42" t="n">
         <v>9</v>
       </c>
-      <c r="L42" t="n">
-        <v>15</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>6</v>
-      </c>
-      <c r="R42" t="n">
-        <v>8</v>
-      </c>
-      <c r="S42" t="n">
-        <v>13</v>
-      </c>
-      <c r="T42" t="n">
-        <v>17</v>
-      </c>
-      <c r="U42" t="n">
-        <v>19</v>
-      </c>
-      <c r="V42" t="n">
-        <v>25</v>
-      </c>
-      <c r="W42" t="n">
-        <v>11</v>
-      </c>
       <c r="X42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y42" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Z42" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Stadion Galgenwaard</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Herculesplein 241, Utrecht</t>
+        </is>
+      </c>
       <c r="AC42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE42" t="n">
-        <v>5.4</v>
+        <v>1.74</v>
       </c>
       <c r="AF42" t="n">
-        <v>4.58</v>
+        <v>3.8</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.44</v>
+        <v>4.75</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.3</v>
+        <v>3.27</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL42" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.7</v>
+        <v>2.83</v>
       </c>
       <c r="AO42" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.99</v>
+        <v>1.58</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AU42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
         <v>0</v>
@@ -20553,10 +20561,10 @@
         <v>1</v>
       </c>
       <c r="BA42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="BC42" t="n">
         <v>0</v>
@@ -20577,64 +20585,64 @@
         <v>1</v>
       </c>
       <c r="BI42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ42" t="n">
         <v>3</v>
       </c>
-      <c r="BJ42" t="n">
-        <v>7</v>
-      </c>
       <c r="BK42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BN42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO42" t="n">
         <v>0</v>
       </c>
       <c r="BP42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR42" t="n">
         <v>3</v>
       </c>
       <c r="BS42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU42" t="n">
         <v>1</v>
       </c>
       <c r="BV42" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="BW42" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="BX42" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="BY42" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="BZ42" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="CA42" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="CB42" t="n">
-        <v>4.45</v>
+        <v>2.82</v>
       </c>
       <c r="CC42" t="n">
         <v>0</v>
@@ -20664,13 +20672,13 @@
         <v>0</v>
       </c>
       <c r="CL42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO42" t="n">
         <v>0</v>
@@ -20682,73 +20690,73 @@
         <v>1</v>
       </c>
       <c r="CR42" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS42" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU42" t="n">
         <v>16</v>
       </c>
-      <c r="CS42" t="n">
-        <v>10</v>
-      </c>
-      <c r="CT42" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU42" t="n">
-        <v>11</v>
-      </c>
       <c r="CV42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW42" t="n">
         <v>1</v>
       </c>
       <c r="CX42" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY42" t="n">
         <v>8</v>
       </c>
-      <c r="CY42" t="n">
-        <v>12</v>
-      </c>
       <c r="CZ42" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DA42" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB42" t="n">
         <v>75</v>
       </c>
       <c r="DC42" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD42" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DE42" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF42" t="n">
+        <v>3</v>
+      </c>
+      <c r="DG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DI42" t="n">
         <v>1.5</v>
       </c>
-      <c r="DE42" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DF42" t="n">
-        <v>0</v>
-      </c>
-      <c r="DG42" t="n">
-        <v>2</v>
-      </c>
-      <c r="DH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI42" t="n">
-        <v>2.33</v>
-      </c>
       <c r="DJ42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DK42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL42" t="n">
-        <v>1.46</v>
+        <v>1.89</v>
       </c>
       <c r="DM42" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="DN42" t="n">
-        <v>3.73</v>
+        <v>3.54</v>
       </c>
       <c r="DO42" t="n">
         <v>14</v>
@@ -20757,10 +20765,10 @@
         <v>1</v>
       </c>
       <c r="DQ42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS42" t="b">
         <v>0</v>
@@ -20772,74 +20780,82 @@
         <v>0</v>
       </c>
       <c r="DV42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW42" t="n">
-        <v>17.45</v>
+        <v>16.85</v>
       </c>
       <c r="DX42" t="n">
-        <v>6.62</v>
+        <v>7.28</v>
       </c>
       <c r="DY42" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="DZ42" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="EA42" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="EB42" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="EC42" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="ED42" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EE42" t="inlineStr">
         <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EF42" t="inlineStr"/>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EF42" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EG42" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="EH42" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EI42" t="inlineStr"/>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI42" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
       <c r="EJ42" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EK42" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EL42" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EM42" t="inlineStr"/>
@@ -20863,149 +20879,141 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
         <v>45914.52083333334</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>9</v>
+      </c>
+      <c r="L43" t="n">
+        <v>15</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>6</v>
+      </c>
+      <c r="R43" t="n">
+        <v>8</v>
+      </c>
+      <c r="S43" t="n">
+        <v>13</v>
+      </c>
+      <c r="T43" t="n">
+        <v>17</v>
+      </c>
+      <c r="U43" t="n">
+        <v>19</v>
+      </c>
+      <c r="V43" t="n">
+        <v>25</v>
+      </c>
+      <c r="W43" t="n">
+        <v>11</v>
+      </c>
+      <c r="X43" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU43" t="n">
         <v>3</v>
       </c>
-      <c r="K43" t="n">
-        <v>4</v>
-      </c>
-      <c r="L43" t="n">
-        <v>7</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6</v>
-      </c>
-      <c r="S43" t="n">
-        <v>11</v>
-      </c>
-      <c r="T43" t="n">
-        <v>7</v>
-      </c>
-      <c r="U43" t="n">
-        <v>14</v>
-      </c>
-      <c r="V43" t="n">
-        <v>13</v>
-      </c>
-      <c r="W43" t="n">
-        <v>9</v>
-      </c>
-      <c r="X43" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Stadion Galgenwaard</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>Herculesplein 241, Utrecht</t>
-        </is>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1</v>
-      </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX43" t="n">
         <v>0</v>
@@ -21017,10 +21025,10 @@
         <v>1</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB43" t="n">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="BC43" t="n">
         <v>0</v>
@@ -21041,101 +21049,101 @@
         <v>1</v>
       </c>
       <c r="BI43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ43" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK43" t="n">
         <v>3</v>
       </c>
-      <c r="BK43" t="n">
-        <v>1</v>
-      </c>
       <c r="BL43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM43" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN43" t="n">
         <v>5</v>
       </c>
-      <c r="BN43" t="n">
-        <v>2</v>
-      </c>
       <c r="BO43" t="n">
         <v>0</v>
       </c>
       <c r="BP43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR43" t="n">
         <v>3</v>
       </c>
       <c r="BS43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT43" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CB43" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="CC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN43" t="n">
         <v>3</v>
       </c>
-      <c r="BU43" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV43" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW43" t="n">
-        <v>39</v>
-      </c>
-      <c r="BX43" t="n">
-        <v>92</v>
-      </c>
-      <c r="BY43" t="n">
-        <v>113</v>
-      </c>
-      <c r="BZ43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CA43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CB43" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="CC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI43" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ43" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM43" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN43" t="n">
-        <v>0</v>
-      </c>
       <c r="CO43" t="n">
         <v>0</v>
       </c>
@@ -21146,85 +21154,85 @@
         <v>1</v>
       </c>
       <c r="CR43" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="CS43" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="CT43" t="n">
         <v>1</v>
       </c>
       <c r="CU43" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CV43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CW43" t="n">
         <v>1</v>
       </c>
       <c r="CX43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CY43" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CZ43" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DA43" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DB43" t="n">
         <v>75</v>
       </c>
       <c r="DC43" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DD43" t="n">
-        <v>2.29</v>
+        <v>1.5</v>
       </c>
       <c r="DE43" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="DF43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DH43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="DI43" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="DJ43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DK43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL43" t="n">
-        <v>1.89</v>
+        <v>1.46</v>
       </c>
       <c r="DM43" t="n">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="DN43" t="n">
-        <v>3.54</v>
+        <v>3.73</v>
       </c>
       <c r="DO43" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
       </c>
       <c r="DQ43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS43" t="b">
         <v>0</v>
@@ -21236,82 +21244,74 @@
         <v>0</v>
       </c>
       <c r="DV43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW43" t="n">
-        <v>16.85</v>
+        <v>17.45</v>
       </c>
       <c r="DX43" t="n">
-        <v>7.28</v>
+        <v>6.62</v>
       </c>
       <c r="DY43" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ43" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="EA43" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EB43" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="EC43" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="ED43" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EE43" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EF43" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EF43" t="inlineStr"/>
       <c r="EG43" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EH43" t="inlineStr">
         <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EI43" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EI43" t="inlineStr"/>
       <c r="EJ43" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EK43" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EL43" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EM43" t="inlineStr"/>
@@ -23559,7 +23559,7 @@
         <v>2.8</v>
       </c>
       <c r="DO48" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP48" t="b">
         <v>1</v>
@@ -25443,7 +25443,7 @@
         <v>4.61</v>
       </c>
       <c r="DO52" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -27770,7 +27770,7 @@
         <v>100</v>
       </c>
       <c r="DD57" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE57" t="n">
         <v>0.29</v>
@@ -27803,7 +27803,7 @@
         <v>2.97</v>
       </c>
       <c r="DO57" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP57" t="b">
         <v>1</v>
@@ -30623,7 +30623,7 @@
         <v>3.72</v>
       </c>
       <c r="DO63" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP63" t="b">
         <v>1</v>
@@ -31509,7 +31509,7 @@
         <v>1.43</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF65" t="n">
         <v>2</v>
@@ -31539,7 +31539,7 @@
         <v>3.22</v>
       </c>
       <c r="DO65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32027,7 +32027,7 @@
         <v>2.96</v>
       </c>
       <c r="DO66" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -36335,170 +36335,170 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45948.69791666666</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
       </c>
       <c r="I76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>10</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>6</v>
+      </c>
+      <c r="R76" t="n">
         <v>3</v>
-      </c>
-      <c r="J76" t="n">
-        <v>6</v>
-      </c>
-      <c r="K76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" t="n">
-        <v>7</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>8</v>
-      </c>
-      <c r="R76" t="n">
-        <v>2</v>
       </c>
       <c r="S76" t="n">
         <v>16</v>
       </c>
       <c r="T76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V76" t="n">
+        <v>3</v>
+      </c>
+      <c r="W76" t="n">
+        <v>12</v>
+      </c>
+      <c r="X76" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Stadion Galgenwaard</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Herculesplein 241, Utrecht</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AU76" t="n">
         <v>4</v>
       </c>
-      <c r="W76" t="n">
-        <v>7</v>
-      </c>
-      <c r="X76" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>43</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Philips Stadion</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Frederiklaan 10, Eindhoven</t>
-        </is>
-      </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL76" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN76" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ76" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AR76" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS76" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT76" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AU76" t="n">
+      <c r="AV76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX76" t="n">
         <v>3</v>
       </c>
-      <c r="AV76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX76" t="n">
-        <v>1</v>
-      </c>
       <c r="AY76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA76" t="n">
         <v>1</v>
       </c>
       <c r="BB76" t="n">
-        <v>121</v>
+        <v>376</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36513,7 +36513,7 @@
         <v>1</v>
       </c>
       <c r="BI76" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BJ76" t="n">
         <v>0</v>
@@ -36522,14 +36522,14 @@
         <v>3</v>
       </c>
       <c r="BL76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM76" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN76" t="n">
         <v>3</v>
       </c>
-      <c r="BN76" t="n">
-        <v>4</v>
-      </c>
       <c r="BO76" t="n">
         <v>0</v>
       </c>
@@ -36552,25 +36552,25 @@
         <v>1</v>
       </c>
       <c r="BV76" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="BW76" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BX76" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="BY76" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="BZ76" t="n">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="CA76" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="CB76" t="n">
-        <v>3.02</v>
+        <v>2.79</v>
       </c>
       <c r="CC76" t="n">
         <v>0</v>
@@ -36618,37 +36618,37 @@
         <v>1</v>
       </c>
       <c r="CR76" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS76" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="CT76" t="n">
         <v>1</v>
       </c>
       <c r="CU76" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CV76" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CW76" t="n">
         <v>1</v>
       </c>
       <c r="CX76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CY76" t="n">
         <v>10</v>
       </c>
       <c r="CZ76" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA76" t="n">
         <v>75</v>
       </c>
-      <c r="DA76" t="n">
-        <v>100</v>
-      </c>
       <c r="DB76" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DC76" t="n">
         <v>88</v>
@@ -36657,34 +36657,34 @@
         <v>2.29</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
       </c>
       <c r="DG76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH76" t="n">
         <v>1.25</v>
       </c>
-      <c r="DH76" t="n">
-        <v>2.38</v>
-      </c>
       <c r="DI76" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="DJ76" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK76" t="n">
         <v>25</v>
       </c>
-      <c r="DK76" t="n">
-        <v>0</v>
-      </c>
       <c r="DL76" t="n">
-        <v>2.39</v>
+        <v>1.65</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.54</v>
+        <v>1.16</v>
       </c>
       <c r="DN76" t="n">
-        <v>3.93</v>
+        <v>2.81</v>
       </c>
       <c r="DO76" t="n">
         <v>14</v>
@@ -36699,7 +36699,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -36711,14 +36711,14 @@
         <v>1</v>
       </c>
       <c r="DW76" t="n">
-        <v>13.13</v>
+        <v>12.46</v>
       </c>
       <c r="DX76" t="n">
-        <v>3.69</v>
+        <v>3.16</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
@@ -36728,27 +36728,27 @@
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr"/>
@@ -36757,15 +36757,19 @@
       <c r="EI76" t="inlineStr"/>
       <c r="EJ76" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EK76" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EL76" t="inlineStr"/>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
       <c r="EM76" t="inlineStr"/>
       <c r="EN76" t="inlineStr"/>
       <c r="EO76" t="inlineStr"/>
@@ -36787,34 +36791,34 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
         <v>45948.69791666666</v>
       </c>
       <c r="G77" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
         <v>3</v>
       </c>
-      <c r="H77" t="n">
-        <v>1</v>
-      </c>
-      <c r="I77" t="n">
-        <v>4</v>
-      </c>
       <c r="J77" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M77" t="n">
         <v>1</v>
@@ -36829,128 +36833,128 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S77" t="n">
         <v>16</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U77" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V77" t="n">
+        <v>4</v>
+      </c>
+      <c r="W77" t="n">
+        <v>7</v>
+      </c>
+      <c r="X77" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Philips Stadion</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Frederiklaan 10, Eindhoven</t>
+        </is>
+      </c>
+      <c r="AC77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AU77" t="n">
         <v>3</v>
       </c>
-      <c r="W77" t="n">
-        <v>12</v>
-      </c>
-      <c r="X77" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Stadion Galgenwaard</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>Herculesplein 241, Utrecht</t>
-        </is>
-      </c>
-      <c r="AC77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AG77" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AK77" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL77" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM77" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN77" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO77" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AP77" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ77" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR77" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS77" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AT77" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AU77" t="n">
-        <v>4</v>
-      </c>
       <c r="AV77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ77" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA77" t="n">
         <v>1</v>
       </c>
       <c r="BB77" t="n">
-        <v>376</v>
+        <v>121</v>
       </c>
       <c r="BC77" t="n">
         <v>0</v>
       </c>
       <c r="BD77" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BE77" t="n">
         <v>0</v>
@@ -36965,7 +36969,7 @@
         <v>1</v>
       </c>
       <c r="BI77" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BJ77" t="n">
         <v>0</v>
@@ -36974,133 +36978,133 @@
         <v>3</v>
       </c>
       <c r="BL77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM77" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU77" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV77" t="n">
         <v>7</v>
       </c>
-      <c r="BN77" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ77" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR77" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS77" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT77" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU77" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV77" t="n">
-        <v>56</v>
-      </c>
-      <c r="BW77" t="n">
-        <v>22</v>
-      </c>
-      <c r="BX77" t="n">
-        <v>133</v>
-      </c>
-      <c r="BY77" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ77" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CA77" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="CB77" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CC77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP77" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR77" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS77" t="n">
-        <v>12</v>
-      </c>
-      <c r="CT77" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU77" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV77" t="n">
-        <v>12</v>
-      </c>
       <c r="CW77" t="n">
         <v>1</v>
       </c>
       <c r="CX77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CY77" t="n">
         <v>10</v>
       </c>
       <c r="CZ77" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="DA77" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB77" t="n">
         <v>75</v>
-      </c>
-      <c r="DB77" t="n">
-        <v>50</v>
       </c>
       <c r="DC77" t="n">
         <v>88</v>
@@ -37109,34 +37113,34 @@
         <v>2.29</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.29</v>
+        <v>0.71</v>
       </c>
       <c r="DF77" t="n">
         <v>1.75</v>
       </c>
       <c r="DG77" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="DH77" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DI77" t="n">
         <v>1.25</v>
       </c>
-      <c r="DI77" t="n">
-        <v>0.88</v>
-      </c>
       <c r="DJ77" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="DK77" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL77" t="n">
-        <v>1.65</v>
+        <v>2.39</v>
       </c>
       <c r="DM77" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="DN77" t="n">
-        <v>2.81</v>
+        <v>3.93</v>
       </c>
       <c r="DO77" t="n">
         <v>14</v>
@@ -37151,7 +37155,7 @@
         <v>1</v>
       </c>
       <c r="DS77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT77" t="b">
         <v>0</v>
@@ -37163,14 +37167,14 @@
         <v>1</v>
       </c>
       <c r="DW77" t="n">
-        <v>12.46</v>
+        <v>13.13</v>
       </c>
       <c r="DX77" t="n">
-        <v>3.16</v>
+        <v>3.69</v>
       </c>
       <c r="DY77" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ77" t="inlineStr">
@@ -37180,27 +37184,27 @@
       </c>
       <c r="EA77" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="EB77" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="EC77" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="ED77" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE77" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EF77" t="inlineStr"/>
@@ -37209,19 +37213,15 @@
       <c r="EI77" t="inlineStr"/>
       <c r="EJ77" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="EK77" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EL77" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EL77" t="inlineStr"/>
       <c r="EM77" t="inlineStr"/>
       <c r="EN77" t="inlineStr"/>
       <c r="EO77" t="inlineStr"/>
@@ -37562,7 +37562,7 @@
         <v>88</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE78" t="n">
         <v>1.63</v>
@@ -37595,7 +37595,7 @@
         <v>3.9</v>
       </c>
       <c r="DO78" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -39019,7 +39019,7 @@
         <v>3.08</v>
       </c>
       <c r="DO81" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
@@ -40401,7 +40401,7 @@
         <v>2</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF84" t="n">
         <v>2.5</v>
@@ -40431,7 +40431,7 @@
         <v>3.42</v>
       </c>
       <c r="DO84" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -42335,7 +42335,7 @@
         <v>3.98</v>
       </c>
       <c r="DO88" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP88" t="b">
         <v>1</v>
@@ -44650,7 +44650,7 @@
         <v>100</v>
       </c>
       <c r="DD93" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE93" t="n">
         <v>0.71</v>
@@ -44683,7 +44683,7 @@
         <v>3.34</v>
       </c>
       <c r="DO93" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP93" t="b">
         <v>1</v>
@@ -46679,40 +46679,40 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
         <v>45963.5625</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K98" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -46721,22 +46721,22 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R98" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T98" t="n">
         <v>6</v>
       </c>
       <c r="U98" t="n">
+        <v>18</v>
+      </c>
+      <c r="V98" t="n">
         <v>10</v>
-      </c>
-      <c r="V98" t="n">
-        <v>20</v>
       </c>
       <c r="W98" t="n">
         <v>7</v>
@@ -46745,77 +46745,69 @@
         <v>12</v>
       </c>
       <c r="Y98" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Z98" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>Sparta-Stadion Het Kasteel</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>Spartapark Noord 1, Rotterdam</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE98" t="n">
-        <v>4.2</v>
+        <v>2.89</v>
       </c>
       <c r="AF98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG98" t="n">
-        <v>1.7</v>
+        <v>2.44</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AI98" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AJ98" t="n">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="AK98" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM98" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL98" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM98" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN98" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AO98" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AR98" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AS98" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AT98" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AU98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV98" t="n">
         <v>0</v>
@@ -46824,25 +46816,25 @@
         <v>0</v>
       </c>
       <c r="AX98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY98" t="n">
         <v>1</v>
       </c>
       <c r="AZ98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA98" t="n">
         <v>0</v>
       </c>
       <c r="BB98" t="n">
-        <v>378</v>
+        <v>-1</v>
       </c>
       <c r="BC98" t="n">
         <v>0</v>
       </c>
       <c r="BD98" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BE98" t="n">
         <v>0</v>
@@ -46857,73 +46849,73 @@
         <v>1</v>
       </c>
       <c r="BI98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BJ98" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BK98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR98" t="n">
         <v>3</v>
       </c>
-      <c r="BM98" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN98" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO98" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP98" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ98" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR98" t="n">
-        <v>1</v>
-      </c>
       <c r="BS98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU98" t="n">
         <v>1</v>
       </c>
       <c r="BV98" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BW98" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="BX98" t="n">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="BY98" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="BZ98" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="CA98" t="n">
-        <v>2.63</v>
+        <v>1.21</v>
       </c>
       <c r="CB98" t="n">
-        <v>3.77</v>
+        <v>3.13</v>
       </c>
       <c r="CC98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD98" t="n">
         <v>0</v>
       </c>
       <c r="CE98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF98" t="n">
         <v>0</v>
@@ -46947,88 +46939,88 @@
         <v>0</v>
       </c>
       <c r="CM98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ98" t="n">
         <v>1</v>
       </c>
       <c r="CR98" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="CS98" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CT98" t="n">
         <v>1</v>
       </c>
       <c r="CU98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CV98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CW98" t="n">
         <v>1</v>
       </c>
       <c r="CX98" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="CY98" t="n">
         <v>9</v>
       </c>
       <c r="CZ98" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA98" t="n">
         <v>70</v>
       </c>
-      <c r="DA98" t="n">
+      <c r="DB98" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC98" t="n">
         <v>80</v>
       </c>
-      <c r="DB98" t="n">
+      <c r="DD98" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE98" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF98" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH98" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ98" t="n">
         <v>50</v>
       </c>
-      <c r="DC98" t="n">
-        <v>90</v>
-      </c>
-      <c r="DD98" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="DE98" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DF98" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG98" t="n">
-        <v>2</v>
-      </c>
-      <c r="DH98" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DI98" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="DJ98" t="n">
+      <c r="DK98" t="n">
         <v>30</v>
       </c>
-      <c r="DK98" t="n">
-        <v>20</v>
-      </c>
       <c r="DL98" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="DM98" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="DN98" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="DO98" t="n">
         <v>14</v>
@@ -47037,7 +47029,7 @@
         <v>1</v>
       </c>
       <c r="DQ98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR98" t="b">
         <v>0</v>
@@ -47052,80 +47044,104 @@
         <v>0</v>
       </c>
       <c r="DV98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW98" t="n">
-        <v>12.53</v>
+        <v>10.99</v>
       </c>
       <c r="DX98" t="n">
-        <v>6.3</v>
+        <v>6.54</v>
       </c>
       <c r="DY98" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="DZ98" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA98" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB98" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="EC98" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="ED98" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EE98" t="inlineStr">
         <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="EF98" t="inlineStr"/>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EF98" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
       <c r="EG98" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="EH98" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EI98" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EJ98" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EK98" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EL98" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EM98" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EN98" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EO98" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="EI98" t="inlineStr"/>
-      <c r="EJ98" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EK98" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EL98" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EM98" t="inlineStr"/>
-      <c r="EN98" t="inlineStr"/>
-      <c r="EO98" t="inlineStr"/>
-      <c r="EP98" t="inlineStr"/>
+      <c r="EP98" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -47143,64 +47159,64 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>45963.5625</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
+        <v>6</v>
+      </c>
+      <c r="K99" t="n">
+        <v>9</v>
+      </c>
+      <c r="L99" t="n">
+        <v>15</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>3</v>
+      </c>
+      <c r="R99" t="n">
+        <v>14</v>
+      </c>
+      <c r="S99" t="n">
         <v>7</v>
-      </c>
-      <c r="K99" t="n">
-        <v>3</v>
-      </c>
-      <c r="L99" t="n">
-        <v>10</v>
-      </c>
-      <c r="M99" t="n">
-        <v>2</v>
-      </c>
-      <c r="N99" t="n">
-        <v>4</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>7</v>
-      </c>
-      <c r="R99" t="n">
-        <v>4</v>
-      </c>
-      <c r="S99" t="n">
-        <v>11</v>
       </c>
       <c r="T99" t="n">
         <v>6</v>
       </c>
       <c r="U99" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="V99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="W99" t="n">
         <v>7</v>
@@ -47209,69 +47225,77 @@
         <v>12</v>
       </c>
       <c r="Y99" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="Z99" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>Sparta-Stadion Het Kasteel</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>Spartapark Noord 1, Rotterdam</t>
+        </is>
+      </c>
       <c r="AC99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AF99" t="n">
         <v>4</v>
       </c>
-      <c r="AE99" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF99" t="n">
-        <v>3</v>
-      </c>
       <c r="AG99" t="n">
-        <v>2.44</v>
+        <v>1.7</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="AK99" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT99" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL99" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN99" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO99" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AP99" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ99" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR99" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AS99" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT99" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AU99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV99" t="n">
         <v>0</v>
@@ -47280,25 +47304,25 @@
         <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY99" t="n">
         <v>1</v>
       </c>
       <c r="AZ99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA99" t="n">
         <v>0</v>
       </c>
       <c r="BB99" t="n">
-        <v>-1</v>
+        <v>378</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -47313,73 +47337,73 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BJ99" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM99" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN99" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BO99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ99" t="n">
         <v>1</v>
       </c>
       <c r="BR99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BW99" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="BX99" t="n">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="BY99" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ99" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="CA99" t="n">
-        <v>1.21</v>
+        <v>2.63</v>
       </c>
       <c r="CB99" t="n">
-        <v>3.13</v>
+        <v>3.77</v>
       </c>
       <c r="CC99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD99" t="n">
         <v>0</v>
       </c>
       <c r="CE99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF99" t="n">
         <v>0</v>
@@ -47403,97 +47427,97 @@
         <v>0</v>
       </c>
       <c r="CM99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ99" t="n">
         <v>1</v>
       </c>
       <c r="CR99" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="CS99" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CT99" t="n">
         <v>1</v>
       </c>
       <c r="CU99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CV99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CW99" t="n">
         <v>1</v>
       </c>
       <c r="CX99" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="CY99" t="n">
         <v>9</v>
       </c>
       <c r="CZ99" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB99" t="n">
         <v>50</v>
       </c>
-      <c r="DA99" t="n">
-        <v>70</v>
-      </c>
-      <c r="DB99" t="n">
-        <v>40</v>
-      </c>
       <c r="DC99" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="DE99" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DF99" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DG99" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH99" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DI99" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DJ99" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK99" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL99" t="n">
         <v>1.29</v>
       </c>
-      <c r="DF99" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DG99" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DH99" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="DI99" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DJ99" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK99" t="n">
-        <v>30</v>
-      </c>
-      <c r="DL99" t="n">
-        <v>1.41</v>
-      </c>
       <c r="DM99" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="DN99" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="DO99" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP99" t="b">
         <v>1</v>
       </c>
       <c r="DQ99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR99" t="b">
         <v>0</v>
@@ -47508,104 +47532,80 @@
         <v>0</v>
       </c>
       <c r="DV99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW99" t="n">
-        <v>10.99</v>
+        <v>12.53</v>
       </c>
       <c r="DX99" t="n">
-        <v>6.54</v>
+        <v>6.3</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="EA99" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EB99" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="EC99" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="ED99" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EE99" t="inlineStr">
         <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EF99" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr"/>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EH99" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr"/>
+      <c r="EJ99" t="inlineStr">
+        <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="EI99" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EJ99" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="EK99" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EM99" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EN99" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EO99" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EP99" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr"/>
+      <c r="EN99" t="inlineStr"/>
+      <c r="EO99" t="inlineStr"/>
+      <c r="EP99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -50775,7 +50775,7 @@
         <v>3.41</v>
       </c>
       <c r="DO106" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP106" t="b">
         <v>1</v>
@@ -51209,7 +51209,7 @@
         <v>2.29</v>
       </c>
       <c r="DE107" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF107" t="n">
         <v>2</v>
@@ -51239,7 +51239,7 @@
         <v>3.51</v>
       </c>
       <c r="DO107" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -53538,7 +53538,7 @@
         <v>92</v>
       </c>
       <c r="DD112" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="DE112" t="n">
         <v>1</v>
@@ -53571,7 +53571,7 @@
         <v>3.28</v>
       </c>
       <c r="DO112" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP112" t="b">
         <v>1</v>
@@ -56387,7 +56387,7 @@
         <v>2.58</v>
       </c>
       <c r="DO118" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="DP118" t="b">
         <v>1</v>
@@ -58867,162 +58867,170 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H124" t="n">
         <v>2</v>
       </c>
       <c r="I124" t="n">
+        <v>4</v>
+      </c>
+      <c r="J124" t="n">
+        <v>4</v>
+      </c>
+      <c r="K124" t="n">
         <v>3</v>
       </c>
-      <c r="J124" t="n">
+      <c r="L124" t="n">
+        <v>7</v>
+      </c>
+      <c r="M124" t="n">
+        <v>2</v>
+      </c>
+      <c r="N124" t="n">
+        <v>2</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>6</v>
+      </c>
+      <c r="R124" t="n">
+        <v>8</v>
+      </c>
+      <c r="S124" t="n">
+        <v>5</v>
+      </c>
+      <c r="T124" t="n">
+        <v>9</v>
+      </c>
+      <c r="U124" t="n">
+        <v>11</v>
+      </c>
+      <c r="V124" t="n">
+        <v>17</v>
+      </c>
+      <c r="W124" t="n">
+        <v>9</v>
+      </c>
+      <c r="X124" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>De Adelaarshorst</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>Vetkampstraat 1, Deventer</t>
+        </is>
+      </c>
+      <c r="AC124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ124" t="n">
         <v>3</v>
       </c>
-      <c r="K124" t="n">
-        <v>5</v>
-      </c>
-      <c r="L124" t="n">
-        <v>8</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0</v>
-      </c>
-      <c r="N124" t="n">
-        <v>3</v>
-      </c>
-      <c r="O124" t="n">
-        <v>0</v>
-      </c>
-      <c r="P124" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q124" t="n">
-        <v>2</v>
-      </c>
-      <c r="R124" t="n">
-        <v>7</v>
-      </c>
-      <c r="S124" t="n">
-        <v>10</v>
-      </c>
-      <c r="T124" t="n">
-        <v>4</v>
-      </c>
-      <c r="U124" t="n">
-        <v>12</v>
-      </c>
-      <c r="V124" t="n">
-        <v>11</v>
-      </c>
-      <c r="W124" t="n">
-        <v>8</v>
-      </c>
-      <c r="X124" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y124" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z124" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA124" t="inlineStr"/>
-      <c r="AB124" t="inlineStr"/>
-      <c r="AC124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD124" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE124" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AF124" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AG124" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AH124" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI124" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AJ124" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AK124" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL124" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AM124" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN124" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO124" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AP124" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AQ124" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR124" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AS124" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="AT124" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AU124" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV124" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY124" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ124" t="n">
-        <v>2</v>
-      </c>
       <c r="BA124" t="n">
         <v>1</v>
       </c>
       <c r="BB124" t="n">
-        <v>367</v>
+        <v>-1</v>
       </c>
       <c r="BC124" t="n">
         <v>0</v>
       </c>
       <c r="BD124" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="BE124" t="n">
         <v>0</v>
@@ -59037,64 +59045,64 @@
         <v>1</v>
       </c>
       <c r="BI124" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ124" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BK124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT124" t="n">
         <v>3</v>
       </c>
-      <c r="BL124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM124" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN124" t="n">
-        <v>4</v>
-      </c>
-      <c r="BO124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ124" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR124" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS124" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT124" t="n">
-        <v>2</v>
-      </c>
       <c r="BU124" t="n">
         <v>1</v>
       </c>
       <c r="BV124" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="BW124" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="BX124" t="n">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="BY124" t="n">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="BZ124" t="n">
-        <v>1.28</v>
+        <v>1.55</v>
       </c>
       <c r="CA124" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="CB124" t="n">
-        <v>2.91</v>
+        <v>3.43</v>
       </c>
       <c r="CC124" t="n">
         <v>0</v>
@@ -59127,10 +59135,10 @@
         <v>0</v>
       </c>
       <c r="CM124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO124" t="n">
         <v>0</v>
@@ -59142,73 +59150,73 @@
         <v>1</v>
       </c>
       <c r="CR124" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="CS124" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="CT124" t="n">
         <v>1</v>
       </c>
       <c r="CU124" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CV124" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="CW124" t="n">
         <v>1</v>
       </c>
       <c r="CX124" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="CY124" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CZ124" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="DA124" t="n">
         <v>92</v>
       </c>
       <c r="DB124" t="n">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="DC124" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="DD124" t="n">
-        <v>0.75</v>
+        <v>1.71</v>
       </c>
       <c r="DE124" t="n">
-        <v>2.29</v>
+        <v>0.71</v>
       </c>
       <c r="DF124" t="n">
-        <v>0.86</v>
+        <v>1.83</v>
       </c>
       <c r="DG124" t="n">
-        <v>2.17</v>
+        <v>0.67</v>
       </c>
       <c r="DH124" t="n">
-        <v>0.77</v>
+        <v>1.23</v>
       </c>
       <c r="DI124" t="n">
-        <v>2.15</v>
+        <v>1.54</v>
       </c>
       <c r="DJ124" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="DK124" t="n">
         <v>9</v>
       </c>
       <c r="DL124" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="DM124" t="n">
-        <v>2.08</v>
+        <v>1.51</v>
       </c>
       <c r="DN124" t="n">
-        <v>3.9</v>
+        <v>3.09</v>
       </c>
       <c r="DO124" t="n">
         <v>14</v>
@@ -59223,7 +59231,7 @@
         <v>1</v>
       </c>
       <c r="DS124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT124" t="b">
         <v>0</v>
@@ -59235,82 +59243,74 @@
         <v>1</v>
       </c>
       <c r="DW124" t="n">
-        <v>5.14</v>
+        <v>6.3</v>
       </c>
       <c r="DX124" t="n">
-        <v>20.38</v>
+        <v>11.11</v>
       </c>
       <c r="DY124" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="DZ124" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="EA124" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EB124" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="EC124" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="ED124" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EE124" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EF124" t="inlineStr"/>
-      <c r="EG124" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="EH124" t="inlineStr">
-        <is>
-          <t>1.74</t>
-        </is>
-      </c>
+      <c r="EG124" t="inlineStr"/>
+      <c r="EH124" t="inlineStr"/>
       <c r="EI124" t="inlineStr"/>
       <c r="EJ124" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EK124" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EL124" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EM124" t="inlineStr"/>
       <c r="EN124" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EO124" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="EP124" t="inlineStr"/>
@@ -59331,143 +59331,135 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F125" s="2" t="n">
         <v>45991.5625</v>
       </c>
       <c r="G125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H125" t="n">
         <v>2</v>
       </c>
       <c r="I125" t="n">
+        <v>3</v>
+      </c>
+      <c r="J125" t="n">
+        <v>3</v>
+      </c>
+      <c r="K125" t="n">
+        <v>5</v>
+      </c>
+      <c r="L125" t="n">
+        <v>8</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>3</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>2</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="n">
         <v>4</v>
       </c>
-      <c r="J125" t="n">
-        <v>4</v>
-      </c>
-      <c r="K125" t="n">
+      <c r="U125" t="n">
+        <v>12</v>
+      </c>
+      <c r="V125" t="n">
+        <v>11</v>
+      </c>
+      <c r="W125" t="n">
+        <v>8</v>
+      </c>
+      <c r="X125" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA125" t="inlineStr"/>
+      <c r="AB125" t="inlineStr"/>
+      <c r="AC125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD125" t="n">
         <v>3</v>
       </c>
-      <c r="L125" t="n">
-        <v>7</v>
-      </c>
-      <c r="M125" t="n">
-        <v>2</v>
-      </c>
-      <c r="N125" t="n">
-        <v>2</v>
-      </c>
-      <c r="O125" t="n">
-        <v>0</v>
-      </c>
-      <c r="P125" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q125" t="n">
-        <v>6</v>
-      </c>
-      <c r="R125" t="n">
-        <v>8</v>
-      </c>
-      <c r="S125" t="n">
-        <v>5</v>
-      </c>
-      <c r="T125" t="n">
-        <v>9</v>
-      </c>
-      <c r="U125" t="n">
-        <v>11</v>
-      </c>
-      <c r="V125" t="n">
-        <v>17</v>
-      </c>
-      <c r="W125" t="n">
-        <v>9</v>
-      </c>
-      <c r="X125" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y125" t="n">
-        <v>59</v>
-      </c>
-      <c r="Z125" t="n">
-        <v>41</v>
-      </c>
-      <c r="AA125" t="inlineStr">
-        <is>
-          <t>De Adelaarshorst</t>
-        </is>
-      </c>
-      <c r="AB125" t="inlineStr">
-        <is>
-          <t>Vetkampstraat 1, Deventer</t>
-        </is>
-      </c>
-      <c r="AC125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>2</v>
-      </c>
       <c r="AE125" t="n">
-        <v>2.5</v>
+        <v>6.1</v>
       </c>
       <c r="AF125" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="AG125" t="n">
-        <v>2.33</v>
+        <v>1.53</v>
       </c>
       <c r="AH125" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AI125" t="n">
-        <v>1.78</v>
+        <v>1.42</v>
       </c>
       <c r="AJ125" t="n">
-        <v>2.89</v>
+        <v>2.18</v>
       </c>
       <c r="AK125" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AL125" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AM125" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AN125" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AO125" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AR125" t="n">
-        <v>2.5</v>
+        <v>2.19</v>
       </c>
       <c r="AS125" t="n">
-        <v>3.04</v>
+        <v>3.66</v>
       </c>
       <c r="AT125" t="n">
-        <v>1.47</v>
+        <v>1.66</v>
       </c>
       <c r="AU125" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV125" t="n">
         <v>0</v>
@@ -59476,25 +59468,25 @@
         <v>1</v>
       </c>
       <c r="AX125" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY125" t="n">
         <v>1</v>
       </c>
       <c r="AZ125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA125" t="n">
         <v>1</v>
       </c>
       <c r="BB125" t="n">
-        <v>-1</v>
+        <v>367</v>
       </c>
       <c r="BC125" t="n">
         <v>0</v>
       </c>
       <c r="BD125" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="BE125" t="n">
         <v>0</v>
@@ -59509,22 +59501,22 @@
         <v>1</v>
       </c>
       <c r="BI125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BJ125" t="n">
+        <v>4</v>
+      </c>
+      <c r="BK125" t="n">
         <v>3</v>
       </c>
-      <c r="BK125" t="n">
-        <v>2</v>
-      </c>
       <c r="BL125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM125" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN125" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BO125" t="n">
         <v>0</v>
@@ -59533,40 +59525,40 @@
         <v>1</v>
       </c>
       <c r="BQ125" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS125" t="n">
         <v>1</v>
       </c>
       <c r="BT125" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU125" t="n">
         <v>1</v>
       </c>
       <c r="BV125" t="n">
+        <v>53</v>
+      </c>
+      <c r="BW125" t="n">
         <v>60</v>
       </c>
-      <c r="BW125" t="n">
-        <v>34</v>
-      </c>
       <c r="BX125" t="n">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="BY125" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="BZ125" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="CA125" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="CB125" t="n">
-        <v>3.43</v>
+        <v>2.91</v>
       </c>
       <c r="CC125" t="n">
         <v>0</v>
@@ -59599,10 +59591,10 @@
         <v>0</v>
       </c>
       <c r="CM125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO125" t="n">
         <v>0</v>
@@ -59614,73 +59606,73 @@
         <v>1</v>
       </c>
       <c r="CR125" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="CS125" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="CT125" t="n">
         <v>1</v>
       </c>
       <c r="CU125" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="CV125" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW125" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX125" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY125" t="n">
         <v>9</v>
       </c>
-      <c r="CW125" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX125" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY125" t="n">
-        <v>7</v>
-      </c>
       <c r="CZ125" t="n">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="DA125" t="n">
         <v>92</v>
       </c>
       <c r="DB125" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="DC125" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="DD125" t="n">
-        <v>1.71</v>
+        <v>0.75</v>
       </c>
       <c r="DE125" t="n">
-        <v>0.71</v>
+        <v>2.29</v>
       </c>
       <c r="DF125" t="n">
-        <v>1.83</v>
+        <v>0.86</v>
       </c>
       <c r="DG125" t="n">
-        <v>0.67</v>
+        <v>2.17</v>
       </c>
       <c r="DH125" t="n">
-        <v>1.23</v>
+        <v>0.77</v>
       </c>
       <c r="DI125" t="n">
-        <v>1.54</v>
+        <v>2.15</v>
       </c>
       <c r="DJ125" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="DK125" t="n">
         <v>9</v>
       </c>
       <c r="DL125" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="DM125" t="n">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="DN125" t="n">
-        <v>3.09</v>
+        <v>3.9</v>
       </c>
       <c r="DO125" t="n">
         <v>14</v>
@@ -59695,7 +59687,7 @@
         <v>1</v>
       </c>
       <c r="DS125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT125" t="b">
         <v>0</v>
@@ -59707,74 +59699,82 @@
         <v>1</v>
       </c>
       <c r="DW125" t="n">
-        <v>6.3</v>
+        <v>5.14</v>
       </c>
       <c r="DX125" t="n">
-        <v>11.11</v>
+        <v>20.38</v>
       </c>
       <c r="DY125" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="DZ125" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>90%</t>
         </is>
       </c>
       <c r="EA125" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EB125" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="EC125" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="ED125" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EE125" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EF125" t="inlineStr"/>
-      <c r="EG125" t="inlineStr"/>
-      <c r="EH125" t="inlineStr"/>
+      <c r="EG125" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EH125" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
       <c r="EI125" t="inlineStr"/>
       <c r="EJ125" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EK125" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EL125" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EM125" t="inlineStr"/>
       <c r="EN125" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EO125" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EP125" t="inlineStr"/>
@@ -60256,6 +60256,466 @@
       <c r="EP126" t="inlineStr">
         <is>
           <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Netherlands_Eredivisie_2025-2026</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>14</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Ajax</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>45993.5625</v>
+      </c>
+      <c r="G127" t="n">
+        <v>2</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>2</v>
+      </c>
+      <c r="J127" t="n">
+        <v>3</v>
+      </c>
+      <c r="K127" t="n">
+        <v>5</v>
+      </c>
+      <c r="L127" t="n">
+        <v>8</v>
+      </c>
+      <c r="M127" t="n">
+        <v>1</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>6</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7</v>
+      </c>
+      <c r="S127" t="n">
+        <v>7</v>
+      </c>
+      <c r="T127" t="n">
+        <v>10</v>
+      </c>
+      <c r="U127" t="n">
+        <v>13</v>
+      </c>
+      <c r="V127" t="n">
+        <v>17</v>
+      </c>
+      <c r="W127" t="n">
+        <v>14</v>
+      </c>
+      <c r="X127" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>Johan Cruijff Arena</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>ArenA Boulevard 1, Amsterdam</t>
+        </is>
+      </c>
+      <c r="AC127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>120</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>62</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>51</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>84</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU127" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV127" t="n">
+        <v>14</v>
+      </c>
+      <c r="CW127" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX127" t="n">
+        <v>5</v>
+      </c>
+      <c r="CY127" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ127" t="n">
+        <v>55</v>
+      </c>
+      <c r="DA127" t="n">
+        <v>92</v>
+      </c>
+      <c r="DB127" t="n">
+        <v>38</v>
+      </c>
+      <c r="DC127" t="n">
+        <v>84</v>
+      </c>
+      <c r="DD127" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE127" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DF127" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DG127" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH127" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DI127" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="DJ127" t="n">
+        <v>45</v>
+      </c>
+      <c r="DK127" t="n">
+        <v>9</v>
+      </c>
+      <c r="DL127" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DM127" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DN127" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="DO127" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ127" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV127" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW127" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="DX127" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="DY127" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="DZ127" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="EA127" t="inlineStr">
+        <is>
+          <t>3.69</t>
+        </is>
+      </c>
+      <c r="EB127" t="inlineStr">
+        <is>
+          <t>3.76</t>
+        </is>
+      </c>
+      <c r="EC127" t="inlineStr">
+        <is>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="ED127" t="inlineStr">
+        <is>
+          <t>1.64</t>
+        </is>
+      </c>
+      <c r="EE127" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="EF127" t="inlineStr"/>
+      <c r="EG127" t="inlineStr"/>
+      <c r="EH127" t="inlineStr"/>
+      <c r="EI127" t="inlineStr"/>
+      <c r="EJ127" t="inlineStr"/>
+      <c r="EK127" t="inlineStr"/>
+      <c r="EL127" t="inlineStr"/>
+      <c r="EM127" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="EN127" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EO127" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EP127" t="inlineStr">
+        <is>
+          <t>1.48</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP127" headerRowCount="1">
-  <autoFilter ref="A1:EP127"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP128" headerRowCount="1">
+  <autoFilter ref="A1:EP128"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP127"/>
+  <dimension ref="A1:EP128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -4677,7 +4677,7 @@
         <v>1.83</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DF8" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE12" t="n">
         <v>2.29</v>
@@ -8167,40 +8167,40 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>45886.52083333334</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M16" t="n">
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -8209,122 +8209,122 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="n">
         <v>15</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
+        <v>15</v>
+      </c>
+      <c r="V16" t="n">
+        <v>20</v>
+      </c>
+      <c r="W16" t="n">
+        <v>9</v>
+      </c>
+      <c r="X16" t="n">
         <v>11</v>
       </c>
-      <c r="U16" t="n">
-        <v>19</v>
-      </c>
-      <c r="V16" t="n">
-        <v>15</v>
-      </c>
-      <c r="W16" t="n">
-        <v>10</v>
-      </c>
-      <c r="X16" t="n">
-        <v>12</v>
-      </c>
       <c r="Y16" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>De Grolsch Veste</t>
+          <t>Sparta-Stadion Het Kasteel</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Colosseum 65, Enschede</t>
+          <t>Spartapark Noord 1, Rotterdam</t>
         </is>
       </c>
       <c r="AC16" t="n">
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
-        <v>5.2</v>
+        <v>2.39</v>
       </c>
       <c r="AF16" t="n">
-        <v>4.45</v>
+        <v>3.55</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AO16" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AS16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AU16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA16" t="n">
         <v>1</v>
       </c>
       <c r="BB16" t="n">
-        <v>121</v>
+        <v>371</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
@@ -8345,73 +8345,73 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL16" t="n">
         <v>4</v>
       </c>
-      <c r="BJ16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK16" t="n">
+      <c r="BM16" t="n">
         <v>4</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>7</v>
       </c>
       <c r="BN16" t="n">
         <v>7</v>
       </c>
       <c r="BO16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="BW16" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="BX16" t="n">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="BY16" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CC16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD16" t="n">
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF16" t="n">
         <v>0</v>
@@ -8432,13 +8432,13 @@
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CS16" t="n">
         <v>24</v>
@@ -8459,19 +8459,19 @@
         <v>1</v>
       </c>
       <c r="CU16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CV16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CY16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ16" t="n">
         <v>0</v>
@@ -8486,10 +8486,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.57</v>
+        <v>1.14</v>
       </c>
       <c r="DE16" t="n">
-        <v>3</v>
+        <v>0.71</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8528,7 +8528,7 @@
         <v>1</v>
       </c>
       <c r="DR16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS16" t="b">
         <v>0</v>
@@ -8540,17 +8540,17 @@
         <v>0</v>
       </c>
       <c r="DV16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW16" t="inlineStr"/>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
@@ -8560,65 +8560,73 @@
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="EF16" t="inlineStr"/>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
       <c r="EG16" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EH16" t="inlineStr">
         <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EI16" t="inlineStr"/>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI16" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="EM16" t="inlineStr"/>
       <c r="EN16" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EO16" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EP16" t="inlineStr"/>
@@ -8639,164 +8647,164 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>45886.52083333334</v>
       </c>
       <c r="G17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
       </c>
       <c r="L17" t="n">
+        <v>14</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>4</v>
+      </c>
+      <c r="R17" t="n">
+        <v>4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="n">
         <v>11</v>
       </c>
-      <c r="M17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>5</v>
-      </c>
-      <c r="R17" t="n">
-        <v>5</v>
-      </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
+        <v>19</v>
+      </c>
+      <c r="V17" t="n">
+        <v>15</v>
+      </c>
+      <c r="W17" t="n">
         <v>10</v>
       </c>
-      <c r="T17" t="n">
-        <v>15</v>
-      </c>
-      <c r="U17" t="n">
-        <v>15</v>
-      </c>
-      <c r="V17" t="n">
-        <v>20</v>
-      </c>
-      <c r="W17" t="n">
-        <v>9</v>
-      </c>
       <c r="X17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y17" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Z17" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>Sparta-Stadion Het Kasteel</t>
+          <t>De Grolsch Veste</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Spartapark Noord 1, Rotterdam</t>
+          <t>Colosseum 65, Enschede</t>
         </is>
       </c>
       <c r="AC17" t="n">
         <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.39</v>
+        <v>5.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>3.55</v>
+        <v>4.45</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.15</v>
+        <v>2.61</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AO17" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AS17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AU17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA17" t="n">
         <v>1</v>
       </c>
       <c r="BB17" t="n">
-        <v>371</v>
+        <v>121</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8817,73 +8825,73 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL17" t="n">
         <v>3</v>
       </c>
-      <c r="BL17" t="n">
-        <v>4</v>
-      </c>
       <c r="BM17" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BN17" t="n">
         <v>7</v>
       </c>
       <c r="BO17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="BW17" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="BX17" t="n">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="BY17" t="n">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.99</v>
+        <v>1.53</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF17" t="n">
         <v>0</v>
@@ -8904,13 +8912,13 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8922,7 +8930,7 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CS17" t="n">
         <v>24</v>
@@ -8931,19 +8939,19 @@
         <v>1</v>
       </c>
       <c r="CU17" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV17" t="n">
         <v>10</v>
       </c>
-      <c r="CV17" t="n">
-        <v>9</v>
-      </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CY17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ17" t="n">
         <v>0</v>
@@ -8958,10 +8966,10 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.71</v>
+        <v>3</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9000,7 +9008,7 @@
         <v>1</v>
       </c>
       <c r="DR17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS17" t="b">
         <v>0</v>
@@ -9012,17 +9020,17 @@
         <v>0</v>
       </c>
       <c r="DV17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW17" t="inlineStr"/>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
@@ -9032,73 +9040,65 @@
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="EF17" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EF17" t="inlineStr"/>
       <c r="EG17" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EH17" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI17" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr"/>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EM17" t="inlineStr"/>
       <c r="EN17" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EO17" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EP17" t="inlineStr"/>
@@ -10857,7 +10857,7 @@
         <v>2.29</v>
       </c>
       <c r="DE21" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DF21" t="n">
         <v>3</v>
@@ -15538,7 +15538,7 @@
         <v>100</v>
       </c>
       <c r="DD31" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE31" t="n">
         <v>1.29</v>
@@ -18991,170 +18991,170 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
         <v>45913.79166666666</v>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J39" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
         <v>3</v>
       </c>
       <c r="L39" t="n">
+        <v>7</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>6</v>
+      </c>
+      <c r="R39" t="n">
+        <v>4</v>
+      </c>
+      <c r="S39" t="n">
         <v>9</v>
       </c>
-      <c r="M39" t="n">
-        <v>2</v>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>5</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
+        <v>6</v>
+      </c>
+      <c r="U39" t="n">
+        <v>15</v>
+      </c>
+      <c r="V39" t="n">
+        <v>10</v>
+      </c>
+      <c r="W39" t="n">
+        <v>15</v>
+      </c>
+      <c r="X39" t="n">
+        <v>17</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>De Grolsch Veste</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>Colosseum 65, Enschede</t>
+        </is>
+      </c>
+      <c r="AC39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AU39" t="n">
         <v>4</v>
       </c>
-      <c r="T39" t="n">
-        <v>10</v>
-      </c>
-      <c r="U39" t="n">
-        <v>9</v>
-      </c>
-      <c r="V39" t="n">
-        <v>11</v>
-      </c>
-      <c r="W39" t="n">
-        <v>10</v>
-      </c>
-      <c r="X39" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>47</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>Stadion Feijenoord</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>Van Zandvlietplein 1, Rotterdam</t>
-        </is>
-      </c>
-      <c r="AC39" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>1</v>
-      </c>
       <c r="AV39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA39" t="n">
         <v>1</v>
       </c>
       <c r="BB39" t="n">
-        <v>367</v>
+        <v>-1</v>
       </c>
       <c r="BC39" t="n">
         <v>0</v>
       </c>
       <c r="BD39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BE39" t="n">
         <v>0</v>
@@ -19175,7 +19175,7 @@
         <v>1</v>
       </c>
       <c r="BK39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL39" t="n">
         <v>2</v>
@@ -19184,163 +19184,163 @@
         <v>4</v>
       </c>
       <c r="BN39" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU39" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV39" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW39" t="n">
+        <v>28</v>
+      </c>
+      <c r="BX39" t="n">
+        <v>119</v>
+      </c>
+      <c r="BY39" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ39" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CA39" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CB39" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR39" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS39" t="n">
+        <v>29</v>
+      </c>
+      <c r="CT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU39" t="n">
+        <v>16</v>
+      </c>
+      <c r="CV39" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW39" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX39" t="n">
         <v>5</v>
-      </c>
-      <c r="BO39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ39" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS39" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT39" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU39" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV39" t="n">
-        <v>50</v>
-      </c>
-      <c r="BW39" t="n">
-        <v>60</v>
-      </c>
-      <c r="BX39" t="n">
-        <v>76</v>
-      </c>
-      <c r="BY39" t="n">
-        <v>110</v>
-      </c>
-      <c r="BZ39" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CA39" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CB39" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="CC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>18</v>
-      </c>
-      <c r="CS39" t="n">
-        <v>23</v>
-      </c>
-      <c r="CT39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU39" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV39" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW39" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX39" t="n">
-        <v>7</v>
       </c>
       <c r="CY39" t="n">
         <v>10</v>
       </c>
       <c r="CZ39" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DA39" t="n">
         <v>100</v>
       </c>
       <c r="DB39" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="DC39" t="n">
         <v>100</v>
       </c>
       <c r="DD39" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="DE39" t="n">
-        <v>0.71</v>
+        <v>0.29</v>
       </c>
       <c r="DF39" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG39" t="n">
         <v>0</v>
       </c>
       <c r="DH39" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="DI39" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="DJ39" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK39" t="n">
         <v>0</v>
       </c>
       <c r="DL39" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DM39" t="n">
-        <v>1.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DN39" t="n">
-        <v>3.64</v>
+        <v>2.65</v>
       </c>
       <c r="DO39" t="n">
         <v>14</v>
@@ -19349,13 +19349,13 @@
         <v>1</v>
       </c>
       <c r="DQ39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT39" t="b">
         <v>0</v>
@@ -19364,17 +19364,17 @@
         <v>0</v>
       </c>
       <c r="DV39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW39" t="n">
-        <v>15.9</v>
+        <v>16.03</v>
       </c>
       <c r="DX39" t="n">
-        <v>7.35</v>
+        <v>7.1</v>
       </c>
       <c r="DY39" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="DZ39" t="inlineStr">
@@ -19384,65 +19384,73 @@
       </c>
       <c r="EA39" t="inlineStr">
         <is>
-          <t>8.39</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="EB39" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>4.66</t>
         </is>
       </c>
       <c r="EC39" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="ED39" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EE39" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EF39" t="inlineStr"/>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EF39" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
       <c r="EG39" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="EH39" t="inlineStr">
         <is>
-          <t>1.81</t>
-        </is>
-      </c>
-      <c r="EI39" t="inlineStr"/>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="EI39" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
       <c r="EJ39" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EK39" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="EL39" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EM39" t="inlineStr"/>
       <c r="EN39" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="EO39" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.01</t>
         </is>
       </c>
       <c r="EP39" t="inlineStr"/>
@@ -19463,34 +19471,34 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
         <v>45913.79166666666</v>
       </c>
       <c r="G40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K40" t="n">
         <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M40" t="n">
         <v>2</v>
@@ -19499,134 +19507,134 @@
         <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R40" t="n">
+        <v>1</v>
+      </c>
+      <c r="S40" t="n">
         <v>4</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
+        <v>10</v>
+      </c>
+      <c r="U40" t="n">
         <v>9</v>
       </c>
-      <c r="T40" t="n">
-        <v>6</v>
-      </c>
-      <c r="U40" t="n">
-        <v>15</v>
-      </c>
       <c r="V40" t="n">
+        <v>11</v>
+      </c>
+      <c r="W40" t="n">
         <v>10</v>
       </c>
-      <c r="W40" t="n">
-        <v>15</v>
-      </c>
       <c r="X40" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Y40" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="Z40" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>De Grolsch Veste</t>
+          <t>Stadion Feijenoord</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Colosseum 65, Enschede</t>
+          <t>Van Zandvlietplein 1, Rotterdam</t>
         </is>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AD40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AF40" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="AG40" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AH40" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="AJ40" t="n">
-        <v>2.67</v>
+        <v>2.35</v>
       </c>
       <c r="AK40" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL40" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.41</v>
+        <v>1.51</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AO40" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR40" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AS40" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="AU40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BA40" t="n">
         <v>1</v>
       </c>
       <c r="BB40" t="n">
-        <v>-1</v>
+        <v>367</v>
       </c>
       <c r="BC40" t="n">
         <v>0</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE40" t="n">
         <v>0</v>
@@ -19647,7 +19655,7 @@
         <v>1</v>
       </c>
       <c r="BK40" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL40" t="n">
         <v>2</v>
@@ -19656,58 +19664,58 @@
         <v>4</v>
       </c>
       <c r="BN40" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT40" t="n">
         <v>3</v>
       </c>
-      <c r="BO40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ40" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS40" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT40" t="n">
-        <v>1</v>
-      </c>
       <c r="BU40" t="n">
         <v>1</v>
       </c>
       <c r="BV40" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="BW40" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BX40" t="n">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="BY40" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="BZ40" t="n">
-        <v>1.81</v>
+        <v>1.28</v>
       </c>
       <c r="CA40" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="CB40" t="n">
-        <v>2.93</v>
+        <v>2.49</v>
       </c>
       <c r="CC40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD40" t="n">
         <v>0</v>
       </c>
       <c r="CE40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF40" t="n">
         <v>0</v>
@@ -19728,10 +19736,10 @@
         <v>0</v>
       </c>
       <c r="CL40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN40" t="n">
         <v>0</v>
@@ -19746,73 +19754,73 @@
         <v>1</v>
       </c>
       <c r="CR40" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="CS40" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="CT40" t="n">
         <v>1</v>
       </c>
       <c r="CU40" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CV40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="CW40" t="n">
         <v>1</v>
       </c>
       <c r="CX40" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CY40" t="n">
         <v>10</v>
       </c>
       <c r="CZ40" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA40" t="n">
         <v>100</v>
       </c>
       <c r="DB40" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="DC40" t="n">
         <v>100</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.57</v>
+        <v>2.14</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.29</v>
+        <v>0.71</v>
       </c>
       <c r="DF40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG40" t="n">
         <v>0</v>
       </c>
       <c r="DH40" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="DI40" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="DJ40" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK40" t="n">
         <v>0</v>
       </c>
       <c r="DL40" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="DM40" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="DN40" t="n">
-        <v>2.65</v>
+        <v>3.64</v>
       </c>
       <c r="DO40" t="n">
         <v>14</v>
@@ -19821,13 +19829,13 @@
         <v>1</v>
       </c>
       <c r="DQ40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT40" t="b">
         <v>0</v>
@@ -19836,17 +19844,17 @@
         <v>0</v>
       </c>
       <c r="DV40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW40" t="n">
-        <v>16.03</v>
+        <v>15.9</v>
       </c>
       <c r="DX40" t="n">
-        <v>7.1</v>
+        <v>7.35</v>
       </c>
       <c r="DY40" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="DZ40" t="inlineStr">
@@ -19856,73 +19864,65 @@
       </c>
       <c r="EA40" t="inlineStr">
         <is>
-          <t>6.13</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="EB40" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="EC40" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="ED40" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EE40" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EF40" t="inlineStr"/>
+      <c r="EG40" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EH40" t="inlineStr">
+        <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="EE40" t="inlineStr">
+      <c r="EI40" t="inlineStr"/>
+      <c r="EJ40" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="EK40" t="inlineStr">
         <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="EF40" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="EG40" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="EH40" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="EI40" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EJ40" t="inlineStr">
-        <is>
-          <t>1.64</t>
-        </is>
-      </c>
-      <c r="EK40" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
       <c r="EL40" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="EM40" t="inlineStr"/>
       <c r="EN40" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EO40" t="inlineStr">
         <is>
-          <t>2.01</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EP40" t="inlineStr"/>
@@ -20262,7 +20262,7 @@
         <v>75</v>
       </c>
       <c r="DD41" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE41" t="n">
         <v>1.29</v>
@@ -20729,7 +20729,7 @@
         <v>2.29</v>
       </c>
       <c r="DE42" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DF42" t="n">
         <v>3</v>
@@ -28722,7 +28722,7 @@
         <v>67</v>
       </c>
       <c r="DD59" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE59" t="n">
         <v>3</v>
@@ -31509,7 +31509,7 @@
         <v>1.43</v>
       </c>
       <c r="DE65" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DF65" t="n">
         <v>2</v>
@@ -37243,40 +37243,40 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>45948.79166666666</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
         <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J78" t="n">
+        <v>3</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2</v>
+      </c>
+      <c r="L78" t="n">
         <v>5</v>
       </c>
-      <c r="K78" t="n">
-        <v>4</v>
-      </c>
-      <c r="L78" t="n">
-        <v>9</v>
-      </c>
       <c r="M78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -37291,122 +37291,122 @@
         <v>3</v>
       </c>
       <c r="S78" t="n">
+        <v>13</v>
+      </c>
+      <c r="T78" t="n">
+        <v>8</v>
+      </c>
+      <c r="U78" t="n">
+        <v>19</v>
+      </c>
+      <c r="V78" t="n">
         <v>11</v>
       </c>
-      <c r="T78" t="n">
+      <c r="W78" t="n">
+        <v>9</v>
+      </c>
+      <c r="X78" t="n">
         <v>10</v>
       </c>
-      <c r="U78" t="n">
-        <v>17</v>
-      </c>
-      <c r="V78" t="n">
-        <v>13</v>
-      </c>
-      <c r="W78" t="n">
-        <v>13</v>
-      </c>
-      <c r="X78" t="n">
-        <v>19</v>
-      </c>
       <c r="Y78" t="n">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="Z78" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Johan Cruijff Arena</t>
+          <t>Rat Verlegh Stadion</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>ArenA Boulevard 1, Amsterdam</t>
+          <t>Stadionstraat 23, Breda</t>
         </is>
       </c>
       <c r="AC78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU78" t="n">
         <v>4</v>
       </c>
-      <c r="AD78" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE78" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF78" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="AG78" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="AH78" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI78" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AJ78" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AK78" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL78" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM78" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AN78" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO78" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AP78" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ78" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR78" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AS78" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT78" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AU78" t="n">
-        <v>2</v>
-      </c>
       <c r="AV78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX78" t="n">
         <v>0</v>
       </c>
       <c r="AY78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB78" t="n">
-        <v>378</v>
+        <v>-1</v>
       </c>
       <c r="BC78" t="n">
         <v>0</v>
       </c>
       <c r="BD78" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="BE78" t="n">
         <v>0</v>
@@ -37421,22 +37421,22 @@
         <v>1</v>
       </c>
       <c r="BI78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK78" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM78" t="n">
         <v>3</v>
       </c>
       <c r="BN78" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BO78" t="n">
         <v>0</v>
@@ -37445,52 +37445,52 @@
         <v>1</v>
       </c>
       <c r="BQ78" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BR78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS78" t="n">
         <v>1</v>
       </c>
       <c r="BT78" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BU78" t="n">
         <v>1</v>
       </c>
       <c r="BV78" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="BW78" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="BX78" t="n">
-        <v>116</v>
+        <v>97</v>
       </c>
       <c r="BY78" t="n">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="BZ78" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="CA78" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="CB78" t="n">
         <v>3.21</v>
       </c>
       <c r="CC78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG78" t="n">
         <v>0</v>
@@ -37511,7 +37511,7 @@
         <v>0</v>
       </c>
       <c r="CM78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN78" t="n">
         <v>0</v>
@@ -37526,19 +37526,19 @@
         <v>1</v>
       </c>
       <c r="CR78" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CS78" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="CT78" t="n">
         <v>1</v>
       </c>
       <c r="CU78" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="CV78" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CW78" t="n">
         <v>1</v>
@@ -37550,49 +37550,49 @@
         <v>9</v>
       </c>
       <c r="CZ78" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="DA78" t="n">
         <v>88</v>
       </c>
       <c r="DB78" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="DC78" t="n">
         <v>88</v>
       </c>
       <c r="DD78" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="DE78" t="n">
-        <v>1.63</v>
+        <v>0.86</v>
       </c>
       <c r="DF78" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="DG78" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="DH78" t="n">
-        <v>2</v>
+        <v>0.88</v>
       </c>
       <c r="DI78" t="n">
-        <v>1.88</v>
+        <v>0.88</v>
       </c>
       <c r="DJ78" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="DK78" t="n">
         <v>13</v>
       </c>
       <c r="DL78" t="n">
-        <v>1.97</v>
+        <v>1.55</v>
       </c>
       <c r="DM78" t="n">
-        <v>1.93</v>
+        <v>1.1</v>
       </c>
       <c r="DN78" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="DO78" t="n">
         <v>14</v>
@@ -37604,10 +37604,10 @@
         <v>1</v>
       </c>
       <c r="DR78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT78" t="b">
         <v>0</v>
@@ -37616,94 +37616,102 @@
         <v>0</v>
       </c>
       <c r="DV78" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW78" t="n">
-        <v>12.42</v>
+        <v>13.08</v>
       </c>
       <c r="DX78" t="n">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="DY78" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="DZ78" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="EA78" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="EB78" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="EC78" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="ED78" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EE78" t="inlineStr">
         <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="EF78" t="inlineStr"/>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EG78" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EH78" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EI78" t="inlineStr"/>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
       <c r="EJ78" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EK78" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EL78" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EM78" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EN78" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EO78" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="EP78" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.52</t>
         </is>
       </c>
     </row>
@@ -37723,40 +37731,40 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
         <v>45948.79166666666</v>
       </c>
       <c r="G79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H79" t="n">
         <v>2</v>
       </c>
       <c r="I79" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" t="n">
+        <v>5</v>
+      </c>
+      <c r="K79" t="n">
         <v>4</v>
       </c>
-      <c r="J79" t="n">
-        <v>3</v>
-      </c>
-      <c r="K79" t="n">
-        <v>2</v>
-      </c>
       <c r="L79" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -37771,122 +37779,122 @@
         <v>3</v>
       </c>
       <c r="S79" t="n">
+        <v>11</v>
+      </c>
+      <c r="T79" t="n">
+        <v>10</v>
+      </c>
+      <c r="U79" t="n">
+        <v>17</v>
+      </c>
+      <c r="V79" t="n">
         <v>13</v>
       </c>
-      <c r="T79" t="n">
-        <v>8</v>
-      </c>
-      <c r="U79" t="n">
+      <c r="W79" t="n">
+        <v>13</v>
+      </c>
+      <c r="X79" t="n">
         <v>19</v>
       </c>
-      <c r="V79" t="n">
-        <v>11</v>
-      </c>
-      <c r="W79" t="n">
-        <v>9</v>
-      </c>
-      <c r="X79" t="n">
-        <v>10</v>
-      </c>
       <c r="Y79" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="Z79" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Rat Verlegh Stadion</t>
+          <t>Johan Cruijff Arena</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>Stadionstraat 23, Breda</t>
+          <t>ArenA Boulevard 1, Amsterdam</t>
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AF79" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.15</v>
+        <v>3.46</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AJ79" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="AK79" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL79" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AM79" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AN79" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AO79" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="AP79" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR79" t="n">
-        <v>2.59</v>
+        <v>2.27</v>
       </c>
       <c r="AS79" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AT79" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AU79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX79" t="n">
         <v>0</v>
       </c>
       <c r="AY79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA79" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB79" t="n">
-        <v>-1</v>
+        <v>378</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -37901,22 +37909,22 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK79" t="n">
         <v>3</v>
       </c>
-      <c r="BJ79" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK79" t="n">
-        <v>0</v>
-      </c>
       <c r="BL79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM79" t="n">
         <v>3</v>
       </c>
       <c r="BN79" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BO79" t="n">
         <v>0</v>
@@ -37925,52 +37933,52 @@
         <v>1</v>
       </c>
       <c r="BQ79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BR79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS79" t="n">
         <v>1</v>
       </c>
       <c r="BT79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="BW79" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="BX79" t="n">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="BY79" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="BZ79" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="CB79" t="n">
         <v>3.21</v>
       </c>
       <c r="CC79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG79" t="n">
         <v>0</v>
@@ -37991,7 +37999,7 @@
         <v>0</v>
       </c>
       <c r="CM79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN79" t="n">
         <v>0</v>
@@ -38006,19 +38014,19 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CS79" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV79" t="n">
         <v>12</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV79" t="n">
-        <v>11</v>
       </c>
       <c r="CW79" t="n">
         <v>1</v>
@@ -38030,49 +38038,49 @@
         <v>9</v>
       </c>
       <c r="CZ79" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="DA79" t="n">
         <v>88</v>
       </c>
       <c r="DB79" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="DC79" t="n">
         <v>88</v>
       </c>
       <c r="DD79" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="DE79" t="n">
-        <v>0.86</v>
+        <v>1.63</v>
       </c>
       <c r="DF79" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DG79" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DH79" t="n">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="DI79" t="n">
-        <v>0.88</v>
+        <v>1.88</v>
       </c>
       <c r="DJ79" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="DK79" t="n">
         <v>13</v>
       </c>
       <c r="DL79" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.1</v>
+        <v>1.93</v>
       </c>
       <c r="DN79" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="DO79" t="n">
         <v>14</v>
@@ -38084,10 +38092,10 @@
         <v>1</v>
       </c>
       <c r="DR79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT79" t="b">
         <v>0</v>
@@ -38096,102 +38104,94 @@
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW79" t="n">
-        <v>13.08</v>
+        <v>12.42</v>
       </c>
       <c r="DX79" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EF79" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EF79" t="inlineStr"/>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EI79" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EI79" t="inlineStr"/>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EM79" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EP79" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
@@ -38675,162 +38675,170 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
         <v>45949.52083333334</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L81" t="n">
+        <v>6</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>5</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6</v>
+      </c>
+      <c r="S81" t="n">
+        <v>6</v>
+      </c>
+      <c r="T81" t="n">
+        <v>8</v>
+      </c>
+      <c r="U81" t="n">
         <v>11</v>
       </c>
-      <c r="M81" t="n">
+      <c r="V81" t="n">
+        <v>14</v>
+      </c>
+      <c r="W81" t="n">
+        <v>10</v>
+      </c>
+      <c r="X81" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Van Donge &amp; De Roo Stadion</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Honingerdijk 110, Rotterdam</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
         <v>3</v>
       </c>
-      <c r="N81" t="n">
-        <v>2</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>2</v>
-      </c>
-      <c r="S81" t="n">
-        <v>12</v>
-      </c>
-      <c r="T81" t="n">
-        <v>6</v>
-      </c>
-      <c r="U81" t="n">
-        <v>12</v>
-      </c>
-      <c r="V81" t="n">
-        <v>8</v>
-      </c>
-      <c r="W81" t="n">
-        <v>11</v>
-      </c>
-      <c r="X81" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>2</v>
-      </c>
       <c r="AE81" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AF81" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AG81" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH81" t="n">
         <v>1.22</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AJ81" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL81" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AM81" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AO81" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AR81" t="n">
         <v>2.5</v>
       </c>
       <c r="AS81" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AU81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX81" t="n">
         <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA81" t="n">
         <v>1</v>
       </c>
       <c r="BB81" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -38848,130 +38856,130 @@
         <v>1</v>
       </c>
       <c r="BJ81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK81" t="n">
         <v>3</v>
       </c>
-      <c r="BK81" t="n">
-        <v>6</v>
-      </c>
       <c r="BL81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>59</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
         <v>7</v>
       </c>
-      <c r="BO81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT81" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV81" t="n">
-        <v>35</v>
-      </c>
-      <c r="BW81" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX81" t="n">
-        <v>78</v>
-      </c>
-      <c r="BY81" t="n">
-        <v>41</v>
-      </c>
-      <c r="BZ81" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CA81" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="CB81" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CC81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR81" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS81" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU81" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV81" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX81" t="n">
+      <c r="CY81" t="n">
         <v>8</v>
-      </c>
-      <c r="CY81" t="n">
-        <v>10</v>
       </c>
       <c r="CZ81" t="n">
         <v>63</v>
@@ -38986,22 +38994,22 @@
         <v>75</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.57</v>
+        <v>1.13</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.29</v>
+        <v>0.57</v>
       </c>
       <c r="DF81" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="DG81" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="DH81" t="n">
-        <v>1.88</v>
+        <v>0.75</v>
       </c>
       <c r="DI81" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="DJ81" t="n">
         <v>38</v>
@@ -39010,13 +39018,13 @@
         <v>25</v>
       </c>
       <c r="DL81" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="DM81" t="n">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="DN81" t="n">
-        <v>3.08</v>
+        <v>2.37</v>
       </c>
       <c r="DO81" t="n">
         <v>14</v>
@@ -39025,7 +39033,7 @@
         <v>1</v>
       </c>
       <c r="DQ81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR81" t="b">
         <v>0</v>
@@ -39042,74 +39050,102 @@
       <c r="DV81" t="b">
         <v>0</v>
       </c>
-      <c r="DW81" t="inlineStr"/>
-      <c r="DX81" t="inlineStr"/>
-      <c r="DY81" t="inlineStr"/>
-      <c r="DZ81" t="inlineStr"/>
+      <c r="DW81" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="DX81" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="DY81" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ81" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EJ81" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EM81" t="inlineStr"/>
-      <c r="EN81" t="inlineStr"/>
-      <c r="EO81" t="inlineStr"/>
-      <c r="EP81" t="inlineStr"/>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EN81" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO81" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP81" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -39127,170 +39163,162 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
         <v>45949.52083333334</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J82" t="n">
+        <v>7</v>
+      </c>
+      <c r="K82" t="n">
         <v>4</v>
       </c>
-      <c r="K82" t="n">
-        <v>2</v>
-      </c>
       <c r="L82" t="n">
+        <v>11</v>
+      </c>
+      <c r="M82" t="n">
+        <v>3</v>
+      </c>
+      <c r="N82" t="n">
+        <v>2</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>2</v>
+      </c>
+      <c r="S82" t="n">
+        <v>12</v>
+      </c>
+      <c r="T82" t="n">
         <v>6</v>
       </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
+      <c r="U82" t="n">
+        <v>12</v>
+      </c>
+      <c r="V82" t="n">
+        <v>8</v>
+      </c>
+      <c r="W82" t="n">
+        <v>11</v>
+      </c>
+      <c r="X82" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="n">
         <v>3</v>
       </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>5</v>
-      </c>
-      <c r="R82" t="n">
-        <v>6</v>
-      </c>
-      <c r="S82" t="n">
-        <v>6</v>
-      </c>
-      <c r="T82" t="n">
-        <v>8</v>
-      </c>
-      <c r="U82" t="n">
-        <v>11</v>
-      </c>
-      <c r="V82" t="n">
-        <v>14</v>
-      </c>
-      <c r="W82" t="n">
-        <v>10</v>
-      </c>
-      <c r="X82" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Van Donge &amp; De Roo Stadion</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>Honingerdijk 110, Rotterdam</t>
-        </is>
-      </c>
-      <c r="AC82" t="n">
-        <v>0</v>
-      </c>
       <c r="AD82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE82" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AF82" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="AG82" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="AH82" t="n">
         <v>1.22</v>
       </c>
       <c r="AI82" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AJ82" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="AK82" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL82" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AM82" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AN82" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AO82" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AR82" t="n">
         <v>2.5</v>
       </c>
       <c r="AS82" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="AT82" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AU82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX82" t="n">
         <v>0</v>
       </c>
       <c r="AY82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA82" t="n">
         <v>1</v>
       </c>
       <c r="BB82" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -39308,28 +39336,28 @@
         <v>1</v>
       </c>
       <c r="BJ82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN82" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BO82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ82" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR82" t="n">
         <v>2</v>
@@ -39338,31 +39366,31 @@
         <v>1</v>
       </c>
       <c r="BT82" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="BW82" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="BX82" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="BY82" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="BZ82" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="CA82" t="n">
-        <v>1.47</v>
+        <v>0.73</v>
       </c>
       <c r="CB82" t="n">
-        <v>2.63</v>
+        <v>1.74</v>
       </c>
       <c r="CC82" t="n">
         <v>0</v>
@@ -39389,7 +39417,7 @@
         <v>1</v>
       </c>
       <c r="CK82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL82" t="n">
         <v>0</v>
@@ -39398,7 +39426,7 @@
         <v>0</v>
       </c>
       <c r="CN82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO82" t="n">
         <v>0</v>
@@ -39410,28 +39438,28 @@
         <v>1</v>
       </c>
       <c r="CR82" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="CS82" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="CT82" t="n">
         <v>1</v>
       </c>
       <c r="CU82" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="CV82" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY82" t="n">
         <v>10</v>
-      </c>
-      <c r="CW82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX82" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY82" t="n">
-        <v>8</v>
       </c>
       <c r="CZ82" t="n">
         <v>63</v>
@@ -39446,22 +39474,22 @@
         <v>75</v>
       </c>
       <c r="DD82" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE82" t="n">
         <v>1.29</v>
       </c>
-      <c r="DE82" t="n">
-        <v>0.57</v>
-      </c>
       <c r="DF82" t="n">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="DG82" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="DH82" t="n">
-        <v>0.75</v>
+        <v>1.88</v>
       </c>
       <c r="DI82" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="DJ82" t="n">
         <v>38</v>
@@ -39470,13 +39498,13 @@
         <v>25</v>
       </c>
       <c r="DL82" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="DM82" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.37</v>
+        <v>3.08</v>
       </c>
       <c r="DO82" t="n">
         <v>14</v>
@@ -39485,7 +39513,7 @@
         <v>1</v>
       </c>
       <c r="DQ82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR82" t="b">
         <v>0</v>
@@ -39502,102 +39530,74 @@
       <c r="DV82" t="b">
         <v>0</v>
       </c>
-      <c r="DW82" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="DX82" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="DY82" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="DZ82" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+      <c r="DW82" t="inlineStr"/>
+      <c r="DX82" t="inlineStr"/>
+      <c r="DY82" t="inlineStr"/>
+      <c r="DZ82" t="inlineStr"/>
       <c r="EA82" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="EB82" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EC82" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="ED82" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EF82" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EI82" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EJ82" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EK82" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EL82" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EM82" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="EN82" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EO82" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EP82" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr"/>
+      <c r="EN82" t="inlineStr"/>
+      <c r="EO82" t="inlineStr"/>
+      <c r="EP82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -40401,7 +40401,7 @@
         <v>2</v>
       </c>
       <c r="DE84" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DF84" t="n">
         <v>2.5</v>
@@ -48878,7 +48878,7 @@
         <v>80</v>
       </c>
       <c r="DD102" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE102" t="n">
         <v>0.5</v>
@@ -51209,7 +51209,7 @@
         <v>2.29</v>
       </c>
       <c r="DE107" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DF107" t="n">
         <v>2</v>
@@ -52747,12 +52747,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F111" s="2" t="n">
@@ -52762,134 +52762,134 @@
         <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J111" t="n">
+        <v>9</v>
+      </c>
+      <c r="K111" t="n">
+        <v>2</v>
+      </c>
+      <c r="L111" t="n">
+        <v>11</v>
+      </c>
+      <c r="M111" t="n">
+        <v>2</v>
+      </c>
+      <c r="N111" t="n">
+        <v>1</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>5</v>
+      </c>
+      <c r="R111" t="n">
         <v>4</v>
       </c>
-      <c r="K111" t="n">
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="n">
         <v>4</v>
       </c>
-      <c r="L111" t="n">
+      <c r="U111" t="n">
+        <v>15</v>
+      </c>
+      <c r="V111" t="n">
         <v>8</v>
       </c>
-      <c r="M111" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" t="n">
+      <c r="W111" t="n">
+        <v>4</v>
+      </c>
+      <c r="X111" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y111" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z111" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>Johan Cruijff Arena</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>ArenA Boulevard 1, Amsterdam</t>
+        </is>
+      </c>
+      <c r="AC111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD111" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE111" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF111" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AH111" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI111" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ111" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AK111" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL111" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM111" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AN111" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AP111" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ111" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR111" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS111" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT111" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AU111" t="n">
         <v>3</v>
       </c>
-      <c r="O111" t="n">
-        <v>0</v>
-      </c>
-      <c r="P111" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q111" t="n">
-        <v>4</v>
-      </c>
-      <c r="R111" t="n">
-        <v>6</v>
-      </c>
-      <c r="S111" t="n">
-        <v>7</v>
-      </c>
-      <c r="T111" t="n">
-        <v>12</v>
-      </c>
-      <c r="U111" t="n">
-        <v>11</v>
-      </c>
-      <c r="V111" t="n">
-        <v>18</v>
-      </c>
-      <c r="W111" t="n">
-        <v>5</v>
-      </c>
-      <c r="X111" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y111" t="n">
-        <v>52</v>
-      </c>
-      <c r="Z111" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA111" t="inlineStr">
-        <is>
-          <t>Kras Stadion</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>Sportlaan 10, Volendam</t>
-        </is>
-      </c>
-      <c r="AC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD111" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE111" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AF111" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG111" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH111" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI111" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AJ111" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AK111" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL111" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM111" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN111" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AO111" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AP111" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ111" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR111" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS111" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AT111" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AU111" t="n">
-        <v>2</v>
-      </c>
       <c r="AV111" t="n">
         <v>0</v>
       </c>
       <c r="AW111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX111" t="n">
         <v>1</v>
@@ -52901,16 +52901,16 @@
         <v>2</v>
       </c>
       <c r="BA111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB111" t="n">
-        <v>-1</v>
+        <v>374</v>
       </c>
       <c r="BC111" t="n">
         <v>0</v>
       </c>
       <c r="BD111" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="BE111" t="n">
         <v>0</v>
@@ -52925,7 +52925,7 @@
         <v>1</v>
       </c>
       <c r="BI111" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BJ111" t="n">
         <v>1</v>
@@ -52934,91 +52934,91 @@
         <v>4</v>
       </c>
       <c r="BL111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM111" t="n">
+        <v>6</v>
+      </c>
+      <c r="BN111" t="n">
+        <v>5</v>
+      </c>
+      <c r="BO111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR111" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS111" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU111" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV111" t="n">
+        <v>98</v>
+      </c>
+      <c r="BW111" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX111" t="n">
+        <v>141</v>
+      </c>
+      <c r="BY111" t="n">
+        <v>82</v>
+      </c>
+      <c r="BZ111" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CA111" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CB111" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="CC111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL111" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM111" t="n">
         <v>3</v>
       </c>
-      <c r="BM111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN111" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR111" t="n">
-        <v>3</v>
-      </c>
-      <c r="BS111" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT111" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU111" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV111" t="n">
-        <v>55</v>
-      </c>
-      <c r="BW111" t="n">
-        <v>60</v>
-      </c>
-      <c r="BX111" t="n">
-        <v>78</v>
-      </c>
-      <c r="BY111" t="n">
-        <v>73</v>
-      </c>
-      <c r="BZ111" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CA111" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CB111" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="CC111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL111" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM111" t="n">
-        <v>0</v>
-      </c>
       <c r="CN111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO111" t="n">
         <v>0</v>
@@ -53030,73 +53030,73 @@
         <v>1</v>
       </c>
       <c r="CR111" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="CS111" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT111" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU111" t="n">
         <v>13</v>
       </c>
-      <c r="CT111" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU111" t="n">
-        <v>12</v>
-      </c>
       <c r="CV111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CW111" t="n">
         <v>1</v>
       </c>
       <c r="CX111" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="CY111" t="n">
         <v>7</v>
       </c>
       <c r="CZ111" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="DA111" t="n">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="DB111" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC111" t="n">
+        <v>92</v>
+      </c>
+      <c r="DD111" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE111" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF111" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DG111" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH111" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DI111" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DJ111" t="n">
         <v>42</v>
       </c>
-      <c r="DC111" t="n">
-        <v>84</v>
-      </c>
-      <c r="DD111" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DE111" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="DF111" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="DG111" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DH111" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="DI111" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DJ111" t="n">
-        <v>34</v>
-      </c>
       <c r="DK111" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="DL111" t="n">
-        <v>1.4</v>
+        <v>1.82</v>
       </c>
       <c r="DM111" t="n">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="DN111" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="DO111" t="n">
         <v>14</v>
@@ -53108,7 +53108,7 @@
         <v>1</v>
       </c>
       <c r="DR111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS111" t="b">
         <v>0</v>
@@ -53123,14 +53123,14 @@
         <v>1</v>
       </c>
       <c r="DW111" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="DX111" t="n">
-        <v>7.73</v>
+        <v>5.17</v>
       </c>
       <c r="DY111" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="DZ111" t="inlineStr">
@@ -53140,65 +53140,65 @@
       </c>
       <c r="EA111" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="EB111" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="EC111" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="ED111" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE111" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="EF111" t="inlineStr"/>
       <c r="EG111" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EH111" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EI111" t="inlineStr"/>
       <c r="EJ111" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EK111" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EL111" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="EM111" t="inlineStr"/>
       <c r="EN111" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EO111" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP111" t="inlineStr"/>
@@ -53219,12 +53219,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F112" s="2" t="n">
@@ -53234,134 +53234,134 @@
         <v>1</v>
       </c>
       <c r="H112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I112" t="n">
+        <v>2</v>
+      </c>
+      <c r="J112" t="n">
+        <v>4</v>
+      </c>
+      <c r="K112" t="n">
+        <v>4</v>
+      </c>
+      <c r="L112" t="n">
+        <v>8</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="n">
         <v>3</v>
       </c>
-      <c r="J112" t="n">
-        <v>9</v>
-      </c>
-      <c r="K112" t="n">
-        <v>2</v>
-      </c>
-      <c r="L112" t="n">
+      <c r="O112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>4</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6</v>
+      </c>
+      <c r="S112" t="n">
+        <v>7</v>
+      </c>
+      <c r="T112" t="n">
+        <v>12</v>
+      </c>
+      <c r="U112" t="n">
         <v>11</v>
       </c>
-      <c r="M112" t="n">
-        <v>2</v>
-      </c>
-      <c r="N112" t="n">
-        <v>1</v>
-      </c>
-      <c r="O112" t="n">
-        <v>0</v>
-      </c>
-      <c r="P112" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q112" t="n">
+      <c r="V112" t="n">
+        <v>18</v>
+      </c>
+      <c r="W112" t="n">
         <v>5</v>
       </c>
-      <c r="R112" t="n">
+      <c r="X112" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y112" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z112" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>Kras Stadion</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>Sportlaan 10, Volendam</t>
+        </is>
+      </c>
+      <c r="AC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD112" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE112" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AF112" t="n">
         <v>4</v>
       </c>
-      <c r="S112" t="n">
-        <v>10</v>
-      </c>
-      <c r="T112" t="n">
-        <v>4</v>
-      </c>
-      <c r="U112" t="n">
-        <v>15</v>
-      </c>
-      <c r="V112" t="n">
-        <v>8</v>
-      </c>
-      <c r="W112" t="n">
-        <v>4</v>
-      </c>
-      <c r="X112" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y112" t="n">
-        <v>64</v>
-      </c>
-      <c r="Z112" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>Johan Cruijff Arena</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>ArenA Boulevard 1, Amsterdam</t>
-        </is>
-      </c>
-      <c r="AC112" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD112" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE112" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AF112" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AG112" t="n">
-        <v>7.4</v>
+        <v>1.62</v>
       </c>
       <c r="AH112" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AI112" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AJ112" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AK112" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL112" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AM112" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AN112" t="n">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AO112" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="AP112" t="n">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AR112" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AS112" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="AT112" t="n">
-        <v>1.76</v>
+        <v>1.54</v>
       </c>
       <c r="AU112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV112" t="n">
         <v>0</v>
       </c>
       <c r="AW112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX112" t="n">
         <v>1</v>
@@ -53373,16 +53373,16 @@
         <v>2</v>
       </c>
       <c r="BA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB112" t="n">
-        <v>374</v>
+        <v>-1</v>
       </c>
       <c r="BC112" t="n">
         <v>0</v>
       </c>
       <c r="BD112" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="BE112" t="n">
         <v>0</v>
@@ -53397,7 +53397,7 @@
         <v>1</v>
       </c>
       <c r="BI112" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BJ112" t="n">
         <v>1</v>
@@ -53406,169 +53406,169 @@
         <v>4</v>
       </c>
       <c r="BL112" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BM112" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BN112" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS112" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT112" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU112" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV112" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW112" t="n">
+        <v>60</v>
+      </c>
+      <c r="BX112" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY112" t="n">
+        <v>73</v>
+      </c>
+      <c r="BZ112" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CA112" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CB112" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="CC112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP112" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR112" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS112" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT112" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU112" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV112" t="n">
         <v>5</v>
       </c>
-      <c r="BO112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR112" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS112" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU112" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV112" t="n">
-        <v>98</v>
-      </c>
-      <c r="BW112" t="n">
-        <v>44</v>
-      </c>
-      <c r="BX112" t="n">
-        <v>141</v>
-      </c>
-      <c r="BY112" t="n">
-        <v>82</v>
-      </c>
-      <c r="BZ112" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CA112" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="CB112" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="CC112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM112" t="n">
-        <v>3</v>
-      </c>
-      <c r="CN112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP112" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR112" t="n">
-        <v>26</v>
-      </c>
-      <c r="CS112" t="n">
-        <v>11</v>
-      </c>
-      <c r="CT112" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU112" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV112" t="n">
-        <v>4</v>
-      </c>
       <c r="CW112" t="n">
         <v>1</v>
       </c>
       <c r="CX112" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="CY112" t="n">
         <v>7</v>
       </c>
       <c r="CZ112" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="DA112" t="n">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="DB112" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="DC112" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="DD112" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="DE112" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="DF112" t="n">
-        <v>2.17</v>
+        <v>1.83</v>
       </c>
       <c r="DG112" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="DH112" t="n">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="DI112" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="DJ112" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="DK112" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="DL112" t="n">
-        <v>1.82</v>
+        <v>1.4</v>
       </c>
       <c r="DM112" t="n">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="DN112" t="n">
-        <v>3.28</v>
+        <v>3.17</v>
       </c>
       <c r="DO112" t="n">
         <v>14</v>
@@ -53580,7 +53580,7 @@
         <v>1</v>
       </c>
       <c r="DR112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS112" t="b">
         <v>0</v>
@@ -53595,14 +53595,14 @@
         <v>1</v>
       </c>
       <c r="DW112" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="DX112" t="n">
-        <v>5.17</v>
+        <v>7.73</v>
       </c>
       <c r="DY112" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="DZ112" t="inlineStr">
@@ -53612,65 +53612,65 @@
       </c>
       <c r="EA112" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EB112" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="EC112" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="ED112" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EE112" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EF112" t="inlineStr"/>
       <c r="EG112" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="EH112" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EI112" t="inlineStr"/>
       <c r="EJ112" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EK112" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="EL112" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EM112" t="inlineStr"/>
       <c r="EN112" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EO112" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EP112" t="inlineStr"/>
@@ -53691,170 +53691,170 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
         <v>45983.83333333334</v>
       </c>
       <c r="G113" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J113" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K113" t="n">
+        <v>3</v>
+      </c>
+      <c r="L113" t="n">
+        <v>9</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1</v>
+      </c>
+      <c r="N113" t="n">
+        <v>2</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>12</v>
+      </c>
+      <c r="R113" t="n">
+        <v>3</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="n">
+        <v>2</v>
+      </c>
+      <c r="U113" t="n">
+        <v>22</v>
+      </c>
+      <c r="V113" t="n">
         <v>5</v>
       </c>
-      <c r="L113" t="n">
-        <v>12</v>
-      </c>
-      <c r="M113" t="n">
-        <v>1</v>
-      </c>
-      <c r="N113" t="n">
-        <v>1</v>
-      </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>4</v>
-      </c>
-      <c r="R113" t="n">
-        <v>7</v>
-      </c>
-      <c r="S113" t="n">
-        <v>9</v>
-      </c>
-      <c r="T113" t="n">
-        <v>5</v>
-      </c>
-      <c r="U113" t="n">
-        <v>13</v>
-      </c>
-      <c r="V113" t="n">
-        <v>12</v>
-      </c>
       <c r="W113" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="X113" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Y113" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="Z113" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Sparta-Stadion Het Kasteel</t>
+          <t>Polman Stadion</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>Spartapark Noord 1, Rotterdam</t>
+          <t>Stadionlaan 1, Almelo</t>
         </is>
       </c>
       <c r="AC113" t="n">
         <v>1</v>
       </c>
       <c r="AD113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.87</v>
+        <v>2.34</v>
       </c>
       <c r="AF113" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AG113" t="n">
-        <v>3.75</v>
+        <v>2.56</v>
       </c>
       <c r="AH113" t="n">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AI113" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AJ113" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="AK113" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL113" t="n">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="AM113" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AN113" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AO113" t="n">
-        <v>3.04</v>
+        <v>3.28</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.23</v>
+        <v>2.39</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AR113" t="n">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="AS113" t="n">
-        <v>2.89</v>
+        <v>3.6</v>
       </c>
       <c r="AT113" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AU113" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV113" t="n">
         <v>1</v>
       </c>
       <c r="AW113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AY113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA113" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BB113" t="n">
-        <v>-1</v>
+        <v>370</v>
       </c>
       <c r="BC113" t="n">
         <v>0</v>
       </c>
       <c r="BD113" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="BE113" t="n">
         <v>0</v>
@@ -53869,64 +53869,64 @@
         <v>1</v>
       </c>
       <c r="BI113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ113" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BL113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BM113" t="n">
         <v>4</v>
       </c>
       <c r="BN113" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BO113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP113" t="n">
         <v>1</v>
       </c>
       <c r="BQ113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU113" t="n">
         <v>1</v>
       </c>
       <c r="BV113" t="n">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="BW113" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="BX113" t="n">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="BY113" t="n">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="BZ113" t="n">
-        <v>1.58</v>
+        <v>2.57</v>
       </c>
       <c r="CA113" t="n">
-        <v>1.51</v>
+        <v>0.84</v>
       </c>
       <c r="CB113" t="n">
-        <v>3.09</v>
+        <v>3.41</v>
       </c>
       <c r="CC113" t="n">
         <v>0</v>
@@ -53953,7 +53953,7 @@
         <v>1</v>
       </c>
       <c r="CK113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL113" t="n">
         <v>0</v>
@@ -53974,73 +53974,73 @@
         <v>1</v>
       </c>
       <c r="CR113" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CS113" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CT113" t="n">
         <v>1</v>
       </c>
       <c r="CU113" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CV113" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="CW113" t="n">
         <v>1</v>
       </c>
       <c r="CX113" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY113" t="n">
         <v>5</v>
       </c>
-      <c r="CY113" t="n">
-        <v>7</v>
-      </c>
       <c r="CZ113" t="n">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="DA113" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="DB113" t="n">
-        <v>33</v>
+        <v>65</v>
       </c>
       <c r="DC113" t="n">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="DD113" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="DE113" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
       <c r="DF113" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="DG113" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="DH113" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DI113" t="n">
         <v>1.33</v>
       </c>
       <c r="DJ113" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="DK113" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="DL113" t="n">
-        <v>1.27</v>
+        <v>1.61</v>
       </c>
       <c r="DM113" t="n">
-        <v>1.11</v>
+        <v>1.28</v>
       </c>
       <c r="DN113" t="n">
-        <v>2.38</v>
+        <v>2.89</v>
       </c>
       <c r="DO113" t="n">
         <v>14</v>
@@ -54052,89 +54052,97 @@
         <v>1</v>
       </c>
       <c r="DR113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV113" t="b">
         <v>1</v>
       </c>
       <c r="DW113" t="n">
-        <v>4.46</v>
+        <v>2.78</v>
       </c>
       <c r="DX113" t="n">
-        <v>5.47</v>
+        <v>6.56</v>
       </c>
       <c r="DY113" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="DZ113" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="EA113" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EB113" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="EC113" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="ED113" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EE113" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EF113" t="inlineStr"/>
-      <c r="EG113" t="inlineStr"/>
-      <c r="EH113" t="inlineStr"/>
+      <c r="EG113" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EH113" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
       <c r="EI113" t="inlineStr"/>
       <c r="EJ113" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EK113" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EL113" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="EM113" t="inlineStr"/>
       <c r="EN113" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EO113" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EP113" t="inlineStr"/>
@@ -54155,170 +54163,170 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F114" s="2" t="n">
         <v>45983.83333333334</v>
       </c>
       <c r="G114" t="n">
+        <v>1</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" t="n">
+        <v>2</v>
+      </c>
+      <c r="J114" t="n">
+        <v>7</v>
+      </c>
+      <c r="K114" t="n">
+        <v>5</v>
+      </c>
+      <c r="L114" t="n">
+        <v>12</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1</v>
+      </c>
+      <c r="N114" t="n">
+        <v>1</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
         <v>4</v>
       </c>
-      <c r="H114" t="n">
-        <v>2</v>
-      </c>
-      <c r="I114" t="n">
-        <v>6</v>
-      </c>
-      <c r="J114" t="n">
-        <v>6</v>
-      </c>
-      <c r="K114" t="n">
-        <v>3</v>
-      </c>
-      <c r="L114" t="n">
+      <c r="R114" t="n">
+        <v>7</v>
+      </c>
+      <c r="S114" t="n">
         <v>9</v>
       </c>
-      <c r="M114" t="n">
-        <v>1</v>
-      </c>
-      <c r="N114" t="n">
-        <v>2</v>
-      </c>
-      <c r="O114" t="n">
-        <v>0</v>
-      </c>
-      <c r="P114" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q114" t="n">
+      <c r="T114" t="n">
+        <v>5</v>
+      </c>
+      <c r="U114" t="n">
+        <v>13</v>
+      </c>
+      <c r="V114" t="n">
         <v>12</v>
       </c>
-      <c r="R114" t="n">
-        <v>3</v>
-      </c>
-      <c r="S114" t="n">
-        <v>10</v>
-      </c>
-      <c r="T114" t="n">
-        <v>2</v>
-      </c>
-      <c r="U114" t="n">
-        <v>22</v>
-      </c>
-      <c r="V114" t="n">
-        <v>5</v>
-      </c>
       <c r="W114" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="X114" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y114" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="Z114" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Polman Stadion</t>
+          <t>Sparta-Stadion Het Kasteel</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>Stadionlaan 1, Almelo</t>
+          <t>Spartapark Noord 1, Rotterdam</t>
         </is>
       </c>
       <c r="AC114" t="n">
         <v>1</v>
       </c>
       <c r="AD114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE114" t="n">
-        <v>2.34</v>
+        <v>1.87</v>
       </c>
       <c r="AF114" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AG114" t="n">
-        <v>2.56</v>
+        <v>3.75</v>
       </c>
       <c r="AH114" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AI114" t="n">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AJ114" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="AK114" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AL114" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AM114" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN114" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AP114" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AQ114" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR114" t="n">
         <v>2.62</v>
       </c>
-      <c r="AM114" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN114" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO114" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AP114" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AQ114" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AR114" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AS114" t="n">
-        <v>3.6</v>
+        <v>2.89</v>
       </c>
       <c r="AT114" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AU114" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV114" t="n">
         <v>1</v>
       </c>
       <c r="AW114" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX114" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AY114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB114" t="n">
-        <v>370</v>
+        <v>-1</v>
       </c>
       <c r="BC114" t="n">
         <v>0</v>
       </c>
       <c r="BD114" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="BE114" t="n">
         <v>0</v>
@@ -54333,178 +54341,178 @@
         <v>1</v>
       </c>
       <c r="BI114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ114" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK114" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL114" t="n">
         <v>3</v>
-      </c>
-      <c r="BJ114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK114" t="n">
-        <v>3</v>
-      </c>
-      <c r="BL114" t="n">
-        <v>2</v>
       </c>
       <c r="BM114" t="n">
         <v>4</v>
       </c>
       <c r="BN114" t="n">
+        <v>8</v>
+      </c>
+      <c r="BO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR114" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU114" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV114" t="n">
+        <v>64</v>
+      </c>
+      <c r="BW114" t="n">
+        <v>35</v>
+      </c>
+      <c r="BX114" t="n">
+        <v>149</v>
+      </c>
+      <c r="BY114" t="n">
+        <v>102</v>
+      </c>
+      <c r="BZ114" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CA114" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CB114" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP114" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR114" t="n">
+        <v>12</v>
+      </c>
+      <c r="CS114" t="n">
+        <v>23</v>
+      </c>
+      <c r="CT114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU114" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV114" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW114" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX114" t="n">
         <v>5</v>
       </c>
-      <c r="BO114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ114" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR114" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS114" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT114" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU114" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV114" t="n">
-        <v>48</v>
-      </c>
-      <c r="BW114" t="n">
-        <v>41</v>
-      </c>
-      <c r="BX114" t="n">
-        <v>86</v>
-      </c>
-      <c r="BY114" t="n">
-        <v>118</v>
-      </c>
-      <c r="BZ114" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="CA114" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="CB114" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="CC114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP114" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR114" t="n">
-        <v>14</v>
-      </c>
-      <c r="CS114" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU114" t="n">
-        <v>15</v>
-      </c>
-      <c r="CV114" t="n">
-        <v>6</v>
-      </c>
-      <c r="CW114" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX114" t="n">
-        <v>2</v>
-      </c>
       <c r="CY114" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CZ114" t="n">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="DA114" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB114" t="n">
+        <v>33</v>
+      </c>
+      <c r="DC114" t="n">
         <v>92</v>
       </c>
-      <c r="DB114" t="n">
-        <v>65</v>
-      </c>
-      <c r="DC114" t="n">
-        <v>84</v>
-      </c>
       <c r="DD114" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="DE114" t="n">
-        <v>0.71</v>
+        <v>0.57</v>
       </c>
       <c r="DF114" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DG114" t="n">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="DH114" t="n">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="DI114" t="n">
         <v>1.33</v>
       </c>
       <c r="DJ114" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="DK114" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="DL114" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="DM114" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="DN114" t="n">
-        <v>2.89</v>
+        <v>2.38</v>
       </c>
       <c r="DO114" t="n">
         <v>14</v>
@@ -54516,97 +54524,89 @@
         <v>1</v>
       </c>
       <c r="DR114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU114" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV114" t="b">
         <v>1</v>
       </c>
       <c r="DW114" t="n">
-        <v>2.78</v>
+        <v>4.46</v>
       </c>
       <c r="DX114" t="n">
-        <v>6.56</v>
+        <v>5.47</v>
       </c>
       <c r="DY114" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ114" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA114" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="EB114" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.57</t>
         </is>
       </c>
       <c r="EC114" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="ED114" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EE114" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EF114" t="inlineStr"/>
-      <c r="EG114" t="inlineStr">
-        <is>
-          <t>2.44</t>
-        </is>
-      </c>
-      <c r="EH114" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
+      <c r="EG114" t="inlineStr"/>
+      <c r="EH114" t="inlineStr"/>
       <c r="EI114" t="inlineStr"/>
       <c r="EJ114" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EK114" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EL114" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="EM114" t="inlineStr"/>
       <c r="EN114" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EO114" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EP114" t="inlineStr"/>
@@ -55099,162 +55099,170 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
         <v>45984.5625</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K116" t="n">
+        <v>6</v>
+      </c>
+      <c r="L116" t="n">
+        <v>13</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>5</v>
+      </c>
+      <c r="R116" t="n">
+        <v>12</v>
+      </c>
+      <c r="S116" t="n">
+        <v>14</v>
+      </c>
+      <c r="T116" t="n">
+        <v>10</v>
+      </c>
+      <c r="U116" t="n">
+        <v>19</v>
+      </c>
+      <c r="V116" t="n">
+        <v>22</v>
+      </c>
+      <c r="W116" t="n">
         <v>8</v>
       </c>
-      <c r="L116" t="n">
-        <v>9</v>
-      </c>
-      <c r="M116" t="n">
-        <v>2</v>
-      </c>
-      <c r="N116" t="n">
-        <v>2</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>3</v>
-      </c>
-      <c r="R116" t="n">
-        <v>3</v>
-      </c>
-      <c r="S116" t="n">
-        <v>7</v>
-      </c>
-      <c r="T116" t="n">
-        <v>14</v>
-      </c>
-      <c r="U116" t="n">
-        <v>10</v>
-      </c>
-      <c r="V116" t="n">
-        <v>17</v>
-      </c>
-      <c r="W116" t="n">
-        <v>10</v>
-      </c>
       <c r="X116" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y116" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Z116" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA116" t="inlineStr"/>
-      <c r="AB116" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Stadion Feijenoord</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>Van Zandvlietplein 1, Rotterdam</t>
+        </is>
+      </c>
       <c r="AC116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE116" t="n">
-        <v>3.35</v>
+        <v>1.43</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.58</v>
+        <v>5.2</v>
       </c>
       <c r="AG116" t="n">
-        <v>2.11</v>
+        <v>6.8</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AI116" t="n">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AJ116" t="n">
-        <v>2.71</v>
+        <v>2</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL116" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AM116" t="n">
         <v>1.4</v>
       </c>
       <c r="AN116" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AR116" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AS116" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AU116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX116" t="n">
         <v>1</v>
       </c>
       <c r="AY116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB116" t="n">
-        <v>-1</v>
+        <v>379</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -55269,178 +55277,178 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BK116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BM116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN116" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
         <v>4</v>
       </c>
-      <c r="BO116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR116" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT116" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV116" t="n">
-        <v>33</v>
-      </c>
-      <c r="BW116" t="n">
-        <v>60</v>
-      </c>
-      <c r="BX116" t="n">
-        <v>91</v>
-      </c>
-      <c r="BY116" t="n">
-        <v>123</v>
-      </c>
-      <c r="BZ116" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="CA116" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CB116" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN116" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR116" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS116" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU116" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV116" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX116" t="n">
-        <v>10</v>
-      </c>
       <c r="CY116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ116" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="DA116" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="DB116" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="DC116" t="n">
         <v>100</v>
       </c>
       <c r="DD116" t="n">
-        <v>0.75</v>
+        <v>2.14</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.71</v>
+        <v>1.14</v>
       </c>
       <c r="DF116" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG116" t="n">
         <v>0.83</v>
       </c>
-      <c r="DG116" t="n">
-        <v>0.6</v>
-      </c>
       <c r="DH116" t="n">
-        <v>0.75</v>
+        <v>2.33</v>
       </c>
       <c r="DI116" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="DJ116" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="DK116" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="DM116" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="DN116" t="n">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="DO116" t="n">
         <v>14</v>
@@ -55452,29 +55460,29 @@
         <v>1</v>
       </c>
       <c r="DR116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV116" t="b">
         <v>1</v>
       </c>
       <c r="DW116" t="n">
-        <v>4.06</v>
+        <v>3.47</v>
       </c>
       <c r="DX116" t="n">
-        <v>9.84</v>
+        <v>7.56</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
@@ -55484,73 +55492,65 @@
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="EC116" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="ED116" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE116" t="inlineStr">
         <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EF116" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr"/>
       <c r="EG116" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EH116" t="inlineStr">
         <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EI116" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EI116" t="inlineStr"/>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EK116" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EL116" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="EM116" t="inlineStr"/>
       <c r="EN116" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EO116" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EP116" t="inlineStr"/>
@@ -55571,170 +55571,162 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F117" s="2" t="n">
         <v>45984.5625</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>8</v>
+      </c>
+      <c r="L117" t="n">
+        <v>9</v>
+      </c>
+      <c r="M117" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>2</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>3</v>
+      </c>
+      <c r="R117" t="n">
+        <v>3</v>
+      </c>
+      <c r="S117" t="n">
         <v>7</v>
       </c>
-      <c r="K117" t="n">
-        <v>6</v>
-      </c>
-      <c r="L117" t="n">
-        <v>13</v>
-      </c>
-      <c r="M117" t="n">
-        <v>1</v>
-      </c>
-      <c r="N117" t="n">
-        <v>1</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>5</v>
-      </c>
-      <c r="R117" t="n">
-        <v>12</v>
-      </c>
-      <c r="S117" t="n">
+      <c r="T117" t="n">
         <v>14</v>
       </c>
-      <c r="T117" t="n">
+      <c r="U117" t="n">
         <v>10</v>
       </c>
-      <c r="U117" t="n">
-        <v>19</v>
-      </c>
       <c r="V117" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="W117" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X117" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y117" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="Z117" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>Stadion Feijenoord</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>Van Zandvlietplein 1, Rotterdam</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.43</v>
+        <v>3.35</v>
       </c>
       <c r="AF117" t="n">
-        <v>5.2</v>
+        <v>3.58</v>
       </c>
       <c r="AG117" t="n">
-        <v>6.8</v>
+        <v>2.11</v>
       </c>
       <c r="AH117" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AI117" t="n">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AJ117" t="n">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="AK117" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL117" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AM117" t="n">
         <v>1.4</v>
       </c>
       <c r="AN117" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AO117" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AS117" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AT117" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="AU117" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX117" t="n">
         <v>1</v>
       </c>
       <c r="AY117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB117" t="n">
-        <v>379</v>
+        <v>-1</v>
       </c>
       <c r="BC117" t="n">
         <v>0</v>
       </c>
       <c r="BD117" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="BE117" t="n">
         <v>0</v>
@@ -55749,64 +55741,64 @@
         <v>1</v>
       </c>
       <c r="BI117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN117" t="n">
         <v>4</v>
       </c>
-      <c r="BJ117" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK117" t="n">
+      <c r="BO117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT117" t="n">
         <v>3</v>
       </c>
-      <c r="BL117" t="n">
-        <v>4</v>
-      </c>
-      <c r="BM117" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN117" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ117" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR117" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT117" t="n">
-        <v>2</v>
-      </c>
       <c r="BU117" t="n">
         <v>1</v>
       </c>
       <c r="BV117" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="BW117" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="BX117" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="BY117" t="n">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="BZ117" t="n">
-        <v>1.92</v>
+        <v>1.09</v>
       </c>
       <c r="CA117" t="n">
-        <v>2.42</v>
+        <v>1.72</v>
       </c>
       <c r="CB117" t="n">
-        <v>4.34</v>
+        <v>2.81</v>
       </c>
       <c r="CC117" t="n">
         <v>0</v>
@@ -55839,13 +55831,13 @@
         <v>0</v>
       </c>
       <c r="CM117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP117" t="n">
         <v>0</v>
@@ -55854,73 +55846,73 @@
         <v>1</v>
       </c>
       <c r="CR117" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CS117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT117" t="n">
         <v>1</v>
       </c>
       <c r="CU117" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CV117" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CW117" t="n">
         <v>1</v>
       </c>
       <c r="CX117" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="CY117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ117" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="DA117" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="DB117" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="DC117" t="n">
         <v>100</v>
       </c>
       <c r="DD117" t="n">
-        <v>2.14</v>
+        <v>0.75</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.14</v>
+        <v>0.71</v>
       </c>
       <c r="DF117" t="n">
-        <v>2.5</v>
+        <v>0.83</v>
       </c>
       <c r="DG117" t="n">
-        <v>0.83</v>
+        <v>0.6</v>
       </c>
       <c r="DH117" t="n">
-        <v>2.33</v>
+        <v>0.75</v>
       </c>
       <c r="DI117" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="DJ117" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="DK117" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="DL117" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="DM117" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="DN117" t="n">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="DO117" t="n">
         <v>14</v>
@@ -55932,29 +55924,29 @@
         <v>1</v>
       </c>
       <c r="DR117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV117" t="b">
         <v>1</v>
       </c>
       <c r="DW117" t="n">
-        <v>3.47</v>
+        <v>4.06</v>
       </c>
       <c r="DX117" t="n">
-        <v>7.56</v>
+        <v>9.84</v>
       </c>
       <c r="DY117" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="DZ117" t="inlineStr">
@@ -55964,65 +55956,73 @@
       </c>
       <c r="EA117" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EB117" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="EC117" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="ED117" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EE117" t="inlineStr">
         <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="EF117" t="inlineStr"/>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EF117" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
       <c r="EG117" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EH117" t="inlineStr">
         <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EI117" t="inlineStr"/>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EI117" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="EJ117" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EK117" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EL117" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EM117" t="inlineStr"/>
       <c r="EN117" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EO117" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP117" t="inlineStr"/>
@@ -57322,7 +57322,7 @@
         <v>84</v>
       </c>
       <c r="DD120" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="DE120" t="n">
         <v>0.29</v>
@@ -60341,10 +60341,10 @@
         <v>10</v>
       </c>
       <c r="Y127" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z127" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
@@ -60597,7 +60597,7 @@
         <v>2</v>
       </c>
       <c r="DE127" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="DF127" t="n">
         <v>1.86</v>
@@ -60719,6 +60719,494 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Netherlands_Eredivisie_2025-2026</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>15</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Groningen</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>45996.79166666666</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>2</v>
+      </c>
+      <c r="I128" t="n">
+        <v>2</v>
+      </c>
+      <c r="J128" t="n">
+        <v>5</v>
+      </c>
+      <c r="K128" t="n">
+        <v>5</v>
+      </c>
+      <c r="L128" t="n">
+        <v>10</v>
+      </c>
+      <c r="M128" t="n">
+        <v>2</v>
+      </c>
+      <c r="N128" t="n">
+        <v>2</v>
+      </c>
+      <c r="O128" t="n">
+        <v>1</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>6</v>
+      </c>
+      <c r="R128" t="n">
+        <v>8</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="n">
+        <v>12</v>
+      </c>
+      <c r="U128" t="n">
+        <v>16</v>
+      </c>
+      <c r="V128" t="n">
+        <v>20</v>
+      </c>
+      <c r="W128" t="n">
+        <v>10</v>
+      </c>
+      <c r="X128" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>Van Donge &amp; De Roo Stadion</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>Honingerdijk 110, Rotterdam</t>
+        </is>
+      </c>
+      <c r="AC128" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>372</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>22</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>46</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>95</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>11</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU128" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV128" t="n">
+        <v>9</v>
+      </c>
+      <c r="CW128" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX128" t="n">
+        <v>11</v>
+      </c>
+      <c r="CY128" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ128" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA128" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB128" t="n">
+        <v>29</v>
+      </c>
+      <c r="DC128" t="n">
+        <v>71</v>
+      </c>
+      <c r="DD128" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE128" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF128" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DG128" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="DH128" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="DI128" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DJ128" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK128" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL128" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DM128" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DN128" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DO128" t="n">
+        <v>15</v>
+      </c>
+      <c r="DP128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ128" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV128" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW128" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="DX128" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="DY128" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="DZ128" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="EA128" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EB128" t="inlineStr">
+        <is>
+          <t>3.52</t>
+        </is>
+      </c>
+      <c r="EC128" t="inlineStr">
+        <is>
+          <t>3.73</t>
+        </is>
+      </c>
+      <c r="ED128" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EE128" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EF128" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EG128" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EH128" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EI128" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="EJ128" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EK128" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
+      <c r="EL128" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EM128" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EN128" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EO128" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EP128" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -61743,13 +61743,13 @@
         <v>4</v>
       </c>
       <c r="S130" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T130" t="n">
         <v>9</v>
       </c>
       <c r="U130" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="V130" t="n">
         <v>13</v>
@@ -61924,13 +61924,13 @@
         <v>109</v>
       </c>
       <c r="BZ130" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="CA130" t="n">
         <v>1.45</v>
       </c>
       <c r="CB130" t="n">
-        <v>3.86</v>
+        <v>3.92</v>
       </c>
       <c r="CC130" t="n">
         <v>0</v>
@@ -63167,16 +63167,16 @@
         <v>6</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T133" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U133" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="V133" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W133" t="n">
         <v>8</v>
@@ -63348,10 +63348,10 @@
         <v>111</v>
       </c>
       <c r="BZ133" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="CA133" t="n">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="CB133" t="n">
         <v>3.36</v>
@@ -63658,13 +63658,13 @@
         <v>16</v>
       </c>
       <c r="T134" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U134" t="n">
         <v>23</v>
       </c>
       <c r="V134" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="W134" t="n">
         <v>8</v>
@@ -63673,10 +63673,10 @@
         <v>8</v>
       </c>
       <c r="Y134" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z134" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
@@ -63839,10 +63839,10 @@
         <v>2.29</v>
       </c>
       <c r="CA134" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="CB134" t="n">
-        <v>3.71</v>
+        <v>3.77</v>
       </c>
       <c r="CC134" t="n">
         <v>0</v>
@@ -63890,10 +63890,10 @@
         <v>1</v>
       </c>
       <c r="CR134" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CS134" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CT134" t="n">
         <v>1</v>
@@ -64837,7 +64837,7 @@
         <v>18</v>
       </c>
       <c r="CS136" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT136" t="n">
         <v>1</v>

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -65097,10 +65097,10 @@
         <v>11</v>
       </c>
       <c r="Y137" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z137" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AA137" t="inlineStr"/>
       <c r="AB137" t="inlineStr"/>
@@ -66001,13 +66001,13 @@
         <v>0</v>
       </c>
       <c r="Q139" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R139" t="n">
         <v>6</v>
       </c>
       <c r="S139" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="T139" t="n">
         <v>5</v>
@@ -66188,13 +66188,13 @@
         <v>77</v>
       </c>
       <c r="BZ139" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="CA139" t="n">
         <v>1.26</v>
       </c>
       <c r="CB139" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="CC139" t="n">
         <v>2</v>
@@ -66957,10 +66957,10 @@
         <v>15</v>
       </c>
       <c r="Y141" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Z141" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
@@ -67649,7 +67649,7 @@
         <v>21</v>
       </c>
       <c r="CS142" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="CT142" t="n">
         <v>1</v>
@@ -67667,7 +67667,7 @@
         <v>4</v>
       </c>
       <c r="CY142" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CZ142" t="n">
         <v>66</v>

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -69761,7 +69761,7 @@
         <v>0</v>
       </c>
       <c r="Q147" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R147" t="n">
         <v>8</v>
@@ -69773,7 +69773,7 @@
         <v>11</v>
       </c>
       <c r="U147" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="V147" t="n">
         <v>19</v>
@@ -69940,13 +69940,13 @@
         <v>88</v>
       </c>
       <c r="BZ147" t="n">
-        <v>1.76</v>
+        <v>1.62</v>
       </c>
       <c r="CA147" t="n">
         <v>2.2</v>
       </c>
       <c r="CB147" t="n">
-        <v>3.95</v>
+        <v>3.82</v>
       </c>
       <c r="CC147" t="n">
         <v>0</v>
@@ -70237,10 +70237,10 @@
         <v>16</v>
       </c>
       <c r="Y148" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Z148" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
@@ -70693,7 +70693,7 @@
         <v>1</v>
       </c>
       <c r="Q149" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R149" t="n">
         <v>8</v>
@@ -70705,7 +70705,7 @@
         <v>6</v>
       </c>
       <c r="U149" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="V149" t="n">
         <v>14</v>
@@ -70880,13 +70880,13 @@
         <v>93</v>
       </c>
       <c r="BZ149" t="n">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="CA149" t="n">
         <v>1.88</v>
       </c>
       <c r="CB149" t="n">
-        <v>3.43</v>
+        <v>3.56</v>
       </c>
       <c r="CC149" t="n">
         <v>0</v>
@@ -71044,38 +71044,38 @@
       </c>
       <c r="EA149" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="EB149" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="EC149" t="inlineStr">
         <is>
-          <t>4.47</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="ED149" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EE149" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="EF149" t="inlineStr"/>
       <c r="EG149" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EH149" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EI149" t="inlineStr"/>
@@ -71496,74 +71496,74 @@
       </c>
       <c r="EA150" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EB150" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="EC150" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="ED150" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EE150" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EF150" t="inlineStr"/>
       <c r="EG150" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EH150" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EI150" t="inlineStr"/>
       <c r="EJ150" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK150" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EL150" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="EM150" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="EN150" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EO150" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="EP150" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.46</t>
         </is>
       </c>
     </row>
@@ -71616,7 +71616,7 @@
         <v>2</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -71668,7 +71668,7 @@
         <v>2</v>
       </c>
       <c r="AD151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE151" t="n">
         <v>3.02</v>
@@ -71782,7 +71782,7 @@
         <v>0</v>
       </c>
       <c r="BP151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ151" t="n">
         <v>2</v>
@@ -71791,7 +71791,7 @@
         <v>0</v>
       </c>
       <c r="BS151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT151" t="n">
         <v>2</v>
@@ -71976,41 +71976,49 @@
       </c>
       <c r="EA151" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EB151" t="inlineStr">
         <is>
-          <t>3.62</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EC151" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="ED151" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EE151" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EF151" t="inlineStr"/>
-      <c r="EG151" t="inlineStr"/>
-      <c r="EH151" t="inlineStr"/>
+      <c r="EG151" t="inlineStr">
+        <is>
+          <t>2.64</t>
+        </is>
+      </c>
+      <c r="EH151" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
       <c r="EI151" t="inlineStr"/>
       <c r="EJ151" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EK151" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EL151" t="inlineStr">
@@ -72019,16 +72027,8 @@
         </is>
       </c>
       <c r="EM151" t="inlineStr"/>
-      <c r="EN151" t="inlineStr">
-        <is>
-          <t>1.68</t>
-        </is>
-      </c>
-      <c r="EO151" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
+      <c r="EN151" t="inlineStr"/>
+      <c r="EO151" t="inlineStr"/>
       <c r="EP151" t="inlineStr"/>
     </row>
     <row r="152">
@@ -72440,17 +72440,17 @@
       </c>
       <c r="EA152" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EB152" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="EC152" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="ED152" t="inlineStr">
@@ -72477,39 +72477,23 @@
       <c r="EI152" t="inlineStr"/>
       <c r="EJ152" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EK152" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EL152" t="inlineStr">
         <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="EM152" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="EN152" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EO152" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EP152" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EM152" t="inlineStr"/>
+      <c r="EN152" t="inlineStr"/>
+      <c r="EO152" t="inlineStr"/>
+      <c r="EP152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -72593,10 +72577,10 @@
         <v>6</v>
       </c>
       <c r="Y153" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Z153" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
@@ -72920,65 +72904,65 @@
       </c>
       <c r="EA153" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EB153" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="EC153" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="ED153" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EE153" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EF153" t="inlineStr"/>
       <c r="EG153" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EH153" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EI153" t="inlineStr"/>
       <c r="EJ153" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK153" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="EL153" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="EM153" t="inlineStr"/>
       <c r="EN153" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="EO153" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="EP153" t="inlineStr"/>

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -27961,7 +27961,7 @@
         <v>8</v>
       </c>
       <c r="M58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N58" t="n">
         <v>3</v>
@@ -28013,7 +28013,7 @@
         </is>
       </c>
       <c r="AC58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD58" t="n">
         <v>3</v>
@@ -28133,7 +28133,7 @@
         <v>1</v>
       </c>
       <c r="BQ58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR58" t="n">
         <v>2</v>
@@ -28142,7 +28142,7 @@
         <v>1</v>
       </c>
       <c r="BT58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BU58" t="n">
         <v>1</v>
@@ -28946,8 +28946,16 @@
       <c r="Z60" t="n">
         <v>52</v>
       </c>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>Polman Stadion</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>Stadionlaan 1, Almelo</t>
+        </is>
+      </c>
       <c r="AC60" t="n">
         <v>2</v>
       </c>
@@ -35443,40 +35451,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45948.60416666666</v>
+        <v>45948.61458333334</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K74" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L74" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -35485,10 +35493,10 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="S74" t="n">
         <v>4</v>
@@ -35497,108 +35505,108 @@
         <v>7</v>
       </c>
       <c r="U74" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="V74" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="W74" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X74" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="Y74" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="Z74" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="AA74" t="inlineStr"/>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE74" t="n">
-        <v>7.25</v>
+        <v>2.37</v>
       </c>
       <c r="AF74" t="n">
-        <v>5.1</v>
+        <v>3.74</v>
       </c>
       <c r="AG74" t="n">
-        <v>1.35</v>
+        <v>2.71</v>
       </c>
       <c r="AH74" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AI74" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM74" t="n">
         <v>1.41</v>
       </c>
-      <c r="AJ74" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AK74" t="n">
+      <c r="AN74" t="n">
         <v>1.7</v>
       </c>
-      <c r="AL74" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AM74" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN74" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AO74" t="n">
-        <v>2.9</v>
+        <v>2.56</v>
       </c>
       <c r="AP74" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AR74" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AS74" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AT74" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AU74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW74" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY74" t="n">
+        <v>2</v>
+      </c>
+      <c r="AZ74" t="n">
         <v>4</v>
       </c>
-      <c r="AX74" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY74" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ74" t="n">
-        <v>3</v>
-      </c>
       <c r="BA74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB74" t="n">
-        <v>367</v>
+        <v>-1</v>
       </c>
       <c r="BC74" t="n">
         <v>0</v>
       </c>
       <c r="BD74" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="BE74" t="n">
         <v>0</v>
@@ -35616,73 +35624,73 @@
         <v>1</v>
       </c>
       <c r="BJ74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK74" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM74" t="n">
         <v>3</v>
       </c>
-      <c r="BK74" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL74" t="n">
-        <v>5</v>
-      </c>
-      <c r="BM74" t="n">
+      <c r="BN74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP74" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR74" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS74" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT74" t="n">
         <v>4</v>
       </c>
-      <c r="BN74" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO74" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP74" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ74" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR74" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS74" t="n">
-        <v>3</v>
-      </c>
-      <c r="BT74" t="n">
-        <v>0</v>
-      </c>
       <c r="BU74" t="n">
         <v>1</v>
       </c>
       <c r="BV74" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BW74" t="n">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="BX74" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="BY74" t="n">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="BZ74" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="CA74" t="n">
-        <v>2.5</v>
+        <v>1.07</v>
       </c>
       <c r="CB74" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="CC74" t="n">
         <v>0</v>
       </c>
       <c r="CD74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CE74" t="n">
         <v>0</v>
       </c>
       <c r="CF74" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CG74" t="n">
         <v>0</v>
@@ -35700,7 +35708,7 @@
         <v>0</v>
       </c>
       <c r="CL74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM74" t="n">
         <v>0</v>
@@ -35709,7 +35717,7 @@
         <v>0</v>
       </c>
       <c r="CO74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP74" t="n">
         <v>0</v>
@@ -35718,73 +35726,73 @@
         <v>1</v>
       </c>
       <c r="CR74" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CS74" t="n">
+        <v>26</v>
+      </c>
+      <c r="CT74" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU74" t="n">
         <v>21</v>
       </c>
-      <c r="CT74" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU74" t="n">
+      <c r="CV74" t="n">
         <v>13</v>
       </c>
-      <c r="CV74" t="n">
-        <v>11</v>
-      </c>
       <c r="CW74" t="n">
         <v>1</v>
       </c>
       <c r="CX74" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="CY74" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CZ74" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="DA74" t="n">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="DB74" t="n">
-        <v>59</v>
+        <v>25</v>
       </c>
       <c r="DC74" t="n">
         <v>88</v>
       </c>
       <c r="DD74" t="n">
-        <v>1.25</v>
+        <v>2.13</v>
       </c>
       <c r="DE74" t="n">
-        <v>2</v>
+        <v>1.22</v>
       </c>
       <c r="DF74" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="DG74" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="DH74" t="n">
-        <v>0.38</v>
+        <v>1.63</v>
       </c>
       <c r="DI74" t="n">
-        <v>2.75</v>
+        <v>1.63</v>
       </c>
       <c r="DJ74" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="DK74" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="DL74" t="n">
-        <v>1.64</v>
+        <v>1.96</v>
       </c>
       <c r="DM74" t="n">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="DN74" t="n">
-        <v>3.6</v>
+        <v>4.04</v>
       </c>
       <c r="DO74" t="n">
         <v>17</v>
@@ -35808,74 +35816,54 @@
         <v>1</v>
       </c>
       <c r="DV74" t="b">
-        <v>0</v>
-      </c>
-      <c r="DW74" t="n">
-        <v>12.24</v>
-      </c>
-      <c r="DX74" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="DY74" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="DZ74" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="DW74" t="inlineStr"/>
+      <c r="DX74" t="inlineStr"/>
+      <c r="DY74" t="inlineStr"/>
+      <c r="DZ74" t="inlineStr"/>
       <c r="EA74" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="EB74" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="EC74" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="ED74" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EE74" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EF74" t="inlineStr"/>
-      <c r="EG74" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EH74" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
+      <c r="EG74" t="inlineStr"/>
+      <c r="EH74" t="inlineStr"/>
       <c r="EI74" t="inlineStr"/>
       <c r="EJ74" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EK74" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="EL74" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EM74" t="inlineStr"/>
@@ -35899,156 +35887,164 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>45948.60416666666</v>
+        <v>45948.69791666666</v>
       </c>
       <c r="G75" t="n">
         <v>3</v>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" t="n">
+        <v>10</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
         <v>6</v>
-      </c>
-      <c r="J75" t="n">
-        <v>3</v>
-      </c>
-      <c r="K75" t="n">
-        <v>3</v>
-      </c>
-      <c r="L75" t="n">
-        <v>6</v>
-      </c>
-      <c r="M75" t="n">
-        <v>2</v>
-      </c>
-      <c r="N75" t="n">
-        <v>3</v>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q75" t="n">
-        <v>4</v>
       </c>
       <c r="R75" t="n">
         <v>3</v>
       </c>
       <c r="S75" t="n">
+        <v>16</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>22</v>
+      </c>
+      <c r="V75" t="n">
+        <v>3</v>
+      </c>
+      <c r="W75" t="n">
+        <v>12</v>
+      </c>
+      <c r="X75" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Stadion Galgenwaard</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Herculesplein 241, Utrecht</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AU75" t="n">
         <v>4</v>
       </c>
-      <c r="T75" t="n">
-        <v>7</v>
-      </c>
-      <c r="U75" t="n">
-        <v>8</v>
-      </c>
-      <c r="V75" t="n">
-        <v>10</v>
-      </c>
-      <c r="W75" t="n">
-        <v>15</v>
-      </c>
-      <c r="X75" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA75" t="inlineStr"/>
-      <c r="AB75" t="inlineStr"/>
-      <c r="AC75" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD75" t="n">
+      <c r="AV75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX75" t="n">
         <v>3</v>
       </c>
-      <c r="AE75" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL75" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM75" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN75" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AO75" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AP75" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ75" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR75" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AS75" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT75" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AU75" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX75" t="n">
-        <v>2</v>
-      </c>
       <c r="AY75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB75" t="n">
-        <v>-1</v>
+        <v>376</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
@@ -36069,25 +36065,25 @@
         <v>1</v>
       </c>
       <c r="BI75" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BJ75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM75" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BN75" t="n">
         <v>3</v>
       </c>
       <c r="BO75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP75" t="n">
         <v>0</v>
@@ -36096,49 +36092,49 @@
         <v>1</v>
       </c>
       <c r="BR75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU75" t="n">
         <v>1</v>
       </c>
       <c r="BV75" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="BW75" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="BX75" t="n">
-        <v>78</v>
+        <v>133</v>
       </c>
       <c r="BY75" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="BZ75" t="n">
-        <v>1.08</v>
+        <v>2.22</v>
       </c>
       <c r="CA75" t="n">
-        <v>1.07</v>
+        <v>0.57</v>
       </c>
       <c r="CB75" t="n">
-        <v>2.15</v>
+        <v>2.79</v>
       </c>
       <c r="CC75" t="n">
         <v>0</v>
       </c>
       <c r="CD75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CE75" t="n">
         <v>0</v>
       </c>
       <c r="CF75" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CG75" t="n">
         <v>0</v>
@@ -36174,73 +36170,73 @@
         <v>1</v>
       </c>
       <c r="CR75" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS75" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="CT75" t="n">
         <v>1</v>
       </c>
       <c r="CU75" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="CV75" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="CW75" t="n">
         <v>1</v>
       </c>
       <c r="CX75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CY75" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="CZ75" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="DA75" t="n">
         <v>75</v>
       </c>
       <c r="DB75" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DC75" t="n">
         <v>88</v>
       </c>
       <c r="DD75" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="DE75" t="n">
-        <v>1.22</v>
+        <v>0.25</v>
       </c>
       <c r="DF75" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="DG75" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="DH75" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="DI75" t="n">
-        <v>1.63</v>
+        <v>0.88</v>
       </c>
       <c r="DJ75" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="DK75" t="n">
         <v>25</v>
       </c>
       <c r="DL75" t="n">
-        <v>1.96</v>
+        <v>1.65</v>
       </c>
       <c r="DM75" t="n">
-        <v>2.08</v>
+        <v>1.16</v>
       </c>
       <c r="DN75" t="n">
-        <v>4.04</v>
+        <v>2.81</v>
       </c>
       <c r="DO75" t="n">
         <v>17</v>
@@ -36258,41 +36254,53 @@
         <v>1</v>
       </c>
       <c r="DT75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV75" t="b">
         <v>1</v>
       </c>
-      <c r="DW75" t="inlineStr"/>
-      <c r="DX75" t="inlineStr"/>
-      <c r="DY75" t="inlineStr"/>
-      <c r="DZ75" t="inlineStr"/>
+      <c r="DW75" t="n">
+        <v>12.46</v>
+      </c>
+      <c r="DX75" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="DY75" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="DZ75" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EE75" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EF75" t="inlineStr"/>
@@ -36301,17 +36309,17 @@
       <c r="EI75" t="inlineStr"/>
       <c r="EJ75" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EK75" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="EL75" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="EM75" t="inlineStr"/>
@@ -36335,34 +36343,34 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45948.69791666666</v>
       </c>
       <c r="G76" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
         <v>3</v>
       </c>
-      <c r="H76" t="n">
-        <v>1</v>
-      </c>
-      <c r="I76" t="n">
-        <v>4</v>
-      </c>
       <c r="J76" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M76" t="n">
         <v>1</v>
@@ -36377,128 +36385,128 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
         <v>16</v>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U76" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V76" t="n">
+        <v>4</v>
+      </c>
+      <c r="W76" t="n">
+        <v>7</v>
+      </c>
+      <c r="X76" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Philips Stadion</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Frederiklaan 10, Eindhoven</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AU76" t="n">
         <v>3</v>
       </c>
-      <c r="W76" t="n">
-        <v>12</v>
-      </c>
-      <c r="X76" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Stadion Galgenwaard</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Herculesplein 241, Utrecht</t>
-        </is>
-      </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL76" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN76" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ76" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR76" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS76" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AT76" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AU76" t="n">
-        <v>4</v>
-      </c>
       <c r="AV76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA76" t="n">
         <v>1</v>
       </c>
       <c r="BB76" t="n">
-        <v>376</v>
+        <v>121</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36513,7 +36521,7 @@
         <v>1</v>
       </c>
       <c r="BI76" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BJ76" t="n">
         <v>0</v>
@@ -36522,169 +36530,169 @@
         <v>3</v>
       </c>
       <c r="BL76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM76" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU76" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV76" t="n">
         <v>7</v>
       </c>
-      <c r="BN76" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS76" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT76" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU76" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV76" t="n">
-        <v>56</v>
-      </c>
-      <c r="BW76" t="n">
-        <v>22</v>
-      </c>
-      <c r="BX76" t="n">
-        <v>133</v>
-      </c>
-      <c r="BY76" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ76" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CA76" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="CB76" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CC76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP76" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS76" t="n">
-        <v>12</v>
-      </c>
-      <c r="CT76" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU76" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV76" t="n">
-        <v>12</v>
-      </c>
       <c r="CW76" t="n">
         <v>1</v>
       </c>
       <c r="CX76" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CY76" t="n">
         <v>10</v>
       </c>
       <c r="CZ76" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="DA76" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB76" t="n">
         <v>75</v>
-      </c>
-      <c r="DB76" t="n">
-        <v>50</v>
       </c>
       <c r="DC76" t="n">
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.25</v>
+        <v>0.67</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
       </c>
       <c r="DG76" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="DH76" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DI76" t="n">
         <v>1.25</v>
       </c>
-      <c r="DI76" t="n">
-        <v>0.88</v>
-      </c>
       <c r="DJ76" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="DK76" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL76" t="n">
-        <v>1.65</v>
+        <v>2.39</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="DN76" t="n">
-        <v>2.81</v>
+        <v>3.93</v>
       </c>
       <c r="DO76" t="n">
         <v>17</v>
@@ -36699,7 +36707,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -36711,14 +36719,14 @@
         <v>1</v>
       </c>
       <c r="DW76" t="n">
-        <v>12.46</v>
+        <v>13.13</v>
       </c>
       <c r="DX76" t="n">
-        <v>3.16</v>
+        <v>3.69</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
@@ -36728,27 +36736,27 @@
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr"/>
@@ -36757,19 +36765,15 @@
       <c r="EI76" t="inlineStr"/>
       <c r="EJ76" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="EK76" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EL76" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EL76" t="inlineStr"/>
       <c r="EM76" t="inlineStr"/>
       <c r="EN76" t="inlineStr"/>
       <c r="EO76" t="inlineStr"/>
@@ -36791,164 +36795,164 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45948.69791666666</v>
+        <v>45948.79166666666</v>
       </c>
       <c r="G77" t="n">
         <v>2</v>
       </c>
       <c r="H77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I77" t="n">
+        <v>4</v>
+      </c>
+      <c r="J77" t="n">
         <v>3</v>
       </c>
-      <c r="J77" t="n">
+      <c r="K77" t="n">
+        <v>2</v>
+      </c>
+      <c r="L77" t="n">
+        <v>5</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q77" t="n">
         <v>6</v>
       </c>
-      <c r="K77" t="n">
-        <v>1</v>
-      </c>
-      <c r="L77" t="n">
-        <v>7</v>
-      </c>
-      <c r="M77" t="n">
-        <v>1</v>
-      </c>
-      <c r="N77" t="n">
-        <v>1</v>
-      </c>
-      <c r="O77" t="n">
-        <v>0</v>
-      </c>
-      <c r="P77" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q77" t="n">
+      <c r="R77" t="n">
+        <v>3</v>
+      </c>
+      <c r="S77" t="n">
+        <v>13</v>
+      </c>
+      <c r="T77" t="n">
         <v>8</v>
       </c>
-      <c r="R77" t="n">
-        <v>2</v>
-      </c>
-      <c r="S77" t="n">
-        <v>16</v>
-      </c>
-      <c r="T77" t="n">
-        <v>2</v>
-      </c>
       <c r="U77" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="V77" t="n">
+        <v>11</v>
+      </c>
+      <c r="W77" t="n">
+        <v>9</v>
+      </c>
+      <c r="X77" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y77" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z77" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>Rat Verlegh Stadion</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>Stadionstraat 23, Breda</t>
+        </is>
+      </c>
+      <c r="AC77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AU77" t="n">
         <v>4</v>
       </c>
-      <c r="W77" t="n">
-        <v>7</v>
-      </c>
-      <c r="X77" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y77" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z77" t="n">
-        <v>43</v>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>Philips Stadion</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>Frederiklaan 10, Eindhoven</t>
-        </is>
-      </c>
-      <c r="AC77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE77" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF77" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AG77" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AH77" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AI77" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ77" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK77" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL77" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AM77" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN77" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO77" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AP77" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ77" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AR77" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS77" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT77" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AU77" t="n">
+      <c r="AV77" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA77" t="n">
         <v>3</v>
       </c>
-      <c r="AV77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW77" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AY77" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ77" t="n">
-        <v>2</v>
-      </c>
-      <c r="BA77" t="n">
-        <v>1</v>
-      </c>
       <c r="BB77" t="n">
-        <v>121</v>
+        <v>-1</v>
       </c>
       <c r="BC77" t="n">
         <v>0</v>
@@ -36975,31 +36979,31 @@
         <v>0</v>
       </c>
       <c r="BK77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BL77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM77" t="n">
         <v>3</v>
       </c>
       <c r="BN77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BO77" t="n">
         <v>0</v>
       </c>
       <c r="BP77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT77" t="n">
         <v>2</v>
@@ -37008,34 +37012,34 @@
         <v>1</v>
       </c>
       <c r="BV77" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="BW77" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="BX77" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="BY77" t="n">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="BZ77" t="n">
-        <v>2.43</v>
+        <v>1.98</v>
       </c>
       <c r="CA77" t="n">
-        <v>0.59</v>
+        <v>1.22</v>
       </c>
       <c r="CB77" t="n">
-        <v>3.02</v>
+        <v>3.21</v>
       </c>
       <c r="CC77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD77" t="n">
         <v>0</v>
       </c>
       <c r="CE77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF77" t="n">
         <v>0</v>
@@ -37059,7 +37063,7 @@
         <v>0</v>
       </c>
       <c r="CM77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN77" t="n">
         <v>0</v>
@@ -37074,73 +37078,73 @@
         <v>1</v>
       </c>
       <c r="CR77" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="CS77" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="CT77" t="n">
         <v>1</v>
       </c>
       <c r="CU77" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CV77" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="CW77" t="n">
         <v>1</v>
       </c>
       <c r="CX77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CY77" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ77" t="n">
         <v>75</v>
       </c>
       <c r="DA77" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="DB77" t="n">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="DC77" t="n">
         <v>88</v>
       </c>
       <c r="DD77" t="n">
-        <v>2.38</v>
+        <v>1.22</v>
       </c>
       <c r="DE77" t="n">
         <v>0.67</v>
       </c>
       <c r="DF77" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="DG77" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="DH77" t="n">
-        <v>2.38</v>
+        <v>0.88</v>
       </c>
       <c r="DI77" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="DJ77" t="n">
         <v>25</v>
       </c>
       <c r="DK77" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="DL77" t="n">
-        <v>2.39</v>
+        <v>1.55</v>
       </c>
       <c r="DM77" t="n">
-        <v>1.54</v>
+        <v>1.1</v>
       </c>
       <c r="DN77" t="n">
-        <v>3.93</v>
+        <v>2.65</v>
       </c>
       <c r="DO77" t="n">
         <v>17</v>
@@ -37155,7 +37159,7 @@
         <v>1</v>
       </c>
       <c r="DS77" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT77" t="b">
         <v>0</v>
@@ -37167,65 +37171,101 @@
         <v>1</v>
       </c>
       <c r="DW77" t="n">
-        <v>13.13</v>
+        <v>13.08</v>
       </c>
       <c r="DX77" t="n">
-        <v>3.69</v>
+        <v>4.3</v>
       </c>
       <c r="DY77" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="DZ77" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="EA77" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="EB77" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="EC77" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="ED77" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EE77" t="inlineStr">
         <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EF77" t="inlineStr"/>
-      <c r="EG77" t="inlineStr"/>
-      <c r="EH77" t="inlineStr"/>
-      <c r="EI77" t="inlineStr"/>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="EF77" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EG77" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="EH77" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EI77" t="inlineStr">
+        <is>
+          <t>3.37</t>
+        </is>
+      </c>
       <c r="EJ77" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="EK77" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EL77" t="inlineStr"/>
-      <c r="EM77" t="inlineStr"/>
-      <c r="EN77" t="inlineStr"/>
-      <c r="EO77" t="inlineStr"/>
-      <c r="EP77" t="inlineStr"/>
+          <t>2.79</t>
+        </is>
+      </c>
+      <c r="EL77" t="inlineStr">
+        <is>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EM77" t="inlineStr">
+        <is>
+          <t>2.43</t>
+        </is>
+      </c>
+      <c r="EN77" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EO77" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EP77" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -37243,40 +37283,40 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
         <v>45948.79166666666</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H78" t="n">
         <v>2</v>
       </c>
       <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" t="n">
         <v>4</v>
       </c>
-      <c r="J78" t="n">
-        <v>3</v>
-      </c>
-      <c r="K78" t="n">
-        <v>2</v>
-      </c>
       <c r="L78" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="M78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O78" t="n">
         <v>0</v>
@@ -37291,122 +37331,122 @@
         <v>3</v>
       </c>
       <c r="S78" t="n">
+        <v>11</v>
+      </c>
+      <c r="T78" t="n">
+        <v>10</v>
+      </c>
+      <c r="U78" t="n">
+        <v>17</v>
+      </c>
+      <c r="V78" t="n">
         <v>13</v>
       </c>
-      <c r="T78" t="n">
-        <v>8</v>
-      </c>
-      <c r="U78" t="n">
+      <c r="W78" t="n">
+        <v>13</v>
+      </c>
+      <c r="X78" t="n">
         <v>19</v>
       </c>
-      <c r="V78" t="n">
-        <v>11</v>
-      </c>
-      <c r="W78" t="n">
-        <v>9</v>
-      </c>
-      <c r="X78" t="n">
-        <v>10</v>
-      </c>
       <c r="Y78" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="Z78" t="n">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Rat Verlegh Stadion</t>
+          <t>Johan Cruijff Arena</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>Stadionstraat 23, Breda</t>
+          <t>ArenA Boulevard 1, Amsterdam</t>
         </is>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AF78" t="n">
-        <v>3.75</v>
+        <v>3.83</v>
       </c>
       <c r="AG78" t="n">
-        <v>3.15</v>
+        <v>3.46</v>
       </c>
       <c r="AH78" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="AI78" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AJ78" t="n">
-        <v>2.89</v>
+        <v>2.4</v>
       </c>
       <c r="AK78" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AL78" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="AM78" t="n">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="AN78" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="AO78" t="n">
-        <v>2.36</v>
+        <v>2.18</v>
       </c>
       <c r="AP78" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AQ78" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AR78" t="n">
-        <v>2.59</v>
+        <v>2.27</v>
       </c>
       <c r="AS78" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AT78" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AU78" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV78" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX78" t="n">
         <v>0</v>
       </c>
       <c r="AY78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB78" t="n">
-        <v>-1</v>
+        <v>378</v>
       </c>
       <c r="BC78" t="n">
         <v>0</v>
       </c>
       <c r="BD78" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="BE78" t="n">
         <v>0</v>
@@ -37421,22 +37461,22 @@
         <v>1</v>
       </c>
       <c r="BI78" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK78" t="n">
         <v>3</v>
       </c>
-      <c r="BJ78" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK78" t="n">
-        <v>0</v>
-      </c>
       <c r="BL78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM78" t="n">
         <v>3</v>
       </c>
       <c r="BN78" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BO78" t="n">
         <v>0</v>
@@ -37445,52 +37485,52 @@
         <v>1</v>
       </c>
       <c r="BQ78" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BR78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS78" t="n">
         <v>1</v>
       </c>
       <c r="BT78" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU78" t="n">
         <v>1</v>
       </c>
       <c r="BV78" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="BW78" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="BX78" t="n">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="BY78" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="BZ78" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="CA78" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="CB78" t="n">
         <v>3.21</v>
       </c>
       <c r="CC78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG78" t="n">
         <v>0</v>
@@ -37511,7 +37551,7 @@
         <v>0</v>
       </c>
       <c r="CM78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN78" t="n">
         <v>0</v>
@@ -37526,19 +37566,19 @@
         <v>1</v>
       </c>
       <c r="CR78" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="CS78" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU78" t="n">
+        <v>19</v>
+      </c>
+      <c r="CV78" t="n">
         <v>12</v>
-      </c>
-      <c r="CT78" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU78" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV78" t="n">
-        <v>11</v>
       </c>
       <c r="CW78" t="n">
         <v>1</v>
@@ -37550,52 +37590,52 @@
         <v>9</v>
       </c>
       <c r="CZ78" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="DA78" t="n">
         <v>88</v>
       </c>
       <c r="DB78" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="DC78" t="n">
         <v>88</v>
       </c>
       <c r="DD78" t="n">
-        <v>1.22</v>
+        <v>2.11</v>
       </c>
       <c r="DE78" t="n">
-        <v>0.67</v>
+        <v>1.44</v>
       </c>
       <c r="DF78" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="DG78" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DH78" t="n">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="DI78" t="n">
-        <v>0.88</v>
+        <v>1.88</v>
       </c>
       <c r="DJ78" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="DK78" t="n">
         <v>13</v>
       </c>
       <c r="DL78" t="n">
-        <v>1.55</v>
+        <v>1.97</v>
       </c>
       <c r="DM78" t="n">
-        <v>1.1</v>
+        <v>1.93</v>
       </c>
       <c r="DN78" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="DO78" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -37604,10 +37644,10 @@
         <v>1</v>
       </c>
       <c r="DR78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT78" t="b">
         <v>0</v>
@@ -37616,102 +37656,94 @@
         <v>0</v>
       </c>
       <c r="DV78" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW78" t="n">
-        <v>13.08</v>
+        <v>12.42</v>
       </c>
       <c r="DX78" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="DY78" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ78" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="EA78" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="EB78" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="EC78" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="ED78" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="EE78" t="inlineStr">
         <is>
-          <t>2.23</t>
-        </is>
-      </c>
-      <c r="EF78" t="inlineStr">
-        <is>
-          <t>1.34</t>
-        </is>
-      </c>
+          <t>2.77</t>
+        </is>
+      </c>
+      <c r="EF78" t="inlineStr"/>
       <c r="EG78" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EH78" t="inlineStr">
         <is>
-          <t>1.51</t>
-        </is>
-      </c>
-      <c r="EI78" t="inlineStr">
-        <is>
-          <t>3.37</t>
-        </is>
-      </c>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EI78" t="inlineStr"/>
       <c r="EJ78" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="EK78" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EL78" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="EM78" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EN78" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EO78" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EP78" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
@@ -37731,37 +37763,37 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45948.79166666666</v>
+        <v>45949.42708333334</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J79" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L79" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="M79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N79" t="n">
         <v>2</v>
@@ -37776,125 +37808,117 @@
         <v>6</v>
       </c>
       <c r="R79" t="n">
+        <v>7</v>
+      </c>
+      <c r="S79" t="n">
+        <v>12</v>
+      </c>
+      <c r="T79" t="n">
+        <v>8</v>
+      </c>
+      <c r="U79" t="n">
+        <v>18</v>
+      </c>
+      <c r="V79" t="n">
+        <v>15</v>
+      </c>
+      <c r="W79" t="n">
+        <v>9</v>
+      </c>
+      <c r="X79" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y79" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z79" t="n">
+        <v>54</v>
+      </c>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE79" t="n">
         <v>3</v>
       </c>
-      <c r="S79" t="n">
-        <v>11</v>
-      </c>
-      <c r="T79" t="n">
-        <v>10</v>
-      </c>
-      <c r="U79" t="n">
-        <v>17</v>
-      </c>
-      <c r="V79" t="n">
-        <v>13</v>
-      </c>
-      <c r="W79" t="n">
-        <v>13</v>
-      </c>
-      <c r="X79" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y79" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z79" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>Johan Cruijff Arena</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>ArenA Boulevard 1, Amsterdam</t>
-        </is>
-      </c>
-      <c r="AC79" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD79" t="n">
-        <v>2</v>
-      </c>
-      <c r="AE79" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AF79" t="n">
-        <v>3.83</v>
+        <v>3.6</v>
       </c>
       <c r="AG79" t="n">
-        <v>3.46</v>
+        <v>2.3</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AJ79" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR79" t="n">
         <v>2.4</v>
       </c>
-      <c r="AK79" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL79" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AM79" t="n">
+      <c r="AS79" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT79" t="n">
         <v>1.6</v>
       </c>
-      <c r="AN79" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AO79" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AP79" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AQ79" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AR79" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AS79" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT79" t="n">
-        <v>1.58</v>
-      </c>
       <c r="AU79" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW79" t="n">
         <v>2</v>
       </c>
       <c r="AX79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB79" t="n">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="BC79" t="n">
         <v>0</v>
       </c>
       <c r="BD79" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="BE79" t="n">
         <v>0</v>
@@ -37909,64 +37933,64 @@
         <v>1</v>
       </c>
       <c r="BI79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ79" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="BK79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BL79" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BM79" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="BN79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BO79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP79" t="n">
         <v>1</v>
       </c>
       <c r="BQ79" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BR79" t="n">
         <v>1</v>
       </c>
       <c r="BS79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT79" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BU79" t="n">
         <v>1</v>
       </c>
       <c r="BV79" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="BW79" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX79" t="n">
         <v>38</v>
       </c>
-      <c r="BX79" t="n">
-        <v>116</v>
-      </c>
       <c r="BY79" t="n">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="BZ79" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="CA79" t="n">
-        <v>1.31</v>
+        <v>1.57</v>
       </c>
       <c r="CB79" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="CC79" t="n">
         <v>0</v>
@@ -38002,10 +38026,10 @@
         <v>0</v>
       </c>
       <c r="CN79" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP79" t="n">
         <v>0</v>
@@ -38014,76 +38038,76 @@
         <v>1</v>
       </c>
       <c r="CR79" t="n">
+        <v>20</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>13</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU79" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV79" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW79" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX79" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY79" t="n">
+        <v>11</v>
+      </c>
+      <c r="CZ79" t="n">
+        <v>71</v>
+      </c>
+      <c r="DA79" t="n">
+        <v>84</v>
+      </c>
+      <c r="DB79" t="n">
+        <v>71</v>
+      </c>
+      <c r="DC79" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD79" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="DE79" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF79" t="n">
+        <v>1</v>
+      </c>
+      <c r="DG79" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DH79" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DI79" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DJ79" t="n">
+        <v>29</v>
+      </c>
+      <c r="DK79" t="n">
         <v>17</v>
       </c>
-      <c r="CS79" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU79" t="n">
-        <v>19</v>
-      </c>
-      <c r="CV79" t="n">
-        <v>12</v>
-      </c>
-      <c r="CW79" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX79" t="n">
-        <v>6</v>
-      </c>
-      <c r="CY79" t="n">
-        <v>9</v>
-      </c>
-      <c r="CZ79" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA79" t="n">
-        <v>88</v>
-      </c>
-      <c r="DB79" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC79" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD79" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DE79" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DF79" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG79" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DH79" t="n">
-        <v>2</v>
-      </c>
-      <c r="DI79" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DJ79" t="n">
-        <v>38</v>
-      </c>
-      <c r="DK79" t="n">
-        <v>13</v>
-      </c>
       <c r="DL79" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="DM79" t="n">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="DN79" t="n">
-        <v>3.9</v>
+        <v>3.32</v>
       </c>
       <c r="DO79" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -38092,81 +38116,81 @@
         <v>1</v>
       </c>
       <c r="DR79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU79" t="b">
         <v>0</v>
       </c>
       <c r="DV79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW79" t="n">
-        <v>12.42</v>
+        <v>11.72</v>
       </c>
       <c r="DX79" t="n">
-        <v>2.78</v>
+        <v>7.01</v>
       </c>
       <c r="DY79" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="DZ79" t="inlineStr">
         <is>
-          <t>3%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA79" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EB79" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="EC79" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="ED79" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EE79" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="EF79" t="inlineStr"/>
       <c r="EG79" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="EH79" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EI79" t="inlineStr"/>
       <c r="EJ79" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="EK79" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="EL79" t="inlineStr">
@@ -38174,26 +38198,18 @@
           <t>1.18</t>
         </is>
       </c>
-      <c r="EM79" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
+      <c r="EM79" t="inlineStr"/>
       <c r="EN79" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EO79" t="inlineStr">
         <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EP79" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
+          <t>2.01</t>
+        </is>
+      </c>
+      <c r="EP79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -38211,38 +38227,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45949.42708333334</v>
+        <v>45949.52083333334</v>
       </c>
       <c r="G80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2</v>
+      </c>
+      <c r="J80" t="n">
+        <v>7</v>
+      </c>
+      <c r="K80" t="n">
+        <v>4</v>
+      </c>
+      <c r="L80" t="n">
+        <v>11</v>
+      </c>
+      <c r="M80" t="n">
         <v>3</v>
       </c>
-      <c r="I80" t="n">
-        <v>5</v>
-      </c>
-      <c r="J80" t="n">
-        <v>6</v>
-      </c>
-      <c r="K80" t="n">
-        <v>11</v>
-      </c>
-      <c r="L80" t="n">
-        <v>17</v>
-      </c>
-      <c r="M80" t="n">
-        <v>1</v>
-      </c>
       <c r="N80" t="n">
         <v>2</v>
       </c>
@@ -38253,120 +38269,120 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="S80" t="n">
         <v>12</v>
       </c>
       <c r="T80" t="n">
+        <v>6</v>
+      </c>
+      <c r="U80" t="n">
+        <v>12</v>
+      </c>
+      <c r="V80" t="n">
         <v>8</v>
       </c>
-      <c r="U80" t="n">
-        <v>18</v>
-      </c>
-      <c r="V80" t="n">
-        <v>15</v>
-      </c>
       <c r="W80" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="X80" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y80" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="Z80" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="AA80" t="inlineStr"/>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD80" t="n">
         <v>2</v>
       </c>
       <c r="AE80" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AG80" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="AH80" t="n">
         <v>1.22</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="AN80" t="n">
-        <v>1.78</v>
+        <v>2.05</v>
       </c>
       <c r="AO80" t="n">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AR80" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AS80" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="AU80" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY80" t="n">
         <v>1</v>
       </c>
       <c r="AZ80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -38384,175 +38400,175 @@
         <v>1</v>
       </c>
       <c r="BJ80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>35</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>12</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>78</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>41</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>28</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>14</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>10</v>
+      </c>
+      <c r="CV80" t="n">
         <v>11</v>
       </c>
-      <c r="BK80" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM80" t="n">
-        <v>12</v>
-      </c>
-      <c r="BN80" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV80" t="n">
-        <v>20</v>
-      </c>
-      <c r="BW80" t="n">
-        <v>20</v>
-      </c>
-      <c r="BX80" t="n">
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY80" t="n">
+        <v>10</v>
+      </c>
+      <c r="CZ80" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA80" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB80" t="n">
         <v>38</v>
       </c>
-      <c r="BY80" t="n">
-        <v>48</v>
-      </c>
-      <c r="BZ80" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CA80" t="n">
+      <c r="DC80" t="n">
+        <v>75</v>
+      </c>
+      <c r="DD80" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DF80" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG80" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH80" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DI80" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DJ80" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK80" t="n">
+        <v>25</v>
+      </c>
+      <c r="DL80" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DM80" t="n">
         <v>1.57</v>
       </c>
-      <c r="CB80" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="CC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN80" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>20</v>
-      </c>
-      <c r="CS80" t="n">
-        <v>13</v>
-      </c>
-      <c r="CT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU80" t="n">
-        <v>12</v>
-      </c>
-      <c r="CV80" t="n">
-        <v>8</v>
-      </c>
-      <c r="CW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX80" t="n">
-        <v>12</v>
-      </c>
-      <c r="CY80" t="n">
-        <v>11</v>
-      </c>
-      <c r="CZ80" t="n">
-        <v>71</v>
-      </c>
-      <c r="DA80" t="n">
-        <v>84</v>
-      </c>
-      <c r="DB80" t="n">
-        <v>71</v>
-      </c>
-      <c r="DC80" t="n">
-        <v>100</v>
-      </c>
-      <c r="DD80" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="DE80" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DF80" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG80" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DH80" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="DI80" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DJ80" t="n">
-        <v>29</v>
-      </c>
-      <c r="DK80" t="n">
-        <v>17</v>
-      </c>
-      <c r="DL80" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="DM80" t="n">
-        <v>1.33</v>
-      </c>
       <c r="DN80" t="n">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="DO80" t="n">
         <v>17</v>
@@ -38564,99 +38580,87 @@
         <v>1</v>
       </c>
       <c r="DR80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU80" t="b">
         <v>0</v>
       </c>
       <c r="DV80" t="b">
-        <v>1</v>
-      </c>
-      <c r="DW80" t="n">
-        <v>11.72</v>
-      </c>
-      <c r="DX80" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="DY80" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
-      <c r="DZ80" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="DW80" t="inlineStr"/>
+      <c r="DX80" t="inlineStr"/>
+      <c r="DY80" t="inlineStr"/>
+      <c r="DZ80" t="inlineStr"/>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>3.13</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>2.73</t>
-        </is>
-      </c>
-      <c r="EF80" t="inlineStr"/>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EF80" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>1.63</t>
-        </is>
-      </c>
-      <c r="EI80" t="inlineStr"/>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EI80" t="inlineStr">
+        <is>
+          <t>3.27</t>
+        </is>
+      </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="EM80" t="inlineStr"/>
-      <c r="EN80" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EO80" t="inlineStr">
-        <is>
-          <t>2.01</t>
-        </is>
-      </c>
+      <c r="EN80" t="inlineStr"/>
+      <c r="EO80" t="inlineStr"/>
       <c r="EP80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -38675,162 +38679,170 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
         <v>45949.52083333334</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K81" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L81" t="n">
+        <v>6</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0</v>
+      </c>
+      <c r="N81" t="n">
+        <v>3</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>5</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6</v>
+      </c>
+      <c r="S81" t="n">
+        <v>6</v>
+      </c>
+      <c r="T81" t="n">
+        <v>8</v>
+      </c>
+      <c r="U81" t="n">
         <v>11</v>
       </c>
-      <c r="M81" t="n">
+      <c r="V81" t="n">
+        <v>14</v>
+      </c>
+      <c r="W81" t="n">
+        <v>10</v>
+      </c>
+      <c r="X81" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>Van Donge &amp; De Roo Stadion</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>Honingerdijk 110, Rotterdam</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" t="n">
         <v>3</v>
       </c>
-      <c r="N81" t="n">
-        <v>2</v>
-      </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
-      <c r="R81" t="n">
-        <v>2</v>
-      </c>
-      <c r="S81" t="n">
-        <v>12</v>
-      </c>
-      <c r="T81" t="n">
-        <v>6</v>
-      </c>
-      <c r="U81" t="n">
-        <v>12</v>
-      </c>
-      <c r="V81" t="n">
-        <v>8</v>
-      </c>
-      <c r="W81" t="n">
-        <v>11</v>
-      </c>
-      <c r="X81" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA81" t="inlineStr"/>
-      <c r="AB81" t="inlineStr"/>
-      <c r="AC81" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD81" t="n">
-        <v>2</v>
-      </c>
       <c r="AE81" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AF81" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AG81" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH81" t="n">
         <v>1.22</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AJ81" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL81" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AM81" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AN81" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AO81" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AR81" t="n">
         <v>2.5</v>
       </c>
       <c r="AS81" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AU81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX81" t="n">
         <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA81" t="n">
         <v>1</v>
       </c>
       <c r="BB81" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -38848,130 +38860,130 @@
         <v>1</v>
       </c>
       <c r="BJ81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK81" t="n">
         <v>3</v>
       </c>
-      <c r="BK81" t="n">
-        <v>6</v>
-      </c>
       <c r="BL81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM81" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN81" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>59</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU81" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV81" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
         <v>7</v>
       </c>
-      <c r="BO81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP81" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR81" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT81" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU81" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV81" t="n">
-        <v>35</v>
-      </c>
-      <c r="BW81" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX81" t="n">
-        <v>78</v>
-      </c>
-      <c r="BY81" t="n">
-        <v>41</v>
-      </c>
-      <c r="BZ81" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CA81" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="CB81" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CC81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP81" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR81" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS81" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU81" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV81" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX81" t="n">
+      <c r="CY81" t="n">
         <v>8</v>
-      </c>
-      <c r="CY81" t="n">
-        <v>10</v>
       </c>
       <c r="CZ81" t="n">
         <v>63</v>
@@ -38986,22 +38998,22 @@
         <v>75</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="DE81" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="DF81" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="DG81" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="DH81" t="n">
-        <v>1.88</v>
+        <v>0.75</v>
       </c>
       <c r="DI81" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="DJ81" t="n">
         <v>38</v>
@@ -39010,22 +39022,22 @@
         <v>25</v>
       </c>
       <c r="DL81" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="DM81" t="n">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="DN81" t="n">
-        <v>3.08</v>
+        <v>2.37</v>
       </c>
       <c r="DO81" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
       </c>
       <c r="DQ81" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR81" t="b">
         <v>0</v>
@@ -39042,74 +39054,102 @@
       <c r="DV81" t="b">
         <v>0</v>
       </c>
-      <c r="DW81" t="inlineStr"/>
-      <c r="DX81" t="inlineStr"/>
-      <c r="DY81" t="inlineStr"/>
-      <c r="DZ81" t="inlineStr"/>
+      <c r="DW81" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="DX81" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="DY81" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ81" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EJ81" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EM81" t="inlineStr"/>
-      <c r="EN81" t="inlineStr"/>
-      <c r="EO81" t="inlineStr"/>
-      <c r="EP81" t="inlineStr"/>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EN81" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO81" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP81" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -39127,170 +39167,170 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
-        <v>45949.52083333334</v>
+        <v>45949.61458333334</v>
       </c>
       <c r="G82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I82" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J82" t="n">
+        <v>2</v>
+      </c>
+      <c r="K82" t="n">
+        <v>8</v>
+      </c>
+      <c r="L82" t="n">
+        <v>10</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1</v>
+      </c>
+      <c r="N82" t="n">
+        <v>2</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0</v>
+      </c>
+      <c r="R82" t="n">
+        <v>12</v>
+      </c>
+      <c r="S82" t="n">
         <v>4</v>
       </c>
-      <c r="K82" t="n">
-        <v>2</v>
-      </c>
-      <c r="L82" t="n">
-        <v>6</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
+      <c r="T82" t="n">
+        <v>7</v>
+      </c>
+      <c r="U82" t="n">
+        <v>4</v>
+      </c>
+      <c r="V82" t="n">
+        <v>19</v>
+      </c>
+      <c r="W82" t="n">
+        <v>12</v>
+      </c>
+      <c r="X82" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>Polman Stadion</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>Stadionlaan 1, Almelo</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY82" t="n">
         <v>3</v>
       </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>5</v>
-      </c>
-      <c r="R82" t="n">
-        <v>6</v>
-      </c>
-      <c r="S82" t="n">
-        <v>6</v>
-      </c>
-      <c r="T82" t="n">
-        <v>8</v>
-      </c>
-      <c r="U82" t="n">
-        <v>11</v>
-      </c>
-      <c r="V82" t="n">
-        <v>14</v>
-      </c>
-      <c r="W82" t="n">
-        <v>10</v>
-      </c>
-      <c r="X82" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA82" t="inlineStr">
-        <is>
-          <t>Van Donge &amp; De Roo Stadion</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>Honingerdijk 110, Rotterdam</t>
-        </is>
-      </c>
-      <c r="AC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD82" t="n">
+      <c r="AZ82" t="n">
         <v>3</v>
       </c>
-      <c r="AE82" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AM82" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN82" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AO82" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AP82" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AQ82" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR82" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS82" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AT82" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AU82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV82" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>0</v>
-      </c>
       <c r="BA82" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BB82" t="n">
-        <v>374</v>
+        <v>367</v>
       </c>
       <c r="BC82" t="n">
         <v>0</v>
       </c>
       <c r="BD82" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="BE82" t="n">
         <v>0</v>
@@ -39308,296 +39348,272 @@
         <v>1</v>
       </c>
       <c r="BJ82" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>5</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>2</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS82" t="n">
         <v>3</v>
       </c>
-      <c r="BL82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM82" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN82" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP82" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR82" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS82" t="n">
-        <v>1</v>
-      </c>
       <c r="BT82" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BU82" t="n">
         <v>1</v>
       </c>
       <c r="BV82" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BW82" t="n">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="BX82" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>109</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CC82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU82" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV82" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW82" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX82" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY82" t="n">
+        <v>6</v>
+      </c>
+      <c r="CZ82" t="n">
+        <v>88</v>
+      </c>
+      <c r="DA82" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB82" t="n">
         <v>59</v>
       </c>
-      <c r="BY82" t="n">
-        <v>64</v>
-      </c>
-      <c r="BZ82" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CA82" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CB82" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="CC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CL82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP82" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR82" t="n">
-        <v>23</v>
-      </c>
-      <c r="CS82" t="n">
-        <v>27</v>
-      </c>
-      <c r="CT82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU82" t="n">
-        <v>18</v>
-      </c>
-      <c r="CV82" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW82" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX82" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY82" t="n">
-        <v>8</v>
-      </c>
-      <c r="CZ82" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA82" t="n">
-        <v>75</v>
-      </c>
-      <c r="DB82" t="n">
-        <v>38</v>
-      </c>
       <c r="DC82" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="DD82" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DE82" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="DF82" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DG82" t="n">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="DH82" t="n">
-        <v>0.75</v>
+        <v>0.38</v>
       </c>
       <c r="DI82" t="n">
-        <v>1.63</v>
+        <v>2.75</v>
       </c>
       <c r="DJ82" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="DK82" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="DL82" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="DM82" t="n">
-        <v>1.02</v>
+        <v>1.96</v>
       </c>
       <c r="DN82" t="n">
-        <v>2.37</v>
+        <v>3.6</v>
       </c>
       <c r="DO82" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP82" t="b">
         <v>1</v>
       </c>
       <c r="DQ82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU82" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV82" t="b">
         <v>0</v>
       </c>
       <c r="DW82" t="n">
-        <v>13.3</v>
+        <v>12.24</v>
       </c>
       <c r="DX82" t="n">
-        <v>5.57</v>
+        <v>4.02</v>
       </c>
       <c r="DY82" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="DZ82" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="EA82" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EB82" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="EC82" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="ED82" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EE82" t="inlineStr">
         <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="EF82" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
+          <t>2.22</t>
+        </is>
+      </c>
+      <c r="EF82" t="inlineStr"/>
       <c r="EG82" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EH82" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI82" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EI82" t="inlineStr"/>
       <c r="EJ82" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EK82" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="EL82" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EM82" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="EN82" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EO82" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EP82" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="EM82" t="inlineStr"/>
+      <c r="EN82" t="inlineStr"/>
+      <c r="EO82" t="inlineStr"/>
+      <c r="EP82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -40088,7 +40104,7 @@
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>45955.60416666666</v>
+        <v>45955.61111111111</v>
       </c>
       <c r="G84" t="n">
         <v>1</v>
@@ -40109,10 +40125,10 @@
         <v>14</v>
       </c>
       <c r="M84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -40161,10 +40177,10 @@
         </is>
       </c>
       <c r="AC84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE84" t="n">
         <v>2.9</v>
@@ -40281,16 +40297,16 @@
         <v>0</v>
       </c>
       <c r="BQ84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BR84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS84" t="n">
         <v>0</v>
       </c>
       <c r="BT84" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU84" t="n">
         <v>1</v>
@@ -46278,8 +46294,16 @@
       <c r="Z97" t="n">
         <v>43</v>
       </c>
-      <c r="AA97" t="inlineStr"/>
-      <c r="AB97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>Polman Stadion</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>Stadionlaan 1, Almelo</t>
+        </is>
+      </c>
       <c r="AC97" t="n">
         <v>0</v>
       </c>
@@ -54200,7 +54224,7 @@
         <v>12</v>
       </c>
       <c r="R114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -54212,7 +54236,7 @@
         <v>22</v>
       </c>
       <c r="V114" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W114" t="n">
         <v>6</v>
@@ -54387,10 +54411,10 @@
         <v>2.57</v>
       </c>
       <c r="CA114" t="n">
-        <v>0.84</v>
+        <v>0.97</v>
       </c>
       <c r="CB114" t="n">
-        <v>3.41</v>
+        <v>3.54</v>
       </c>
       <c r="CC114" t="n">
         <v>0</v>
@@ -59825,7 +59849,7 @@
         <v>5</v>
       </c>
       <c r="M126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N126" t="n">
         <v>4</v>
@@ -59877,7 +59901,7 @@
         </is>
       </c>
       <c r="AC126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD126" t="n">
         <v>4</v>
@@ -59997,7 +60021,7 @@
         <v>0</v>
       </c>
       <c r="BQ126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR126" t="n">
         <v>4</v>
@@ -60006,7 +60030,7 @@
         <v>0</v>
       </c>
       <c r="BT126" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BU126" t="n">
         <v>1</v>
@@ -64425,10 +64449,10 @@
         <v>1.91</v>
       </c>
       <c r="DM135" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="DN135" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="DO135" t="n">
         <v>16</v>
@@ -68181,10 +68205,10 @@
         <v>2.05</v>
       </c>
       <c r="DM143" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DN143" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="DO143" t="n">
         <v>17</v>

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP153" headerRowCount="1">
-  <autoFilter ref="A1:EP153"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP155" headerRowCount="1">
+  <autoFilter ref="A1:EP155"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP153"/>
+  <dimension ref="A1:EP155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -3237,7 +3237,7 @@
         <v>1.5</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF5" t="n">
         <v>0</v>
@@ -4219,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4674,7 +4674,7 @@
         <v>0</v>
       </c>
       <c r="DD8" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE8" t="n">
         <v>1.44</v>
@@ -4707,7 +4707,7 @@
         <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP8" t="b">
         <v>1</v>
@@ -6101,7 +6101,7 @@
         <v>0.78</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -8167,164 +8167,164 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
         <v>45886.52083333334</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
       </c>
       <c r="L16" t="n">
+        <v>14</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>4</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="n">
         <v>11</v>
       </c>
-      <c r="M16" t="n">
-        <v>1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>5</v>
-      </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
+        <v>19</v>
+      </c>
+      <c r="V16" t="n">
+        <v>15</v>
+      </c>
+      <c r="W16" t="n">
         <v>10</v>
       </c>
-      <c r="T16" t="n">
-        <v>15</v>
-      </c>
-      <c r="U16" t="n">
-        <v>15</v>
-      </c>
-      <c r="V16" t="n">
-        <v>20</v>
-      </c>
-      <c r="W16" t="n">
-        <v>9</v>
-      </c>
       <c r="X16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y16" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Z16" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>Sparta-Stadion Het Kasteel</t>
+          <t>De Grolsch Veste</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>Spartapark Noord 1, Rotterdam</t>
+          <t>Colosseum 65, Enschede</t>
         </is>
       </c>
       <c r="AC16" t="n">
         <v>1</v>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.39</v>
+        <v>5.2</v>
       </c>
       <c r="AF16" t="n">
-        <v>3.55</v>
+        <v>4.45</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.81</v>
+        <v>1.35</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.88</v>
+        <v>2.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.65</v>
+        <v>1.47</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.15</v>
+        <v>2.61</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AO16" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AS16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AU16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
         <v>1</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA16" t="n">
         <v>1</v>
       </c>
       <c r="BB16" t="n">
-        <v>371</v>
+        <v>121</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
@@ -8345,73 +8345,73 @@
         <v>1</v>
       </c>
       <c r="BI16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL16" t="n">
         <v>3</v>
       </c>
-      <c r="BL16" t="n">
-        <v>4</v>
-      </c>
       <c r="BM16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="BN16" t="n">
         <v>7</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BU16" t="n">
         <v>1</v>
       </c>
       <c r="BV16" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="BW16" t="n">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="BX16" t="n">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="BY16" t="n">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.52</v>
+        <v>1.96</v>
       </c>
       <c r="CA16" t="n">
-        <v>1.99</v>
+        <v>1.53</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CC16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
         <v>0</v>
       </c>
       <c r="CE16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF16" t="n">
         <v>0</v>
@@ -8432,13 +8432,13 @@
         <v>0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CM16" t="n">
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO16" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
         <v>1</v>
       </c>
       <c r="CR16" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="CS16" t="n">
         <v>24</v>
@@ -8459,19 +8459,19 @@
         <v>1</v>
       </c>
       <c r="CU16" t="n">
+        <v>12</v>
+      </c>
+      <c r="CV16" t="n">
         <v>10</v>
       </c>
-      <c r="CV16" t="n">
-        <v>9</v>
-      </c>
       <c r="CW16" t="n">
         <v>1</v>
       </c>
       <c r="CX16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="CY16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="CZ16" t="n">
         <v>0</v>
@@ -8486,10 +8486,10 @@
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.75</v>
+        <v>3</v>
       </c>
       <c r="DF16" t="n">
         <v>0</v>
@@ -8528,7 +8528,7 @@
         <v>1</v>
       </c>
       <c r="DR16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS16" t="b">
         <v>0</v>
@@ -8540,17 +8540,17 @@
         <v>0</v>
       </c>
       <c r="DV16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW16" t="inlineStr"/>
       <c r="DX16" t="inlineStr">
         <is>
-          <t>6.91</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="DY16" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="DZ16" t="inlineStr">
@@ -8560,73 +8560,65 @@
       </c>
       <c r="EA16" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EB16" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="EC16" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="ED16" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EE16" t="inlineStr">
         <is>
-          <t>2.28</t>
-        </is>
-      </c>
-      <c r="EF16" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="EF16" t="inlineStr"/>
       <c r="EG16" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="EH16" t="inlineStr">
         <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="EI16" t="inlineStr">
-        <is>
-          <t>3.23</t>
-        </is>
-      </c>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="EI16" t="inlineStr"/>
       <c r="EJ16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="EK16" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EL16" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="EM16" t="inlineStr"/>
       <c r="EN16" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EO16" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EP16" t="inlineStr"/>
@@ -8647,40 +8639,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>45886.52083333334</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -8689,122 +8681,122 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
         <v>15</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V17" t="n">
+        <v>20</v>
+      </c>
+      <c r="W17" t="n">
+        <v>9</v>
+      </c>
+      <c r="X17" t="n">
         <v>11</v>
       </c>
-      <c r="U17" t="n">
-        <v>19</v>
-      </c>
-      <c r="V17" t="n">
-        <v>15</v>
-      </c>
-      <c r="W17" t="n">
-        <v>10</v>
-      </c>
-      <c r="X17" t="n">
-        <v>12</v>
-      </c>
       <c r="Y17" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Z17" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>De Grolsch Veste</t>
+          <t>Sparta-Stadion Het Kasteel</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>Colosseum 65, Enschede</t>
+          <t>Spartapark Noord 1, Rotterdam</t>
         </is>
       </c>
       <c r="AC17" t="n">
         <v>1</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
-        <v>5.2</v>
+        <v>2.39</v>
       </c>
       <c r="AF17" t="n">
-        <v>4.45</v>
+        <v>3.55</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.35</v>
+        <v>1.81</v>
       </c>
       <c r="AJ17" t="n">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.47</v>
+        <v>1.65</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AO17" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AR17" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA17" t="n">
         <v>1</v>
       </c>
       <c r="BB17" t="n">
-        <v>121</v>
+        <v>371</v>
       </c>
       <c r="BC17" t="n">
         <v>0</v>
@@ -8825,73 +8817,73 @@
         <v>1</v>
       </c>
       <c r="BI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>3</v>
+      </c>
+      <c r="BL17" t="n">
         <v>4</v>
       </c>
-      <c r="BJ17" t="n">
-        <v>3</v>
-      </c>
-      <c r="BK17" t="n">
+      <c r="BM17" t="n">
         <v>4</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>7</v>
       </c>
       <c r="BN17" t="n">
         <v>7</v>
       </c>
       <c r="BO17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BS17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BU17" t="n">
         <v>1</v>
       </c>
       <c r="BV17" t="n">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="BW17" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="BX17" t="n">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="BY17" t="n">
-        <v>96</v>
+        <v>129</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.96</v>
+        <v>1.52</v>
       </c>
       <c r="CA17" t="n">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="CC17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD17" t="n">
         <v>0</v>
       </c>
       <c r="CE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF17" t="n">
         <v>0</v>
@@ -8912,13 +8904,13 @@
         <v>0</v>
       </c>
       <c r="CL17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM17" t="n">
         <v>0</v>
       </c>
       <c r="CN17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO17" t="n">
         <v>0</v>
@@ -8930,7 +8922,7 @@
         <v>1</v>
       </c>
       <c r="CR17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="CS17" t="n">
         <v>24</v>
@@ -8939,19 +8931,19 @@
         <v>1</v>
       </c>
       <c r="CU17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="CV17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CW17" t="n">
         <v>1</v>
       </c>
       <c r="CX17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="CY17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="CZ17" t="n">
         <v>0</v>
@@ -8966,10 +8958,10 @@
         <v>0</v>
       </c>
       <c r="DD17" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="DE17" t="n">
-        <v>3</v>
+        <v>0.75</v>
       </c>
       <c r="DF17" t="n">
         <v>0</v>
@@ -9008,7 +9000,7 @@
         <v>1</v>
       </c>
       <c r="DR17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS17" t="b">
         <v>0</v>
@@ -9020,17 +9012,17 @@
         <v>0</v>
       </c>
       <c r="DV17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW17" t="inlineStr"/>
       <c r="DX17" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>6.91</t>
         </is>
       </c>
       <c r="DY17" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="DZ17" t="inlineStr">
@@ -9040,65 +9032,73 @@
       </c>
       <c r="EA17" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="EB17" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="EC17" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="ED17" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EE17" t="inlineStr">
         <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="EF17" t="inlineStr"/>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EF17" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
       <c r="EG17" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EH17" t="inlineStr">
         <is>
-          <t>1.78</t>
-        </is>
-      </c>
-      <c r="EI17" t="inlineStr"/>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="EI17" t="inlineStr">
+        <is>
+          <t>3.23</t>
+        </is>
+      </c>
       <c r="EJ17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EK17" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="EL17" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="EM17" t="inlineStr"/>
       <c r="EN17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EO17" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EP17" t="inlineStr"/>
@@ -9471,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -11321,7 +11321,7 @@
         <v>0.78</v>
       </c>
       <c r="DE22" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF22" t="n">
         <v>0</v>
@@ -17467,7 +17467,7 @@
         <v>3.45</v>
       </c>
       <c r="DO35" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP35" t="b">
         <v>1</v>
@@ -17917,7 +17917,7 @@
         <v>2.11</v>
       </c>
       <c r="DE36" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF36" t="n">
         <v>3</v>
@@ -18849,7 +18849,7 @@
         <v>1.63</v>
       </c>
       <c r="DE38" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF38" t="n">
         <v>0.5</v>
@@ -19782,7 +19782,7 @@
         <v>100</v>
       </c>
       <c r="DD40" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE40" t="n">
         <v>0.25</v>
@@ -20407,141 +20407,149 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
         <v>45914.52083333334</v>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
         <v>3</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
+        <v>4</v>
+      </c>
+      <c r="L42" t="n">
+        <v>7</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>4</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>3</v>
+      </c>
+      <c r="R42" t="n">
         <v>6</v>
       </c>
-      <c r="K42" t="n">
+      <c r="S42" t="n">
+        <v>11</v>
+      </c>
+      <c r="T42" t="n">
+        <v>7</v>
+      </c>
+      <c r="U42" t="n">
+        <v>14</v>
+      </c>
+      <c r="V42" t="n">
+        <v>13</v>
+      </c>
+      <c r="W42" t="n">
         <v>9</v>
       </c>
-      <c r="L42" t="n">
-        <v>15</v>
-      </c>
-      <c r="M42" t="n">
-        <v>1</v>
-      </c>
-      <c r="N42" t="n">
-        <v>5</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>6</v>
-      </c>
-      <c r="R42" t="n">
-        <v>8</v>
-      </c>
-      <c r="S42" t="n">
-        <v>13</v>
-      </c>
-      <c r="T42" t="n">
-        <v>17</v>
-      </c>
-      <c r="U42" t="n">
-        <v>19</v>
-      </c>
-      <c r="V42" t="n">
-        <v>25</v>
-      </c>
-      <c r="W42" t="n">
-        <v>11</v>
-      </c>
       <c r="X42" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y42" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="Z42" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>Stadion Galgenwaard</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>Herculesplein 241, Utrecht</t>
+        </is>
+      </c>
       <c r="AC42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE42" t="n">
-        <v>5.4</v>
+        <v>1.74</v>
       </c>
       <c r="AF42" t="n">
-        <v>4.58</v>
+        <v>3.8</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.44</v>
+        <v>4.75</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.3</v>
+        <v>3.27</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AL42" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.7</v>
+        <v>2.83</v>
       </c>
       <c r="AO42" t="n">
-        <v>2.6</v>
+        <v>1.96</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.99</v>
+        <v>1.58</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AR42" t="n">
-        <v>2.23</v>
+        <v>2.45</v>
       </c>
       <c r="AS42" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AU42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX42" t="n">
         <v>0</v>
@@ -20553,10 +20561,10 @@
         <v>1</v>
       </c>
       <c r="BA42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="BC42" t="n">
         <v>0</v>
@@ -20577,64 +20585,64 @@
         <v>1</v>
       </c>
       <c r="BI42" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ42" t="n">
         <v>3</v>
       </c>
-      <c r="BJ42" t="n">
-        <v>7</v>
-      </c>
       <c r="BK42" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BL42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BN42" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO42" t="n">
         <v>0</v>
       </c>
       <c r="BP42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR42" t="n">
         <v>3</v>
       </c>
       <c r="BS42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BT42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BU42" t="n">
         <v>1</v>
       </c>
       <c r="BV42" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="BW42" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="BX42" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="BY42" t="n">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="BZ42" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="CA42" t="n">
-        <v>2.45</v>
+        <v>1.53</v>
       </c>
       <c r="CB42" t="n">
-        <v>4.45</v>
+        <v>2.82</v>
       </c>
       <c r="CC42" t="n">
         <v>0</v>
@@ -20664,13 +20672,13 @@
         <v>0</v>
       </c>
       <c r="CL42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CM42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CO42" t="n">
         <v>0</v>
@@ -20682,85 +20690,85 @@
         <v>1</v>
       </c>
       <c r="CR42" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS42" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT42" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU42" t="n">
         <v>16</v>
       </c>
-      <c r="CS42" t="n">
-        <v>10</v>
-      </c>
-      <c r="CT42" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU42" t="n">
-        <v>11</v>
-      </c>
       <c r="CV42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="CW42" t="n">
         <v>1</v>
       </c>
       <c r="CX42" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY42" t="n">
         <v>8</v>
       </c>
-      <c r="CY42" t="n">
-        <v>12</v>
-      </c>
       <c r="CZ42" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DA42" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DB42" t="n">
         <v>75</v>
       </c>
       <c r="DC42" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="DD42" t="n">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="DE42" t="n">
         <v>1.44</v>
       </c>
       <c r="DF42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="DG42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DH42" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="DI42" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="DJ42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DK42" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL42" t="n">
-        <v>1.46</v>
+        <v>1.89</v>
       </c>
       <c r="DM42" t="n">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="DN42" t="n">
-        <v>3.73</v>
+        <v>3.54</v>
       </c>
       <c r="DO42" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
       </c>
       <c r="DQ42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS42" t="b">
         <v>0</v>
@@ -20772,74 +20780,82 @@
         <v>0</v>
       </c>
       <c r="DV42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW42" t="n">
-        <v>17.45</v>
+        <v>16.85</v>
       </c>
       <c r="DX42" t="n">
-        <v>6.62</v>
+        <v>7.28</v>
       </c>
       <c r="DY42" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="DZ42" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>19%</t>
         </is>
       </c>
       <c r="EA42" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="EB42" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="EC42" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="ED42" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="EE42" t="inlineStr">
         <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EF42" t="inlineStr"/>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="EF42" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
       <c r="EG42" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="EH42" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EI42" t="inlineStr"/>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="EI42" t="inlineStr">
+        <is>
+          <t>3.06</t>
+        </is>
+      </c>
       <c r="EJ42" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EK42" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EL42" t="inlineStr">
         <is>
-          <t>1.16</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="EM42" t="inlineStr"/>
@@ -20863,149 +20879,141 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
         <v>45914.52083333334</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
+        <v>6</v>
+      </c>
+      <c r="K43" t="n">
+        <v>9</v>
+      </c>
+      <c r="L43" t="n">
+        <v>15</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>5</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>6</v>
+      </c>
+      <c r="R43" t="n">
+        <v>8</v>
+      </c>
+      <c r="S43" t="n">
+        <v>13</v>
+      </c>
+      <c r="T43" t="n">
+        <v>17</v>
+      </c>
+      <c r="U43" t="n">
+        <v>19</v>
+      </c>
+      <c r="V43" t="n">
+        <v>25</v>
+      </c>
+      <c r="W43" t="n">
+        <v>11</v>
+      </c>
+      <c r="X43" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA43" t="inlineStr"/>
+      <c r="AB43" t="inlineStr"/>
+      <c r="AC43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>4.58</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AU43" t="n">
         <v>3</v>
       </c>
-      <c r="K43" t="n">
-        <v>4</v>
-      </c>
-      <c r="L43" t="n">
-        <v>7</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>4</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>3</v>
-      </c>
-      <c r="R43" t="n">
-        <v>6</v>
-      </c>
-      <c r="S43" t="n">
-        <v>11</v>
-      </c>
-      <c r="T43" t="n">
-        <v>7</v>
-      </c>
-      <c r="U43" t="n">
-        <v>14</v>
-      </c>
-      <c r="V43" t="n">
-        <v>13</v>
-      </c>
-      <c r="W43" t="n">
-        <v>9</v>
-      </c>
-      <c r="X43" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>Stadion Galgenwaard</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>Herculesplein 241, Utrecht</t>
-        </is>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AN43" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AO43" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AP43" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AQ43" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AR43" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT43" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>1</v>
-      </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX43" t="n">
         <v>0</v>
@@ -21017,10 +21025,10 @@
         <v>1</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB43" t="n">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="BC43" t="n">
         <v>0</v>
@@ -21041,101 +21049,101 @@
         <v>1</v>
       </c>
       <c r="BI43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ43" t="n">
+        <v>7</v>
+      </c>
+      <c r="BK43" t="n">
         <v>3</v>
       </c>
-      <c r="BK43" t="n">
-        <v>1</v>
-      </c>
       <c r="BL43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM43" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN43" t="n">
         <v>5</v>
       </c>
-      <c r="BN43" t="n">
-        <v>2</v>
-      </c>
       <c r="BO43" t="n">
         <v>0</v>
       </c>
       <c r="BP43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR43" t="n">
         <v>3</v>
       </c>
       <c r="BS43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT43" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU43" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV43" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW43" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX43" t="n">
+        <v>90</v>
+      </c>
+      <c r="BY43" t="n">
+        <v>84</v>
+      </c>
+      <c r="BZ43" t="n">
+        <v>2</v>
+      </c>
+      <c r="CA43" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CB43" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="CC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL43" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN43" t="n">
         <v>3</v>
       </c>
-      <c r="BU43" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV43" t="n">
-        <v>26</v>
-      </c>
-      <c r="BW43" t="n">
-        <v>39</v>
-      </c>
-      <c r="BX43" t="n">
-        <v>92</v>
-      </c>
-      <c r="BY43" t="n">
-        <v>113</v>
-      </c>
-      <c r="BZ43" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CA43" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CB43" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="CC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI43" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ43" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM43" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN43" t="n">
-        <v>0</v>
-      </c>
       <c r="CO43" t="n">
         <v>0</v>
       </c>
@@ -21146,73 +21154,73 @@
         <v>1</v>
       </c>
       <c r="CR43" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="CS43" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="CT43" t="n">
         <v>1</v>
       </c>
       <c r="CU43" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="CV43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CW43" t="n">
         <v>1</v>
       </c>
       <c r="CX43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CY43" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="CZ43" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DA43" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DB43" t="n">
         <v>75</v>
       </c>
       <c r="DC43" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="DD43" t="n">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="DE43" t="n">
         <v>1.44</v>
       </c>
       <c r="DF43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="DG43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DH43" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="DI43" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="DJ43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DK43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL43" t="n">
-        <v>1.89</v>
+        <v>1.46</v>
       </c>
       <c r="DM43" t="n">
-        <v>1.65</v>
+        <v>2.27</v>
       </c>
       <c r="DN43" t="n">
-        <v>3.54</v>
+        <v>3.73</v>
       </c>
       <c r="DO43" t="n">
         <v>17</v>
@@ -21221,10 +21229,10 @@
         <v>1</v>
       </c>
       <c r="DQ43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS43" t="b">
         <v>0</v>
@@ -21236,82 +21244,74 @@
         <v>0</v>
       </c>
       <c r="DV43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW43" t="n">
-        <v>16.85</v>
+        <v>17.45</v>
       </c>
       <c r="DX43" t="n">
-        <v>7.28</v>
+        <v>6.62</v>
       </c>
       <c r="DY43" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="DZ43" t="inlineStr">
         <is>
-          <t>19%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="EA43" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EB43" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="EC43" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="ED43" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="EE43" t="inlineStr">
         <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="EF43" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EF43" t="inlineStr"/>
       <c r="EG43" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="EH43" t="inlineStr">
         <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="EI43" t="inlineStr">
-        <is>
-          <t>3.06</t>
-        </is>
-      </c>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="EI43" t="inlineStr"/>
       <c r="EJ43" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="EK43" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EL43" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EM43" t="inlineStr"/>
@@ -26330,7 +26330,7 @@
         <v>100</v>
       </c>
       <c r="DD54" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE54" t="n">
         <v>2</v>
@@ -26363,7 +26363,7 @@
         <v>3.69</v>
       </c>
       <c r="DO54" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP54" t="b">
         <v>1</v>
@@ -26818,10 +26818,10 @@
         <v>100</v>
       </c>
       <c r="DD55" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE55" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF55" t="n">
         <v>2</v>
@@ -26851,7 +26851,7 @@
         <v>2.28</v>
       </c>
       <c r="DO55" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP55" t="b">
         <v>1</v>
@@ -27290,7 +27290,7 @@
         <v>100</v>
       </c>
       <c r="DD56" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE56" t="n">
         <v>0.5</v>
@@ -28253,7 +28253,7 @@
         <v>1.33</v>
       </c>
       <c r="DE58" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF58" t="n">
         <v>0.67</v>
@@ -28283,7 +28283,7 @@
         <v>2.29</v>
       </c>
       <c r="DO58" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP58" t="b">
         <v>1</v>
@@ -29691,7 +29691,7 @@
         <v>4.45</v>
       </c>
       <c r="DO61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -32477,7 +32477,7 @@
         <v>1.89</v>
       </c>
       <c r="DE67" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF67" t="n">
         <v>2.33</v>
@@ -33882,7 +33882,7 @@
         <v>100</v>
       </c>
       <c r="DD70" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE70" t="n">
         <v>0.44</v>
@@ -34826,7 +34826,7 @@
         <v>100</v>
       </c>
       <c r="DD72" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE72" t="n">
         <v>1</v>
@@ -34859,7 +34859,7 @@
         <v>3.06</v>
       </c>
       <c r="DO72" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -35887,34 +35887,34 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
         <v>45948.69791666666</v>
       </c>
       <c r="G75" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
         <v>3</v>
       </c>
-      <c r="H75" t="n">
-        <v>1</v>
-      </c>
-      <c r="I75" t="n">
-        <v>4</v>
-      </c>
       <c r="J75" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M75" t="n">
         <v>1</v>
@@ -35929,128 +35929,128 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S75" t="n">
         <v>16</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U75" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="V75" t="n">
+        <v>4</v>
+      </c>
+      <c r="W75" t="n">
+        <v>7</v>
+      </c>
+      <c r="X75" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>43</v>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>Philips Stadion</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>Frederiklaan 10, Eindhoven</t>
+        </is>
+      </c>
+      <c r="AC75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AU75" t="n">
         <v>3</v>
       </c>
-      <c r="W75" t="n">
-        <v>12</v>
-      </c>
-      <c r="X75" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>58</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>42</v>
-      </c>
-      <c r="AA75" t="inlineStr">
-        <is>
-          <t>Stadion Galgenwaard</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>Herculesplein 241, Utrecht</t>
-        </is>
-      </c>
-      <c r="AC75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD75" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE75" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AF75" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="AG75" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AH75" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AI75" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AJ75" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AK75" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL75" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM75" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AN75" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO75" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AP75" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ75" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AR75" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AS75" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AT75" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AU75" t="n">
-        <v>4</v>
-      </c>
       <c r="AV75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AY75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA75" t="n">
         <v>1</v>
       </c>
       <c r="BB75" t="n">
-        <v>376</v>
+        <v>121</v>
       </c>
       <c r="BC75" t="n">
         <v>0</v>
       </c>
       <c r="BD75" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="BE75" t="n">
         <v>0</v>
@@ -36065,7 +36065,7 @@
         <v>1</v>
       </c>
       <c r="BI75" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BJ75" t="n">
         <v>0</v>
@@ -36074,169 +36074,169 @@
         <v>3</v>
       </c>
       <c r="BL75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM75" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>26</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>94</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>63</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU75" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV75" t="n">
         <v>7</v>
       </c>
-      <c r="BN75" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS75" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT75" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU75" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV75" t="n">
-        <v>56</v>
-      </c>
-      <c r="BW75" t="n">
-        <v>22</v>
-      </c>
-      <c r="BX75" t="n">
-        <v>133</v>
-      </c>
-      <c r="BY75" t="n">
-        <v>75</v>
-      </c>
-      <c r="BZ75" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CA75" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="CB75" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="CC75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP75" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR75" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS75" t="n">
-        <v>12</v>
-      </c>
-      <c r="CT75" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU75" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV75" t="n">
-        <v>12</v>
-      </c>
       <c r="CW75" t="n">
         <v>1</v>
       </c>
       <c r="CX75" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CY75" t="n">
         <v>10</v>
       </c>
       <c r="CZ75" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="DA75" t="n">
+        <v>100</v>
+      </c>
+      <c r="DB75" t="n">
         <v>75</v>
-      </c>
-      <c r="DB75" t="n">
-        <v>50</v>
       </c>
       <c r="DC75" t="n">
         <v>88</v>
       </c>
       <c r="DD75" t="n">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="DE75" t="n">
-        <v>0.25</v>
+        <v>0.67</v>
       </c>
       <c r="DF75" t="n">
         <v>1.75</v>
       </c>
       <c r="DG75" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="DH75" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DI75" t="n">
         <v>1.25</v>
       </c>
-      <c r="DI75" t="n">
-        <v>0.88</v>
-      </c>
       <c r="DJ75" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="DK75" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="DL75" t="n">
-        <v>1.65</v>
+        <v>2.39</v>
       </c>
       <c r="DM75" t="n">
-        <v>1.16</v>
+        <v>1.54</v>
       </c>
       <c r="DN75" t="n">
-        <v>2.81</v>
+        <v>3.93</v>
       </c>
       <c r="DO75" t="n">
         <v>17</v>
@@ -36251,7 +36251,7 @@
         <v>1</v>
       </c>
       <c r="DS75" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT75" t="b">
         <v>0</v>
@@ -36263,14 +36263,14 @@
         <v>1</v>
       </c>
       <c r="DW75" t="n">
-        <v>12.46</v>
+        <v>13.13</v>
       </c>
       <c r="DX75" t="n">
-        <v>3.16</v>
+        <v>3.69</v>
       </c>
       <c r="DY75" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ75" t="inlineStr">
@@ -36280,27 +36280,27 @@
       </c>
       <c r="EA75" t="inlineStr">
         <is>
-          <t>9.07</t>
+          <t>9.53</t>
         </is>
       </c>
       <c r="EB75" t="inlineStr">
         <is>
-          <t>5.90</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="EC75" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="ED75" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EE75" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="EF75" t="inlineStr"/>
@@ -36309,19 +36309,15 @@
       <c r="EI75" t="inlineStr"/>
       <c r="EJ75" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="EK75" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="EL75" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EL75" t="inlineStr"/>
       <c r="EM75" t="inlineStr"/>
       <c r="EN75" t="inlineStr"/>
       <c r="EO75" t="inlineStr"/>
@@ -36343,170 +36339,170 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
         <v>45948.69791666666</v>
       </c>
       <c r="G76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H76" t="n">
         <v>1</v>
       </c>
       <c r="I76" t="n">
+        <v>4</v>
+      </c>
+      <c r="J76" t="n">
+        <v>10</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" t="n">
+        <v>10</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>6</v>
+      </c>
+      <c r="R76" t="n">
         <v>3</v>
-      </c>
-      <c r="J76" t="n">
-        <v>6</v>
-      </c>
-      <c r="K76" t="n">
-        <v>1</v>
-      </c>
-      <c r="L76" t="n">
-        <v>7</v>
-      </c>
-      <c r="M76" t="n">
-        <v>1</v>
-      </c>
-      <c r="N76" t="n">
-        <v>1</v>
-      </c>
-      <c r="O76" t="n">
-        <v>0</v>
-      </c>
-      <c r="P76" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q76" t="n">
-        <v>8</v>
-      </c>
-      <c r="R76" t="n">
-        <v>2</v>
       </c>
       <c r="S76" t="n">
         <v>16</v>
       </c>
       <c r="T76" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U76" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="V76" t="n">
+        <v>3</v>
+      </c>
+      <c r="W76" t="n">
+        <v>12</v>
+      </c>
+      <c r="X76" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y76" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z76" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>Stadion Galgenwaard</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>Herculesplein 241, Utrecht</t>
+        </is>
+      </c>
+      <c r="AC76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AU76" t="n">
         <v>4</v>
       </c>
-      <c r="W76" t="n">
-        <v>7</v>
-      </c>
-      <c r="X76" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y76" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z76" t="n">
-        <v>43</v>
-      </c>
-      <c r="AA76" t="inlineStr">
-        <is>
-          <t>Philips Stadion</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>Frederiklaan 10, Eindhoven</t>
-        </is>
-      </c>
-      <c r="AC76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE76" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AF76" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AG76" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AH76" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AI76" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AJ76" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AK76" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL76" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AM76" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN76" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AO76" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AP76" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ76" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AR76" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AS76" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT76" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AU76" t="n">
+      <c r="AV76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX76" t="n">
         <v>3</v>
       </c>
-      <c r="AV76" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW76" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX76" t="n">
-        <v>1</v>
-      </c>
       <c r="AY76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ76" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA76" t="n">
         <v>1</v>
       </c>
       <c r="BB76" t="n">
-        <v>121</v>
+        <v>376</v>
       </c>
       <c r="BC76" t="n">
         <v>0</v>
       </c>
       <c r="BD76" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="BE76" t="n">
         <v>0</v>
@@ -36521,7 +36517,7 @@
         <v>1</v>
       </c>
       <c r="BI76" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BJ76" t="n">
         <v>0</v>
@@ -36530,14 +36526,14 @@
         <v>3</v>
       </c>
       <c r="BL76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM76" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN76" t="n">
         <v>3</v>
       </c>
-      <c r="BN76" t="n">
-        <v>4</v>
-      </c>
       <c r="BO76" t="n">
         <v>0</v>
       </c>
@@ -36560,25 +36556,25 @@
         <v>1</v>
       </c>
       <c r="BV76" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="BW76" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BX76" t="n">
-        <v>94</v>
+        <v>133</v>
       </c>
       <c r="BY76" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="BZ76" t="n">
-        <v>2.43</v>
+        <v>2.22</v>
       </c>
       <c r="CA76" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="CB76" t="n">
-        <v>3.02</v>
+        <v>2.79</v>
       </c>
       <c r="CC76" t="n">
         <v>0</v>
@@ -36626,73 +36622,73 @@
         <v>1</v>
       </c>
       <c r="CR76" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="CS76" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="CT76" t="n">
         <v>1</v>
       </c>
       <c r="CU76" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CV76" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CW76" t="n">
         <v>1</v>
       </c>
       <c r="CX76" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="CY76" t="n">
         <v>10</v>
       </c>
       <c r="CZ76" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA76" t="n">
         <v>75</v>
       </c>
-      <c r="DA76" t="n">
-        <v>100</v>
-      </c>
       <c r="DB76" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DC76" t="n">
         <v>88</v>
       </c>
       <c r="DD76" t="n">
-        <v>2.38</v>
+        <v>1.89</v>
       </c>
       <c r="DE76" t="n">
-        <v>0.67</v>
+        <v>0.22</v>
       </c>
       <c r="DF76" t="n">
         <v>1.75</v>
       </c>
       <c r="DG76" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DH76" t="n">
         <v>1.25</v>
       </c>
-      <c r="DH76" t="n">
-        <v>2.38</v>
-      </c>
       <c r="DI76" t="n">
-        <v>1.25</v>
+        <v>0.88</v>
       </c>
       <c r="DJ76" t="n">
+        <v>38</v>
+      </c>
+      <c r="DK76" t="n">
         <v>25</v>
       </c>
-      <c r="DK76" t="n">
-        <v>0</v>
-      </c>
       <c r="DL76" t="n">
-        <v>2.39</v>
+        <v>1.65</v>
       </c>
       <c r="DM76" t="n">
-        <v>1.54</v>
+        <v>1.16</v>
       </c>
       <c r="DN76" t="n">
-        <v>3.93</v>
+        <v>2.81</v>
       </c>
       <c r="DO76" t="n">
         <v>17</v>
@@ -36707,7 +36703,7 @@
         <v>1</v>
       </c>
       <c r="DS76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT76" t="b">
         <v>0</v>
@@ -36719,14 +36715,14 @@
         <v>1</v>
       </c>
       <c r="DW76" t="n">
-        <v>13.13</v>
+        <v>12.46</v>
       </c>
       <c r="DX76" t="n">
-        <v>3.69</v>
+        <v>3.16</v>
       </c>
       <c r="DY76" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="DZ76" t="inlineStr">
@@ -36736,27 +36732,27 @@
       </c>
       <c r="EA76" t="inlineStr">
         <is>
-          <t>9.53</t>
+          <t>9.07</t>
         </is>
       </c>
       <c r="EB76" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>5.90</t>
         </is>
       </c>
       <c r="EC76" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="ED76" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="EE76" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="EF76" t="inlineStr"/>
@@ -36765,15 +36761,19 @@
       <c r="EI76" t="inlineStr"/>
       <c r="EJ76" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EK76" t="inlineStr">
         <is>
-          <t>1.61</t>
-        </is>
-      </c>
-      <c r="EL76" t="inlineStr"/>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="EL76" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
       <c r="EM76" t="inlineStr"/>
       <c r="EN76" t="inlineStr"/>
       <c r="EO76" t="inlineStr"/>
@@ -37117,7 +37117,7 @@
         <v>1.22</v>
       </c>
       <c r="DE77" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF77" t="n">
         <v>1.5</v>
@@ -37635,7 +37635,7 @@
         <v>3.9</v>
       </c>
       <c r="DO78" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP78" t="b">
         <v>1</v>
@@ -38227,162 +38227,170 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
         <v>45949.52083333334</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K80" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L80" t="n">
+        <v>6</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="n">
+        <v>3</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>5</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6</v>
+      </c>
+      <c r="S80" t="n">
+        <v>6</v>
+      </c>
+      <c r="T80" t="n">
+        <v>8</v>
+      </c>
+      <c r="U80" t="n">
         <v>11</v>
       </c>
-      <c r="M80" t="n">
+      <c r="V80" t="n">
+        <v>14</v>
+      </c>
+      <c r="W80" t="n">
+        <v>10</v>
+      </c>
+      <c r="X80" t="n">
+        <v>18</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>Van Donge &amp; De Roo Stadion</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>Honingerdijk 110, Rotterdam</t>
+        </is>
+      </c>
+      <c r="AC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD80" t="n">
         <v>3</v>
       </c>
-      <c r="N80" t="n">
-        <v>2</v>
-      </c>
-      <c r="O80" t="n">
-        <v>0</v>
-      </c>
-      <c r="P80" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
-      <c r="R80" t="n">
-        <v>2</v>
-      </c>
-      <c r="S80" t="n">
-        <v>12</v>
-      </c>
-      <c r="T80" t="n">
-        <v>6</v>
-      </c>
-      <c r="U80" t="n">
-        <v>12</v>
-      </c>
-      <c r="V80" t="n">
-        <v>8</v>
-      </c>
-      <c r="W80" t="n">
-        <v>11</v>
-      </c>
-      <c r="X80" t="n">
-        <v>10</v>
-      </c>
-      <c r="Y80" t="n">
-        <v>61</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>39</v>
-      </c>
-      <c r="AA80" t="inlineStr"/>
-      <c r="AB80" t="inlineStr"/>
-      <c r="AC80" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD80" t="n">
-        <v>2</v>
-      </c>
       <c r="AE80" t="n">
-        <v>1.77</v>
+        <v>2.07</v>
       </c>
       <c r="AF80" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="AG80" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="AH80" t="n">
         <v>1.22</v>
       </c>
       <c r="AI80" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AJ80" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="AK80" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL80" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="AM80" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AN80" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AO80" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AP80" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AR80" t="n">
         <v>2.5</v>
       </c>
       <c r="AS80" t="n">
-        <v>3.27</v>
+        <v>3.04</v>
       </c>
       <c r="AT80" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="AU80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX80" t="n">
         <v>0</v>
       </c>
       <c r="AY80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA80" t="n">
         <v>1</v>
       </c>
       <c r="BB80" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="BC80" t="n">
         <v>0</v>
       </c>
       <c r="BD80" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="BE80" t="n">
         <v>0</v>
@@ -38400,130 +38408,130 @@
         <v>1</v>
       </c>
       <c r="BJ80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK80" t="n">
         <v>3</v>
       </c>
-      <c r="BK80" t="n">
-        <v>6</v>
-      </c>
       <c r="BL80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM80" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BN80" t="n">
+        <v>3</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>23</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>59</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>64</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>27</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU80" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV80" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW80" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX80" t="n">
         <v>7</v>
       </c>
-      <c r="BO80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR80" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT80" t="n">
-        <v>4</v>
-      </c>
-      <c r="BU80" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV80" t="n">
-        <v>35</v>
-      </c>
-      <c r="BW80" t="n">
-        <v>12</v>
-      </c>
-      <c r="BX80" t="n">
-        <v>78</v>
-      </c>
-      <c r="BY80" t="n">
-        <v>41</v>
-      </c>
-      <c r="BZ80" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="CA80" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="CB80" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CC80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP80" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>28</v>
-      </c>
-      <c r="CS80" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU80" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV80" t="n">
-        <v>11</v>
-      </c>
-      <c r="CW80" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX80" t="n">
+      <c r="CY80" t="n">
         <v>8</v>
-      </c>
-      <c r="CY80" t="n">
-        <v>10</v>
       </c>
       <c r="CZ80" t="n">
         <v>63</v>
@@ -38538,22 +38546,22 @@
         <v>75</v>
       </c>
       <c r="DD80" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="DE80" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="DF80" t="n">
-        <v>2.25</v>
+        <v>0.75</v>
       </c>
       <c r="DG80" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="DH80" t="n">
-        <v>1.88</v>
+        <v>0.75</v>
       </c>
       <c r="DI80" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="DJ80" t="n">
         <v>38</v>
@@ -38562,22 +38570,22 @@
         <v>25</v>
       </c>
       <c r="DL80" t="n">
-        <v>1.51</v>
+        <v>1.35</v>
       </c>
       <c r="DM80" t="n">
-        <v>1.57</v>
+        <v>1.02</v>
       </c>
       <c r="DN80" t="n">
-        <v>3.08</v>
+        <v>2.37</v>
       </c>
       <c r="DO80" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
       </c>
       <c r="DQ80" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR80" t="b">
         <v>0</v>
@@ -38594,74 +38602,102 @@
       <c r="DV80" t="b">
         <v>0</v>
       </c>
-      <c r="DW80" t="inlineStr"/>
-      <c r="DX80" t="inlineStr"/>
-      <c r="DY80" t="inlineStr"/>
-      <c r="DZ80" t="inlineStr"/>
+      <c r="DW80" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="DX80" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="DY80" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="DZ80" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="EA80" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EB80" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="EC80" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="ED80" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EE80" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EF80" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EG80" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EH80" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="EI80" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EJ80" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EK80" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="EL80" t="inlineStr">
         <is>
-          <t>1.23</t>
-        </is>
-      </c>
-      <c r="EM80" t="inlineStr"/>
-      <c r="EN80" t="inlineStr"/>
-      <c r="EO80" t="inlineStr"/>
-      <c r="EP80" t="inlineStr"/>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EM80" t="inlineStr">
+        <is>
+          <t>2.41</t>
+        </is>
+      </c>
+      <c r="EN80" t="inlineStr">
+        <is>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EO80" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="EP80" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -38679,170 +38715,162 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
         <v>45949.52083333334</v>
       </c>
       <c r="G81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J81" t="n">
+        <v>7</v>
+      </c>
+      <c r="K81" t="n">
         <v>4</v>
       </c>
-      <c r="K81" t="n">
-        <v>2</v>
-      </c>
       <c r="L81" t="n">
+        <v>11</v>
+      </c>
+      <c r="M81" t="n">
+        <v>3</v>
+      </c>
+      <c r="N81" t="n">
+        <v>2</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="n">
+        <v>2</v>
+      </c>
+      <c r="S81" t="n">
+        <v>12</v>
+      </c>
+      <c r="T81" t="n">
         <v>6</v>
       </c>
-      <c r="M81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N81" t="n">
+      <c r="U81" t="n">
+        <v>12</v>
+      </c>
+      <c r="V81" t="n">
+        <v>8</v>
+      </c>
+      <c r="W81" t="n">
+        <v>11</v>
+      </c>
+      <c r="X81" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y81" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z81" t="n">
+        <v>39</v>
+      </c>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="n">
         <v>3</v>
       </c>
-      <c r="O81" t="n">
-        <v>0</v>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q81" t="n">
-        <v>5</v>
-      </c>
-      <c r="R81" t="n">
-        <v>6</v>
-      </c>
-      <c r="S81" t="n">
-        <v>6</v>
-      </c>
-      <c r="T81" t="n">
-        <v>8</v>
-      </c>
-      <c r="U81" t="n">
-        <v>11</v>
-      </c>
-      <c r="V81" t="n">
-        <v>14</v>
-      </c>
-      <c r="W81" t="n">
-        <v>10</v>
-      </c>
-      <c r="X81" t="n">
-        <v>18</v>
-      </c>
-      <c r="Y81" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z81" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>Van Donge &amp; De Roo Stadion</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>Honingerdijk 110, Rotterdam</t>
-        </is>
-      </c>
-      <c r="AC81" t="n">
-        <v>0</v>
-      </c>
       <c r="AD81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE81" t="n">
-        <v>2.07</v>
+        <v>1.77</v>
       </c>
       <c r="AF81" t="n">
-        <v>3.72</v>
+        <v>3.8</v>
       </c>
       <c r="AG81" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="AH81" t="n">
         <v>1.22</v>
       </c>
       <c r="AI81" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AJ81" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="AK81" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL81" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="AM81" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AN81" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AO81" t="n">
-        <v>2.75</v>
+        <v>2.43</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AR81" t="n">
         <v>2.5</v>
       </c>
       <c r="AS81" t="n">
-        <v>3.04</v>
+        <v>3.27</v>
       </c>
       <c r="AT81" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AU81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX81" t="n">
         <v>0</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA81" t="n">
         <v>1</v>
       </c>
       <c r="BB81" t="n">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="BC81" t="n">
         <v>0</v>
       </c>
       <c r="BD81" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="BE81" t="n">
         <v>0</v>
@@ -38860,28 +38888,28 @@
         <v>1</v>
       </c>
       <c r="BJ81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK81" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BL81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM81" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BN81" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BO81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR81" t="n">
         <v>2</v>
@@ -38890,31 +38918,31 @@
         <v>1</v>
       </c>
       <c r="BT81" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU81" t="n">
         <v>1</v>
       </c>
       <c r="BV81" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="BW81" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="BX81" t="n">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="BY81" t="n">
-        <v>64</v>
+        <v>41</v>
       </c>
       <c r="BZ81" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="CA81" t="n">
-        <v>1.47</v>
+        <v>0.73</v>
       </c>
       <c r="CB81" t="n">
-        <v>2.63</v>
+        <v>1.74</v>
       </c>
       <c r="CC81" t="n">
         <v>0</v>
@@ -38941,7 +38969,7 @@
         <v>1</v>
       </c>
       <c r="CK81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL81" t="n">
         <v>0</v>
@@ -38950,7 +38978,7 @@
         <v>0</v>
       </c>
       <c r="CN81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO81" t="n">
         <v>0</v>
@@ -38962,28 +38990,28 @@
         <v>1</v>
       </c>
       <c r="CR81" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="CS81" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="CT81" t="n">
         <v>1</v>
       </c>
       <c r="CU81" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="CV81" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW81" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX81" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY81" t="n">
         <v>10</v>
-      </c>
-      <c r="CW81" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX81" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY81" t="n">
-        <v>8</v>
       </c>
       <c r="CZ81" t="n">
         <v>63</v>
@@ -38998,22 +39026,22 @@
         <v>75</v>
       </c>
       <c r="DD81" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DE81" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="DF81" t="n">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="DG81" t="n">
-        <v>0.75</v>
+        <v>1.5</v>
       </c>
       <c r="DH81" t="n">
-        <v>0.75</v>
+        <v>1.88</v>
       </c>
       <c r="DI81" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="DJ81" t="n">
         <v>38</v>
@@ -39022,22 +39050,22 @@
         <v>25</v>
       </c>
       <c r="DL81" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="DM81" t="n">
-        <v>1.02</v>
+        <v>1.57</v>
       </c>
       <c r="DN81" t="n">
-        <v>2.37</v>
+        <v>3.08</v>
       </c>
       <c r="DO81" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP81" t="b">
         <v>1</v>
       </c>
       <c r="DQ81" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR81" t="b">
         <v>0</v>
@@ -39054,102 +39082,74 @@
       <c r="DV81" t="b">
         <v>0</v>
       </c>
-      <c r="DW81" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="DX81" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="DY81" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="DZ81" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
+      <c r="DW81" t="inlineStr"/>
+      <c r="DX81" t="inlineStr"/>
+      <c r="DY81" t="inlineStr"/>
+      <c r="DZ81" t="inlineStr"/>
       <c r="EA81" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>4.52</t>
         </is>
       </c>
       <c r="EB81" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="EC81" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="ED81" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EE81" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="EF81" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EG81" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="EH81" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EI81" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.27</t>
         </is>
       </c>
       <c r="EJ81" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="EK81" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EL81" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EM81" t="inlineStr">
-        <is>
-          <t>2.41</t>
-        </is>
-      </c>
-      <c r="EN81" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EO81" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
-      <c r="EP81" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="EM81" t="inlineStr"/>
+      <c r="EN81" t="inlineStr"/>
+      <c r="EO81" t="inlineStr"/>
+      <c r="EP81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -42318,7 +42318,7 @@
         <v>100</v>
       </c>
       <c r="DD88" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE88" t="n">
         <v>1.38</v>
@@ -43254,7 +43254,7 @@
         <v>100</v>
       </c>
       <c r="DD90" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE90" t="n">
         <v>0.75</v>
@@ -43287,7 +43287,7 @@
         <v>3.72</v>
       </c>
       <c r="DO90" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP90" t="b">
         <v>1</v>
@@ -45613,7 +45613,7 @@
         <v>2.11</v>
       </c>
       <c r="DE95" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF95" t="n">
         <v>2.4</v>
@@ -46545,7 +46545,7 @@
         <v>1.25</v>
       </c>
       <c r="DE97" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF97" t="n">
         <v>0.75</v>
@@ -46703,40 +46703,40 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
         <v>45963.5625</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H98" t="n">
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K98" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O98" t="n">
         <v>0</v>
@@ -46745,22 +46745,22 @@
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R98" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="S98" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T98" t="n">
         <v>6</v>
       </c>
       <c r="U98" t="n">
+        <v>18</v>
+      </c>
+      <c r="V98" t="n">
         <v>10</v>
-      </c>
-      <c r="V98" t="n">
-        <v>20</v>
       </c>
       <c r="W98" t="n">
         <v>7</v>
@@ -46769,77 +46769,69 @@
         <v>12</v>
       </c>
       <c r="Y98" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Z98" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>Sparta-Stadion Het Kasteel</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>Spartapark Noord 1, Rotterdam</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="AA98" t="inlineStr"/>
+      <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AE98" t="n">
-        <v>4.2</v>
+        <v>2.89</v>
       </c>
       <c r="AF98" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG98" t="n">
-        <v>1.7</v>
+        <v>2.44</v>
       </c>
       <c r="AH98" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AI98" t="n">
-        <v>1.38</v>
+        <v>1.9</v>
       </c>
       <c r="AJ98" t="n">
-        <v>2.15</v>
+        <v>2.95</v>
       </c>
       <c r="AK98" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL98" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AM98" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL98" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM98" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AN98" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AO98" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="AP98" t="n">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AR98" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AS98" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="AT98" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AU98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV98" t="n">
         <v>0</v>
@@ -46848,25 +46840,25 @@
         <v>0</v>
       </c>
       <c r="AX98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY98" t="n">
         <v>1</v>
       </c>
       <c r="AZ98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA98" t="n">
         <v>0</v>
       </c>
       <c r="BB98" t="n">
-        <v>378</v>
+        <v>-1</v>
       </c>
       <c r="BC98" t="n">
         <v>0</v>
       </c>
       <c r="BD98" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="BE98" t="n">
         <v>0</v>
@@ -46881,73 +46873,73 @@
         <v>1</v>
       </c>
       <c r="BI98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BJ98" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="BK98" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM98" t="n">
+        <v>8</v>
+      </c>
+      <c r="BN98" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ98" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR98" t="n">
         <v>3</v>
       </c>
-      <c r="BM98" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN98" t="n">
-        <v>9</v>
-      </c>
-      <c r="BO98" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP98" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ98" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR98" t="n">
-        <v>1</v>
-      </c>
       <c r="BS98" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BT98" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BU98" t="n">
         <v>1</v>
       </c>
       <c r="BV98" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="BW98" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="BX98" t="n">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="BY98" t="n">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="BZ98" t="n">
-        <v>1.15</v>
+        <v>1.93</v>
       </c>
       <c r="CA98" t="n">
-        <v>2.63</v>
+        <v>1.21</v>
       </c>
       <c r="CB98" t="n">
-        <v>3.77</v>
+        <v>3.13</v>
       </c>
       <c r="CC98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD98" t="n">
         <v>0</v>
       </c>
       <c r="CE98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF98" t="n">
         <v>0</v>
@@ -46971,97 +46963,97 @@
         <v>0</v>
       </c>
       <c r="CM98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ98" t="n">
         <v>1</v>
       </c>
       <c r="CR98" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="CS98" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CT98" t="n">
         <v>1</v>
       </c>
       <c r="CU98" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CV98" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CW98" t="n">
         <v>1</v>
       </c>
       <c r="CX98" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="CY98" t="n">
         <v>9</v>
       </c>
       <c r="CZ98" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA98" t="n">
         <v>70</v>
       </c>
-      <c r="DA98" t="n">
+      <c r="DB98" t="n">
+        <v>40</v>
+      </c>
+      <c r="DC98" t="n">
         <v>80</v>
       </c>
-      <c r="DB98" t="n">
+      <c r="DD98" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DE98" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="DF98" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DH98" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DI98" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="DJ98" t="n">
         <v>50</v>
       </c>
-      <c r="DC98" t="n">
-        <v>90</v>
-      </c>
-      <c r="DD98" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DE98" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DF98" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DG98" t="n">
-        <v>2</v>
-      </c>
-      <c r="DH98" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="DI98" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="DJ98" t="n">
+      <c r="DK98" t="n">
         <v>30</v>
       </c>
-      <c r="DK98" t="n">
-        <v>20</v>
-      </c>
       <c r="DL98" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="DM98" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="DN98" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="DO98" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP98" t="b">
         <v>1</v>
       </c>
       <c r="DQ98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR98" t="b">
         <v>0</v>
@@ -47076,80 +47068,104 @@
         <v>0</v>
       </c>
       <c r="DV98" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW98" t="n">
-        <v>12.53</v>
+        <v>10.99</v>
       </c>
       <c r="DX98" t="n">
-        <v>6.3</v>
+        <v>6.54</v>
       </c>
       <c r="DY98" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="DZ98" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA98" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="EB98" t="inlineStr">
         <is>
-          <t>4.24</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="EC98" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="ED98" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EE98" t="inlineStr">
         <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="EF98" t="inlineStr"/>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="EF98" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
       <c r="EG98" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="EH98" t="inlineStr">
         <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EI98" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EJ98" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EK98" t="inlineStr">
+        <is>
+          <t>2.96</t>
+        </is>
+      </c>
+      <c r="EL98" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="EM98" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EN98" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EO98" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="EI98" t="inlineStr"/>
-      <c r="EJ98" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EK98" t="inlineStr">
-        <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EL98" t="inlineStr">
-        <is>
-          <t>1.16</t>
-        </is>
-      </c>
-      <c r="EM98" t="inlineStr"/>
-      <c r="EN98" t="inlineStr"/>
-      <c r="EO98" t="inlineStr"/>
-      <c r="EP98" t="inlineStr"/>
+      <c r="EP98" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -47167,64 +47183,64 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
         <v>45963.5625</v>
       </c>
       <c r="G99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
       </c>
       <c r="I99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J99" t="n">
+        <v>6</v>
+      </c>
+      <c r="K99" t="n">
+        <v>9</v>
+      </c>
+      <c r="L99" t="n">
+        <v>15</v>
+      </c>
+      <c r="M99" t="n">
+        <v>1</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>3</v>
+      </c>
+      <c r="R99" t="n">
+        <v>14</v>
+      </c>
+      <c r="S99" t="n">
         <v>7</v>
-      </c>
-      <c r="K99" t="n">
-        <v>3</v>
-      </c>
-      <c r="L99" t="n">
-        <v>10</v>
-      </c>
-      <c r="M99" t="n">
-        <v>2</v>
-      </c>
-      <c r="N99" t="n">
-        <v>4</v>
-      </c>
-      <c r="O99" t="n">
-        <v>0</v>
-      </c>
-      <c r="P99" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>7</v>
-      </c>
-      <c r="R99" t="n">
-        <v>4</v>
-      </c>
-      <c r="S99" t="n">
-        <v>11</v>
       </c>
       <c r="T99" t="n">
         <v>6</v>
       </c>
       <c r="U99" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="V99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="W99" t="n">
         <v>7</v>
@@ -47233,69 +47249,77 @@
         <v>12</v>
       </c>
       <c r="Y99" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="Z99" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA99" t="inlineStr"/>
-      <c r="AB99" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>Sparta-Stadion Het Kasteel</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>Spartapark Noord 1, Rotterdam</t>
+        </is>
+      </c>
       <c r="AC99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD99" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE99" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AF99" t="n">
         <v>4</v>
       </c>
-      <c r="AE99" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AF99" t="n">
-        <v>3</v>
-      </c>
       <c r="AG99" t="n">
-        <v>2.44</v>
+        <v>1.7</v>
       </c>
       <c r="AH99" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AI99" t="n">
-        <v>1.9</v>
+        <v>1.38</v>
       </c>
       <c r="AJ99" t="n">
-        <v>2.95</v>
+        <v>2.15</v>
       </c>
       <c r="AK99" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL99" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM99" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AP99" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ99" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR99" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS99" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AT99" t="n">
         <v>1.62</v>
       </c>
-      <c r="AL99" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM99" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN99" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AO99" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AP99" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AQ99" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR99" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AS99" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AT99" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AU99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV99" t="n">
         <v>0</v>
@@ -47304,25 +47328,25 @@
         <v>0</v>
       </c>
       <c r="AX99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY99" t="n">
         <v>1</v>
       </c>
       <c r="AZ99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA99" t="n">
         <v>0</v>
       </c>
       <c r="BB99" t="n">
-        <v>-1</v>
+        <v>378</v>
       </c>
       <c r="BC99" t="n">
         <v>0</v>
       </c>
       <c r="BD99" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BE99" t="n">
         <v>0</v>
@@ -47337,73 +47361,73 @@
         <v>1</v>
       </c>
       <c r="BI99" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BJ99" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BK99" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BM99" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BN99" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BO99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ99" t="n">
         <v>1</v>
       </c>
       <c r="BR99" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BS99" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT99" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU99" t="n">
         <v>1</v>
       </c>
       <c r="BV99" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="BW99" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="BX99" t="n">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="BY99" t="n">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="BZ99" t="n">
-        <v>1.93</v>
+        <v>1.15</v>
       </c>
       <c r="CA99" t="n">
-        <v>1.21</v>
+        <v>2.63</v>
       </c>
       <c r="CB99" t="n">
-        <v>3.13</v>
+        <v>3.77</v>
       </c>
       <c r="CC99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD99" t="n">
         <v>0</v>
       </c>
       <c r="CE99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF99" t="n">
         <v>0</v>
@@ -47427,88 +47451,88 @@
         <v>0</v>
       </c>
       <c r="CM99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ99" t="n">
         <v>1</v>
       </c>
       <c r="CR99" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="CS99" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="CT99" t="n">
         <v>1</v>
       </c>
       <c r="CU99" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="CV99" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CW99" t="n">
         <v>1</v>
       </c>
       <c r="CX99" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="CY99" t="n">
         <v>9</v>
       </c>
       <c r="CZ99" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA99" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB99" t="n">
         <v>50</v>
       </c>
-      <c r="DA99" t="n">
-        <v>70</v>
-      </c>
-      <c r="DB99" t="n">
-        <v>40</v>
-      </c>
       <c r="DC99" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="DD99" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="DE99" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="DF99" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="DG99" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="DH99" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="DI99" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="DJ99" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="DK99" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="DL99" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="DM99" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="DN99" t="n">
-        <v>3.29</v>
+        <v>3.1</v>
       </c>
       <c r="DO99" t="n">
         <v>17</v>
@@ -47517,7 +47541,7 @@
         <v>1</v>
       </c>
       <c r="DQ99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR99" t="b">
         <v>0</v>
@@ -47532,104 +47556,80 @@
         <v>0</v>
       </c>
       <c r="DV99" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW99" t="n">
-        <v>10.99</v>
+        <v>12.53</v>
       </c>
       <c r="DX99" t="n">
-        <v>6.54</v>
+        <v>6.3</v>
       </c>
       <c r="DY99" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="DZ99" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="EA99" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EB99" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>4.24</t>
         </is>
       </c>
       <c r="EC99" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="ED99" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EE99" t="inlineStr">
         <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="EF99" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EF99" t="inlineStr"/>
       <c r="EG99" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EH99" t="inlineStr">
         <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EI99" t="inlineStr"/>
+      <c r="EJ99" t="inlineStr">
+        <is>
           <t>1.49</t>
         </is>
       </c>
-      <c r="EI99" t="inlineStr">
-        <is>
-          <t>3.32</t>
-        </is>
-      </c>
-      <c r="EJ99" t="inlineStr">
-        <is>
-          <t>1.81</t>
-        </is>
-      </c>
       <c r="EK99" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EL99" t="inlineStr">
         <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="EM99" t="inlineStr">
-        <is>
-          <t>2.12</t>
-        </is>
-      </c>
-      <c r="EN99" t="inlineStr">
-        <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EO99" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EP99" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="EM99" t="inlineStr"/>
+      <c r="EN99" t="inlineStr"/>
+      <c r="EO99" t="inlineStr"/>
+      <c r="EP99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -48446,7 +48446,7 @@
         <v>100</v>
       </c>
       <c r="DD101" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE101" t="n">
         <v>1</v>
@@ -51690,7 +51690,7 @@
         <v>100</v>
       </c>
       <c r="DD108" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE108" t="n">
         <v>3</v>
@@ -51723,7 +51723,7 @@
         <v>4.01</v>
       </c>
       <c r="DO108" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP108" t="b">
         <v>1</v>
@@ -53123,7 +53123,7 @@
         <v>3.17</v>
       </c>
       <c r="DO111" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="DP111" t="b">
         <v>1</v>
@@ -55003,7 +55003,7 @@
         <v>3.77</v>
       </c>
       <c r="DO115" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP115" t="b">
         <v>1</v>
@@ -55123,162 +55123,170 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Telstar</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>NEC</t>
         </is>
       </c>
       <c r="F116" s="2" t="n">
         <v>45984.5625</v>
       </c>
       <c r="G116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H116" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J116" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K116" t="n">
+        <v>6</v>
+      </c>
+      <c r="L116" t="n">
+        <v>13</v>
+      </c>
+      <c r="M116" t="n">
+        <v>1</v>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>5</v>
+      </c>
+      <c r="R116" t="n">
+        <v>12</v>
+      </c>
+      <c r="S116" t="n">
+        <v>14</v>
+      </c>
+      <c r="T116" t="n">
+        <v>10</v>
+      </c>
+      <c r="U116" t="n">
+        <v>19</v>
+      </c>
+      <c r="V116" t="n">
+        <v>22</v>
+      </c>
+      <c r="W116" t="n">
         <v>8</v>
       </c>
-      <c r="L116" t="n">
-        <v>9</v>
-      </c>
-      <c r="M116" t="n">
-        <v>2</v>
-      </c>
-      <c r="N116" t="n">
-        <v>2</v>
-      </c>
-      <c r="O116" t="n">
-        <v>0</v>
-      </c>
-      <c r="P116" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q116" t="n">
-        <v>3</v>
-      </c>
-      <c r="R116" t="n">
-        <v>3</v>
-      </c>
-      <c r="S116" t="n">
-        <v>7</v>
-      </c>
-      <c r="T116" t="n">
-        <v>14</v>
-      </c>
-      <c r="U116" t="n">
-        <v>10</v>
-      </c>
-      <c r="V116" t="n">
-        <v>17</v>
-      </c>
-      <c r="W116" t="n">
-        <v>10</v>
-      </c>
       <c r="X116" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y116" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="Z116" t="n">
-        <v>58</v>
-      </c>
-      <c r="AA116" t="inlineStr"/>
-      <c r="AB116" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Stadion Feijenoord</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>Van Zandvlietplein 1, Rotterdam</t>
+        </is>
+      </c>
       <c r="AC116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD116" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE116" t="n">
-        <v>3.35</v>
+        <v>1.43</v>
       </c>
       <c r="AF116" t="n">
-        <v>3.58</v>
+        <v>5.2</v>
       </c>
       <c r="AG116" t="n">
-        <v>2.11</v>
+        <v>6.8</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AI116" t="n">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AJ116" t="n">
-        <v>2.71</v>
+        <v>2</v>
       </c>
       <c r="AK116" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL116" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AM116" t="n">
         <v>1.4</v>
       </c>
       <c r="AN116" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AO116" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AP116" t="n">
-        <v>2.14</v>
+        <v>1.95</v>
       </c>
       <c r="AQ116" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AR116" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="AS116" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AT116" t="n">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="AU116" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX116" t="n">
         <v>1</v>
       </c>
       <c r="AY116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AZ116" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BA116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB116" t="n">
-        <v>-1</v>
+        <v>379</v>
       </c>
       <c r="BC116" t="n">
         <v>0</v>
       </c>
       <c r="BD116" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="BE116" t="n">
         <v>0</v>
@@ -55293,178 +55301,178 @@
         <v>1</v>
       </c>
       <c r="BI116" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BJ116" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BK116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BL116" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BM116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BN116" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS116" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT116" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU116" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV116" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW116" t="n">
+        <v>27</v>
+      </c>
+      <c r="BX116" t="n">
+        <v>106</v>
+      </c>
+      <c r="BY116" t="n">
+        <v>77</v>
+      </c>
+      <c r="BZ116" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CA116" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CB116" t="n">
+        <v>4.34</v>
+      </c>
+      <c r="CC116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP116" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR116" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS116" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU116" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV116" t="n">
+        <v>8</v>
+      </c>
+      <c r="CW116" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX116" t="n">
         <v>4</v>
       </c>
-      <c r="BO116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR116" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT116" t="n">
-        <v>3</v>
-      </c>
-      <c r="BU116" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV116" t="n">
-        <v>33</v>
-      </c>
-      <c r="BW116" t="n">
-        <v>60</v>
-      </c>
-      <c r="BX116" t="n">
-        <v>91</v>
-      </c>
-      <c r="BY116" t="n">
-        <v>123</v>
-      </c>
-      <c r="BZ116" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="CA116" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CB116" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CC116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN116" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CP116" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR116" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS116" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU116" t="n">
-        <v>10</v>
-      </c>
-      <c r="CV116" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW116" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX116" t="n">
-        <v>10</v>
-      </c>
       <c r="CY116" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="CZ116" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="DA116" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="DB116" t="n">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="DC116" t="n">
         <v>100</v>
       </c>
       <c r="DD116" t="n">
-        <v>0.78</v>
+        <v>2.11</v>
       </c>
       <c r="DE116" t="n">
-        <v>0.75</v>
+        <v>1.33</v>
       </c>
       <c r="DF116" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG116" t="n">
         <v>0.83</v>
       </c>
-      <c r="DG116" t="n">
-        <v>0.6</v>
-      </c>
       <c r="DH116" t="n">
-        <v>0.75</v>
+        <v>2.33</v>
       </c>
       <c r="DI116" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="DJ116" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="DK116" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="DL116" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="DM116" t="n">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="DN116" t="n">
-        <v>3.41</v>
+        <v>4</v>
       </c>
       <c r="DO116" t="n">
         <v>17</v>
@@ -55476,29 +55484,29 @@
         <v>1</v>
       </c>
       <c r="DR116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU116" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV116" t="b">
         <v>1</v>
       </c>
       <c r="DW116" t="n">
-        <v>4.06</v>
+        <v>3.47</v>
       </c>
       <c r="DX116" t="n">
-        <v>9.84</v>
+        <v>7.56</v>
       </c>
       <c r="DY116" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="DZ116" t="inlineStr">
@@ -55508,73 +55516,65 @@
       </c>
       <c r="EA116" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="EB116" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="EC116" t="inlineStr">
         <is>
-          <t>3.73</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="ED116" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EE116" t="inlineStr">
         <is>
-          <t>2.24</t>
-        </is>
-      </c>
-      <c r="EF116" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
+          <t>2.52</t>
+        </is>
+      </c>
+      <c r="EF116" t="inlineStr"/>
       <c r="EG116" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EH116" t="inlineStr">
         <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EI116" t="inlineStr">
-        <is>
-          <t>3.34</t>
-        </is>
-      </c>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EI116" t="inlineStr"/>
       <c r="EJ116" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="EK116" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="EL116" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="EM116" t="inlineStr"/>
       <c r="EN116" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="EO116" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EP116" t="inlineStr"/>
@@ -55595,170 +55595,162 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Telstar</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>NEC</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F117" s="2" t="n">
         <v>45984.5625</v>
       </c>
       <c r="G117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J117" t="n">
+        <v>1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>8</v>
+      </c>
+      <c r="L117" t="n">
+        <v>9</v>
+      </c>
+      <c r="M117" t="n">
+        <v>2</v>
+      </c>
+      <c r="N117" t="n">
+        <v>2</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>3</v>
+      </c>
+      <c r="R117" t="n">
+        <v>3</v>
+      </c>
+      <c r="S117" t="n">
         <v>7</v>
       </c>
-      <c r="K117" t="n">
-        <v>6</v>
-      </c>
-      <c r="L117" t="n">
-        <v>13</v>
-      </c>
-      <c r="M117" t="n">
-        <v>1</v>
-      </c>
-      <c r="N117" t="n">
-        <v>1</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
-        <v>5</v>
-      </c>
-      <c r="R117" t="n">
-        <v>12</v>
-      </c>
-      <c r="S117" t="n">
+      <c r="T117" t="n">
         <v>14</v>
       </c>
-      <c r="T117" t="n">
+      <c r="U117" t="n">
         <v>10</v>
       </c>
-      <c r="U117" t="n">
-        <v>19</v>
-      </c>
       <c r="V117" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="W117" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X117" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="Y117" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="Z117" t="n">
-        <v>45</v>
-      </c>
-      <c r="AA117" t="inlineStr">
-        <is>
-          <t>Stadion Feijenoord</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>Van Zandvlietplein 1, Rotterdam</t>
-        </is>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="AA117" t="inlineStr"/>
+      <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.43</v>
+        <v>3.35</v>
       </c>
       <c r="AF117" t="n">
-        <v>5.2</v>
+        <v>3.58</v>
       </c>
       <c r="AG117" t="n">
-        <v>6.8</v>
+        <v>2.11</v>
       </c>
       <c r="AH117" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AI117" t="n">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AJ117" t="n">
-        <v>2</v>
+        <v>2.71</v>
       </c>
       <c r="AK117" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL117" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AM117" t="n">
         <v>1.4</v>
       </c>
       <c r="AN117" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AO117" t="n">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="AQ117" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AR117" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="AS117" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AT117" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="AU117" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX117" t="n">
         <v>1</v>
       </c>
       <c r="AY117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AZ117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB117" t="n">
-        <v>379</v>
+        <v>-1</v>
       </c>
       <c r="BC117" t="n">
         <v>0</v>
       </c>
       <c r="BD117" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="BE117" t="n">
         <v>0</v>
@@ -55773,64 +55765,64 @@
         <v>1</v>
       </c>
       <c r="BI117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN117" t="n">
         <v>4</v>
       </c>
-      <c r="BJ117" t="n">
-        <v>2</v>
-      </c>
-      <c r="BK117" t="n">
+      <c r="BO117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT117" t="n">
         <v>3</v>
       </c>
-      <c r="BL117" t="n">
-        <v>4</v>
-      </c>
-      <c r="BM117" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN117" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ117" t="n">
-        <v>1</v>
-      </c>
-      <c r="BR117" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS117" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT117" t="n">
-        <v>2</v>
-      </c>
       <c r="BU117" t="n">
         <v>1</v>
       </c>
       <c r="BV117" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="BW117" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="BX117" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="BY117" t="n">
-        <v>77</v>
+        <v>123</v>
       </c>
       <c r="BZ117" t="n">
-        <v>1.92</v>
+        <v>1.09</v>
       </c>
       <c r="CA117" t="n">
-        <v>2.42</v>
+        <v>1.72</v>
       </c>
       <c r="CB117" t="n">
-        <v>4.34</v>
+        <v>2.81</v>
       </c>
       <c r="CC117" t="n">
         <v>0</v>
@@ -55863,13 +55855,13 @@
         <v>0</v>
       </c>
       <c r="CM117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CP117" t="n">
         <v>0</v>
@@ -55878,73 +55870,73 @@
         <v>1</v>
       </c>
       <c r="CR117" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="CS117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="CT117" t="n">
         <v>1</v>
       </c>
       <c r="CU117" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="CV117" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="CW117" t="n">
         <v>1</v>
       </c>
       <c r="CX117" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="CY117" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="CZ117" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="DA117" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="DB117" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="DC117" t="n">
         <v>100</v>
       </c>
       <c r="DD117" t="n">
-        <v>2.11</v>
+        <v>0.78</v>
       </c>
       <c r="DE117" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DF117" t="n">
-        <v>2.5</v>
+        <v>0.83</v>
       </c>
       <c r="DG117" t="n">
-        <v>0.83</v>
+        <v>0.6</v>
       </c>
       <c r="DH117" t="n">
-        <v>2.33</v>
+        <v>0.75</v>
       </c>
       <c r="DI117" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="DJ117" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="DK117" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="DL117" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="DM117" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="DN117" t="n">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="DO117" t="n">
         <v>17</v>
@@ -55956,29 +55948,29 @@
         <v>1</v>
       </c>
       <c r="DR117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV117" t="b">
         <v>1</v>
       </c>
       <c r="DW117" t="n">
-        <v>3.47</v>
+        <v>4.06</v>
       </c>
       <c r="DX117" t="n">
-        <v>7.56</v>
+        <v>9.84</v>
       </c>
       <c r="DY117" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="DZ117" t="inlineStr">
@@ -55988,65 +55980,73 @@
       </c>
       <c r="EA117" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EB117" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="EC117" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>3.73</t>
         </is>
       </c>
       <c r="ED117" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EE117" t="inlineStr">
         <is>
-          <t>2.52</t>
-        </is>
-      </c>
-      <c r="EF117" t="inlineStr"/>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="EF117" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
       <c r="EG117" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="EH117" t="inlineStr">
         <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="EI117" t="inlineStr"/>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EI117" t="inlineStr">
+        <is>
+          <t>3.34</t>
+        </is>
+      </c>
       <c r="EJ117" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="EK117" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="EL117" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="EM117" t="inlineStr"/>
       <c r="EN117" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EO117" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP117" t="inlineStr"/>
@@ -56381,7 +56381,7 @@
         <v>1.75</v>
       </c>
       <c r="DE118" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF118" t="n">
         <v>1.67</v>
@@ -58745,7 +58745,7 @@
         <v>2.38</v>
       </c>
       <c r="DE123" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF123" t="n">
         <v>2.17</v>
@@ -60138,7 +60138,7 @@
         <v>77</v>
       </c>
       <c r="DD126" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE126" t="n">
         <v>1.44</v>
@@ -60171,7 +60171,7 @@
         <v>4.07</v>
       </c>
       <c r="DO126" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP126" t="b">
         <v>1</v>
@@ -62993,7 +62993,7 @@
         <v>2.11</v>
       </c>
       <c r="DE132" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF132" t="n">
         <v>2.14</v>
@@ -64422,7 +64422,7 @@
         <v>86</v>
       </c>
       <c r="DD135" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DE135" t="n">
         <v>0.67</v>
@@ -64455,7 +64455,7 @@
         <v>3.14</v>
       </c>
       <c r="DO135" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP135" t="b">
         <v>1</v>
@@ -65833,7 +65833,7 @@
         <v>1.75</v>
       </c>
       <c r="DE138" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF138" t="n">
         <v>1.57</v>
@@ -68178,7 +68178,7 @@
         <v>73</v>
       </c>
       <c r="DD143" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DE143" t="n">
         <v>0.67</v>
@@ -69585,7 +69585,7 @@
         <v>1.33</v>
       </c>
       <c r="DE146" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DF146" t="n">
         <v>1.13</v>
@@ -71127,12 +71127,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Feyenoord</t>
+          <t>Go Ahead Eagles</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Twente</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F150" s="2" t="n">
@@ -71148,134 +71148,134 @@
         <v>2</v>
       </c>
       <c r="J150" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K150" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="L150" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="M150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P150" t="n">
         <v>0</v>
       </c>
       <c r="Q150" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R150" t="n">
+        <v>3</v>
+      </c>
+      <c r="S150" t="n">
+        <v>5</v>
+      </c>
+      <c r="T150" t="n">
         <v>11</v>
       </c>
-      <c r="S150" t="n">
-        <v>6</v>
-      </c>
-      <c r="T150" t="n">
-        <v>18</v>
-      </c>
       <c r="U150" t="n">
+        <v>8</v>
+      </c>
+      <c r="V150" t="n">
+        <v>14</v>
+      </c>
+      <c r="W150" t="n">
         <v>10</v>
       </c>
-      <c r="V150" t="n">
-        <v>29</v>
-      </c>
-      <c r="W150" t="n">
-        <v>15</v>
-      </c>
       <c r="X150" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y150" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z150" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>Stadion Feijenoord</t>
+          <t>De Adelaarshorst</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>Van Zandvlietplein 1, Rotterdam</t>
+          <t>Vetkampstraat 1, Deventer</t>
         </is>
       </c>
       <c r="AC150" t="n">
         <v>2</v>
       </c>
       <c r="AD150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE150" t="n">
-        <v>1.6</v>
+        <v>3.02</v>
       </c>
       <c r="AF150" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="AG150" t="n">
-        <v>4.9</v>
+        <v>2.31</v>
       </c>
       <c r="AH150" t="n">
         <v>1.18</v>
       </c>
       <c r="AI150" t="n">
-        <v>1.51</v>
+        <v>1.73</v>
       </c>
       <c r="AJ150" t="n">
-        <v>2.2</v>
+        <v>2.57</v>
       </c>
       <c r="AK150" t="n">
         <v>1.57</v>
       </c>
       <c r="AL150" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AM150" t="n">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AN150" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AO150" t="n">
-        <v>2.28</v>
+        <v>2.8</v>
       </c>
       <c r="AP150" t="n">
-        <v>1.88</v>
+        <v>2.14</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AR150" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="AS150" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AT150" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AU150" t="n">
         <v>2</v>
       </c>
       <c r="AV150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ150" t="n">
         <v>1</v>
@@ -71290,7 +71290,7 @@
         <v>0</v>
       </c>
       <c r="BD150" t="n">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="BE150" t="n">
         <v>0</v>
@@ -71308,25 +71308,25 @@
         <v>1</v>
       </c>
       <c r="BJ150" t="n">
+        <v>5</v>
+      </c>
+      <c r="BK150" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL150" t="n">
+        <v>3</v>
+      </c>
+      <c r="BM150" t="n">
         <v>6</v>
       </c>
-      <c r="BK150" t="n">
-        <v>6</v>
-      </c>
-      <c r="BL150" t="n">
-        <v>6</v>
-      </c>
-      <c r="BM150" t="n">
-        <v>7</v>
-      </c>
       <c r="BN150" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="BO150" t="n">
         <v>0</v>
       </c>
       <c r="BP150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ150" t="n">
         <v>2</v>
@@ -71335,7 +71335,7 @@
         <v>0</v>
       </c>
       <c r="BS150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT150" t="n">
         <v>2</v>
@@ -71344,25 +71344,25 @@
         <v>1</v>
       </c>
       <c r="BV150" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW150" t="n">
-        <v>81</v>
+        <v>40</v>
       </c>
       <c r="BX150" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="BY150" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="BZ150" t="n">
-        <v>1.18</v>
+        <v>1</v>
       </c>
       <c r="CA150" t="n">
-        <v>3.17</v>
+        <v>1.39</v>
       </c>
       <c r="CB150" t="n">
-        <v>4.35</v>
+        <v>2.39</v>
       </c>
       <c r="CC150" t="n">
         <v>0</v>
@@ -71398,7 +71398,7 @@
         <v>0</v>
       </c>
       <c r="CN150" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO150" t="n">
         <v>0</v>
@@ -71410,73 +71410,73 @@
         <v>1</v>
       </c>
       <c r="CR150" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="CS150" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU150" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV150" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW150" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX150" t="n">
         <v>11</v>
       </c>
-      <c r="CT150" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU150" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV150" t="n">
-        <v>15</v>
-      </c>
-      <c r="CW150" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX150" t="n">
-        <v>8</v>
-      </c>
       <c r="CY150" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="CZ150" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="DA150" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="DB150" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="DC150" t="n">
         <v>75</v>
       </c>
       <c r="DD150" t="n">
-        <v>2.11</v>
+        <v>1.63</v>
       </c>
       <c r="DE150" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="DF150" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="DG150" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="DH150" t="n">
-        <v>2.13</v>
+        <v>1.13</v>
       </c>
       <c r="DI150" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="DJ150" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="DK150" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="DL150" t="n">
-        <v>2.17</v>
+        <v>1.58</v>
       </c>
       <c r="DM150" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="DN150" t="n">
-        <v>4</v>
+        <v>3.31</v>
       </c>
       <c r="DO150" t="n">
         <v>17</v>
@@ -71503,93 +71503,77 @@
         <v>1</v>
       </c>
       <c r="DW150" t="n">
-        <v>8.56</v>
+        <v>9.56</v>
       </c>
       <c r="DX150" t="n">
-        <v>5.26</v>
+        <v>4.09</v>
       </c>
       <c r="DY150" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="DZ150" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>98%</t>
         </is>
       </c>
       <c r="EA150" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EB150" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="EC150" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="ED150" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="EE150" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="EF150" t="inlineStr"/>
       <c r="EG150" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="EH150" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EI150" t="inlineStr"/>
       <c r="EJ150" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="EK150" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.92</t>
         </is>
       </c>
       <c r="EL150" t="inlineStr">
         <is>
-          <t>1.19</t>
-        </is>
-      </c>
-      <c r="EM150" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="EN150" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EO150" t="inlineStr">
-        <is>
-          <t>2.02</t>
-        </is>
-      </c>
-      <c r="EP150" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
+          <t>1.24</t>
+        </is>
+      </c>
+      <c r="EM150" t="inlineStr"/>
+      <c r="EN150" t="inlineStr"/>
+      <c r="EO150" t="inlineStr"/>
+      <c r="EP150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -71607,12 +71591,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Go Ahead Eagles</t>
+          <t>Feyenoord</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Twente</t>
         </is>
       </c>
       <c r="F151" s="2" t="n">
@@ -71628,134 +71612,134 @@
         <v>2</v>
       </c>
       <c r="J151" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K151" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L151" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="M151" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P151" t="n">
         <v>0</v>
       </c>
       <c r="Q151" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R151" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="S151" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T151" t="n">
+        <v>18</v>
+      </c>
+      <c r="U151" t="n">
+        <v>10</v>
+      </c>
+      <c r="V151" t="n">
+        <v>29</v>
+      </c>
+      <c r="W151" t="n">
+        <v>15</v>
+      </c>
+      <c r="X151" t="n">
         <v>11</v>
       </c>
-      <c r="U151" t="n">
-        <v>8</v>
-      </c>
-      <c r="V151" t="n">
-        <v>14</v>
-      </c>
-      <c r="W151" t="n">
-        <v>10</v>
-      </c>
-      <c r="X151" t="n">
-        <v>13</v>
-      </c>
       <c r="Y151" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z151" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>De Adelaarshorst</t>
+          <t>Stadion Feijenoord</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>Vetkampstraat 1, Deventer</t>
+          <t>Van Zandvlietplein 1, Rotterdam</t>
         </is>
       </c>
       <c r="AC151" t="n">
         <v>2</v>
       </c>
       <c r="AD151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE151" t="n">
-        <v>3.02</v>
+        <v>1.6</v>
       </c>
       <c r="AF151" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="AG151" t="n">
-        <v>2.31</v>
+        <v>4.9</v>
       </c>
       <c r="AH151" t="n">
         <v>1.18</v>
       </c>
       <c r="AI151" t="n">
-        <v>1.73</v>
+        <v>1.51</v>
       </c>
       <c r="AJ151" t="n">
-        <v>2.57</v>
+        <v>2.2</v>
       </c>
       <c r="AK151" t="n">
         <v>1.57</v>
       </c>
       <c r="AL151" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AM151" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AN151" t="n">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AO151" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="AP151" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="AQ151" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR151" t="n">
-        <v>2.41</v>
+        <v>2.12</v>
       </c>
       <c r="AS151" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AT151" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AU151" t="n">
         <v>2</v>
       </c>
       <c r="AV151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX151" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ151" t="n">
         <v>1</v>
@@ -71770,7 +71754,7 @@
         <v>0</v>
       </c>
       <c r="BD151" t="n">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="BE151" t="n">
         <v>0</v>
@@ -71788,175 +71772,175 @@
         <v>1</v>
       </c>
       <c r="BJ151" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BK151" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BL151" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BM151" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN151" t="n">
+        <v>12</v>
+      </c>
+      <c r="BO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS151" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT151" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU151" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV151" t="n">
+        <v>36</v>
+      </c>
+      <c r="BW151" t="n">
+        <v>81</v>
+      </c>
+      <c r="BX151" t="n">
+        <v>88</v>
+      </c>
+      <c r="BY151" t="n">
+        <v>109</v>
+      </c>
+      <c r="BZ151" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CA151" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CB151" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="CC151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP151" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR151" t="n">
+        <v>16</v>
+      </c>
+      <c r="CS151" t="n">
+        <v>11</v>
+      </c>
+      <c r="CT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU151" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV151" t="n">
+        <v>15</v>
+      </c>
+      <c r="CW151" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX151" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY151" t="n">
         <v>6</v>
       </c>
-      <c r="BN151" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP151" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ151" t="n">
-        <v>2</v>
-      </c>
-      <c r="BR151" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS151" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT151" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU151" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV151" t="n">
-        <v>38</v>
-      </c>
-      <c r="BW151" t="n">
-        <v>40</v>
-      </c>
-      <c r="BX151" t="n">
-        <v>87</v>
-      </c>
-      <c r="BY151" t="n">
-        <v>112</v>
-      </c>
-      <c r="BZ151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CA151" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CB151" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CC151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN151" t="n">
-        <v>2</v>
-      </c>
-      <c r="CO151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP151" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR151" t="n">
-        <v>21</v>
-      </c>
-      <c r="CS151" t="n">
-        <v>20</v>
-      </c>
-      <c r="CT151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU151" t="n">
-        <v>13</v>
-      </c>
-      <c r="CV151" t="n">
-        <v>10</v>
-      </c>
-      <c r="CW151" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX151" t="n">
-        <v>11</v>
-      </c>
-      <c r="CY151" t="n">
-        <v>9</v>
-      </c>
       <c r="CZ151" t="n">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="DA151" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="DB151" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="DC151" t="n">
         <v>75</v>
       </c>
       <c r="DD151" t="n">
-        <v>1.63</v>
+        <v>2.11</v>
       </c>
       <c r="DE151" t="n">
-        <v>1.44</v>
+        <v>1.22</v>
       </c>
       <c r="DF151" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="DG151" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DH151" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DI151" t="n">
         <v>1.5</v>
       </c>
-      <c r="DH151" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="DI151" t="n">
-        <v>1.63</v>
-      </c>
       <c r="DJ151" t="n">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="DK151" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="DL151" t="n">
-        <v>1.58</v>
+        <v>2.17</v>
       </c>
       <c r="DM151" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="DN151" t="n">
-        <v>3.31</v>
+        <v>4</v>
       </c>
       <c r="DO151" t="n">
         <v>17</v>
@@ -71983,77 +71967,93 @@
         <v>1</v>
       </c>
       <c r="DW151" t="n">
-        <v>9.56</v>
+        <v>8.56</v>
       </c>
       <c r="DX151" t="n">
-        <v>4.09</v>
+        <v>5.26</v>
       </c>
       <c r="DY151" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="DZ151" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA151" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>3.72</t>
         </is>
       </c>
       <c r="EB151" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="EC151" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="ED151" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="EE151" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="EF151" t="inlineStr"/>
       <c r="EG151" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EH151" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EI151" t="inlineStr"/>
       <c r="EJ151" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EK151" t="inlineStr">
         <is>
-          <t>2.92</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="EL151" t="inlineStr">
         <is>
-          <t>1.24</t>
-        </is>
-      </c>
-      <c r="EM151" t="inlineStr"/>
-      <c r="EN151" t="inlineStr"/>
-      <c r="EO151" t="inlineStr"/>
-      <c r="EP151" t="inlineStr"/>
+          <t>1.19</t>
+        </is>
+      </c>
+      <c r="EM151" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="EN151" t="inlineStr">
+        <is>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EO151" t="inlineStr">
+        <is>
+          <t>2.02</t>
+        </is>
+      </c>
+      <c r="EP151" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -72423,7 +72423,7 @@
         <v>3.45</v>
       </c>
       <c r="DO152" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="DP152" t="b">
         <v>1</v>
@@ -72990,6 +72990,958 @@
         </is>
       </c>
       <c r="EP153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Netherlands_Eredivisie_2025-2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>18</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Volendam</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>46032.64583333334</v>
+      </c>
+      <c r="G154" t="n">
+        <v>1</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" t="n">
+        <v>1</v>
+      </c>
+      <c r="J154" t="n">
+        <v>7</v>
+      </c>
+      <c r="K154" t="n">
+        <v>2</v>
+      </c>
+      <c r="L154" t="n">
+        <v>9</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="n">
+        <v>1</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q154" t="n">
+        <v>8</v>
+      </c>
+      <c r="R154" t="n">
+        <v>2</v>
+      </c>
+      <c r="S154" t="n">
+        <v>9</v>
+      </c>
+      <c r="T154" t="n">
+        <v>5</v>
+      </c>
+      <c r="U154" t="n">
+        <v>17</v>
+      </c>
+      <c r="V154" t="n">
+        <v>7</v>
+      </c>
+      <c r="W154" t="n">
+        <v>10</v>
+      </c>
+      <c r="X154" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y154" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z154" t="n">
+        <v>51</v>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>AFAS Stadion</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>Stadionweg 1, Alkmaar</t>
+        </is>
+      </c>
+      <c r="AC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE154" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AF154" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH154" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI154" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ154" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK154" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL154" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM154" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN154" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AP154" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AQ154" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AR154" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AS154" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AT154" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AU154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY154" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB154" t="n">
+        <v>378</v>
+      </c>
+      <c r="BC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD154" t="n">
+        <v>75</v>
+      </c>
+      <c r="BE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF154" t="n">
+        <v>18202</v>
+      </c>
+      <c r="BG154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI154" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ154" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK154" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM154" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN154" t="n">
+        <v>4</v>
+      </c>
+      <c r="BO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT154" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU154" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV154" t="n">
+        <v>61</v>
+      </c>
+      <c r="BW154" t="n">
+        <v>45</v>
+      </c>
+      <c r="BX154" t="n">
+        <v>101</v>
+      </c>
+      <c r="BY154" t="n">
+        <v>106</v>
+      </c>
+      <c r="BZ154" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CA154" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="CB154" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CC154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CL154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP154" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR154" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS154" t="n">
+        <v>22</v>
+      </c>
+      <c r="CT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU154" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV154" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW154" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX154" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY154" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ154" t="n">
+        <v>88</v>
+      </c>
+      <c r="DA154" t="n">
+        <v>94</v>
+      </c>
+      <c r="DB154" t="n">
+        <v>75</v>
+      </c>
+      <c r="DC154" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD154" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DE154" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DF154" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DG154" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DH154" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="DI154" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="DJ154" t="n">
+        <v>13</v>
+      </c>
+      <c r="DK154" t="n">
+        <v>7</v>
+      </c>
+      <c r="DL154" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DM154" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DN154" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="DO154" t="n">
+        <v>17</v>
+      </c>
+      <c r="DP154" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV154" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW154" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="DX154" t="n">
+        <v>7.72</v>
+      </c>
+      <c r="DY154" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="DZ154" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA154" t="inlineStr">
+        <is>
+          <t>16.13</t>
+        </is>
+      </c>
+      <c r="EB154" t="inlineStr">
+        <is>
+          <t>8.56</t>
+        </is>
+      </c>
+      <c r="EC154" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="ED154" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EE154" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="EF154" t="inlineStr"/>
+      <c r="EG154" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EH154" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EI154" t="inlineStr"/>
+      <c r="EJ154" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="EK154" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="EL154" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="EM154" t="inlineStr"/>
+      <c r="EN154" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EO154" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="EP154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Netherlands_Eredivisie_2025-2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>18</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Twente</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>PEC Zwolle</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>46032.73958333334</v>
+      </c>
+      <c r="G155" t="n">
+        <v>1</v>
+      </c>
+      <c r="H155" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" t="n">
+        <v>2</v>
+      </c>
+      <c r="J155" t="n">
+        <v>7</v>
+      </c>
+      <c r="K155" t="n">
+        <v>2</v>
+      </c>
+      <c r="L155" t="n">
+        <v>9</v>
+      </c>
+      <c r="M155" t="n">
+        <v>1</v>
+      </c>
+      <c r="N155" t="n">
+        <v>3</v>
+      </c>
+      <c r="O155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q155" t="n">
+        <v>7</v>
+      </c>
+      <c r="R155" t="n">
+        <v>1</v>
+      </c>
+      <c r="S155" t="n">
+        <v>19</v>
+      </c>
+      <c r="T155" t="n">
+        <v>2</v>
+      </c>
+      <c r="U155" t="n">
+        <v>26</v>
+      </c>
+      <c r="V155" t="n">
+        <v>3</v>
+      </c>
+      <c r="W155" t="n">
+        <v>6</v>
+      </c>
+      <c r="X155" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y155" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z155" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>De Grolsch Veste</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>Colosseum 65, Enschede</t>
+        </is>
+      </c>
+      <c r="AC155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD155" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE155" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF155" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AH155" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI155" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AJ155" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK155" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AL155" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM155" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN155" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AP155" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AQ155" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AR155" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AS155" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT155" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AU155" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW155" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AY155" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD155" t="n">
+        <v>70</v>
+      </c>
+      <c r="BE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK155" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM155" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN155" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR155" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS155" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT155" t="n">
+        <v>4</v>
+      </c>
+      <c r="BU155" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV155" t="n">
+        <v>95</v>
+      </c>
+      <c r="BW155" t="n">
+        <v>20</v>
+      </c>
+      <c r="BX155" t="n">
+        <v>150</v>
+      </c>
+      <c r="BY155" t="n">
+        <v>69</v>
+      </c>
+      <c r="BZ155" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CA155" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CB155" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CC155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP155" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR155" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS155" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU155" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV155" t="n">
+        <v>6</v>
+      </c>
+      <c r="CW155" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX155" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY155" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ155" t="n">
+        <v>70</v>
+      </c>
+      <c r="DA155" t="n">
+        <v>88</v>
+      </c>
+      <c r="DB155" t="n">
+        <v>46</v>
+      </c>
+      <c r="DC155" t="n">
+        <v>88</v>
+      </c>
+      <c r="DD155" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DE155" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="DF155" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG155" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DH155" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DI155" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="DJ155" t="n">
+        <v>31</v>
+      </c>
+      <c r="DK155" t="n">
+        <v>13</v>
+      </c>
+      <c r="DL155" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="DM155" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="DN155" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DO155" t="n">
+        <v>18</v>
+      </c>
+      <c r="DP155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU155" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV155" t="b">
+        <v>1</v>
+      </c>
+      <c r="DW155" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="DX155" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="DY155" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="DZ155" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="EA155" t="inlineStr">
+        <is>
+          <t>9.06</t>
+        </is>
+      </c>
+      <c r="EB155" t="inlineStr">
+        <is>
+          <t>5.78</t>
+        </is>
+      </c>
+      <c r="EC155" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="ED155" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="EE155" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="EF155" t="inlineStr"/>
+      <c r="EG155" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="EH155" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EI155" t="inlineStr"/>
+      <c r="EJ155" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EK155" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
+      </c>
+      <c r="EL155" t="inlineStr">
+        <is>
+          <t>1.15</t>
+        </is>
+      </c>
+      <c r="EM155" t="inlineStr">
+        <is>
+          <t>2.66</t>
+        </is>
+      </c>
+      <c r="EN155" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EO155" t="inlineStr">
+        <is>
+          <t>2.09</t>
+        </is>
+      </c>
+      <c r="EP155" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -81180,7 +81180,7 @@
         <v>0</v>
       </c>
       <c r="BF171" t="n">
-        <v>-1</v>
+        <v>16997</v>
       </c>
       <c r="BG171" t="n">
         <v>2</v>
@@ -81404,27 +81404,27 @@
       </c>
       <c r="EA171" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="EB171" t="inlineStr">
         <is>
-          <t>5.58</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="EC171" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="ED171" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EE171" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="EF171" t="inlineStr"/>
@@ -81433,28 +81433,28 @@
       <c r="EI171" t="inlineStr"/>
       <c r="EJ171" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="EK171" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="EL171" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="EM171" t="inlineStr"/>
       <c r="EN171" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EO171" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EP171" t="inlineStr"/>

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -84748,7 +84748,7 @@
         <v>0</v>
       </c>
       <c r="N179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O179" t="n">
         <v>0</v>
@@ -84800,7 +84800,7 @@
         <v>0</v>
       </c>
       <c r="AD179" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE179" t="n">
         <v>2.08</v>
@@ -84884,7 +84884,7 @@
         <v>0</v>
       </c>
       <c r="BF179" t="n">
-        <v>-1</v>
+        <v>22543</v>
       </c>
       <c r="BG179" t="n">
         <v>2</v>
@@ -84920,13 +84920,13 @@
         <v>0</v>
       </c>
       <c r="BR179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BS179" t="n">
         <v>1</v>
       </c>
       <c r="BT179" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU179" t="n">
         <v>1</v>

--- a/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
+++ b/data/matches/leagues/Netherlands_Eredivisie_2025-2026.xlsx
@@ -82989,10 +82989,10 @@
         <v>16</v>
       </c>
       <c r="Y181" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Z181" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
@@ -83445,10 +83445,10 @@
         <v>16</v>
       </c>
       <c r="Y182" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Z182" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
@@ -83867,13 +83867,13 @@
         <v>2</v>
       </c>
       <c r="S183" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T183" t="n">
         <v>6</v>
       </c>
       <c r="U183" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V183" t="n">
         <v>8</v>
@@ -84048,13 +84048,13 @@
         <v>143</v>
       </c>
       <c r="BZ183" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="CA183" t="n">
         <v>1.12</v>
       </c>
       <c r="CB183" t="n">
-        <v>2.21</v>
+        <v>2.27</v>
       </c>
       <c r="CC183" t="n">
         <v>0</v>
@@ -84444,7 +84444,7 @@
         <v>0</v>
       </c>
       <c r="BF184" t="n">
-        <v>-1</v>
+        <v>4500</v>
       </c>
       <c r="BG184" t="n">
         <v>2</v>
@@ -84805,10 +84805,10 @@
         <v>8</v>
       </c>
       <c r="Y185" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z185" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="AA185" t="inlineStr">
         <is>
@@ -86173,13 +86173,13 @@
         <v>1</v>
       </c>
       <c r="Q188" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R188" t="n">
         <v>5</v>
       </c>
       <c r="S188" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T188" t="n">
         <v>8</v>
@@ -86300,7 +86300,7 @@
         <v>0</v>
       </c>
       <c r="BF188" t="n">
-        <v>-1</v>
+        <v>6570</v>
       </c>
       <c r="BG188" t="n">
         <v>2</v>
@@ -86360,13 +86360,13 @@
         <v>75</v>
       </c>
       <c r="BZ188" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="CA188" t="n">
         <v>1.46</v>
       </c>
       <c r="CB188" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="CC188" t="n">
         <v>0</v>
